--- a/Results/Phase 2/Hydrogen/hydrogen eutrophication terrestrial results.xlsx
+++ b/Results/Phase 2/Hydrogen/hydrogen eutrophication terrestrial results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0204212547009088</v>
+        <v>0.02042125470090881</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01918706377773997</v>
+        <v>0.01918706377773998</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0199906549447186</v>
+        <v>0.01999065494471862</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03160246538820739</v>
+        <v>0.03160246538820736</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01972917337772709</v>
+        <v>0.01972917337772712</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02127518989315283</v>
+        <v>0.02127518989315286</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0204212547009088</v>
+        <v>0.02042125470090881</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0204212547009088</v>
+        <v>0.02042125470090881</v>
       </c>
       <c r="J2" t="n">
-        <v>0.02036662460227396</v>
+        <v>0.02036662460227398</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0204212547009088</v>
+        <v>0.02042125470090881</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0204212547009088</v>
+        <v>0.02042125470090881</v>
       </c>
       <c r="M2" t="n">
-        <v>0.02155091814663374</v>
+        <v>0.02155091814663375</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0202375211476918</v>
+        <v>0.02023752114769181</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0204212547009088</v>
+        <v>0.02042125470090881</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0204212547009088</v>
+        <v>0.02042125470090881</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0204212547009088</v>
+        <v>0.02042125470090881</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0204212547009088</v>
+        <v>0.02042125470090881</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0204212547009088</v>
+        <v>0.02042125470090881</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0204212547009088</v>
+        <v>0.02042125470090881</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0204212547009088</v>
+        <v>0.02042125470090881</v>
       </c>
       <c r="V2" t="n">
-        <v>0.01986178331308776</v>
+        <v>0.01986178331308778</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0204212547009088</v>
+        <v>0.02042125470090881</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0204212547009088</v>
+        <v>0.02042125470090881</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0204212547009088</v>
+        <v>0.02042125470090881</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0197440791879624</v>
+        <v>0.01974407918796241</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0204212547009088</v>
+        <v>0.02042125470090881</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0204212547009088</v>
+        <v>0.02042125470090881</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.019352538560144</v>
+        <v>0.01935253856014401</v>
       </c>
       <c r="C3" t="n">
-        <v>0.019352538560144</v>
+        <v>0.01935253856014401</v>
       </c>
       <c r="D3" t="n">
-        <v>0.019352538560144</v>
+        <v>0.01935253856014401</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03167968311056005</v>
+        <v>0.03167968311056004</v>
       </c>
       <c r="F3" t="n">
-        <v>0.019352538560144</v>
+        <v>0.01935253856014401</v>
       </c>
       <c r="G3" t="n">
-        <v>0.019352538560144</v>
+        <v>0.01935253856014401</v>
       </c>
       <c r="H3" t="n">
-        <v>0.019352538560144</v>
+        <v>0.01935253856014401</v>
       </c>
       <c r="I3" t="n">
-        <v>0.019352538560144</v>
+        <v>0.01935253856014401</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01929790221601007</v>
+        <v>0.01929790221601009</v>
       </c>
       <c r="K3" t="n">
-        <v>0.019352538560144</v>
+        <v>0.01935253856014401</v>
       </c>
       <c r="L3" t="n">
-        <v>0.019352538560144</v>
+        <v>0.01935253856014401</v>
       </c>
       <c r="M3" t="n">
-        <v>0.019352538560144</v>
+        <v>0.01935253856014401</v>
       </c>
       <c r="N3" t="n">
-        <v>0.019352538560144</v>
+        <v>0.01935253856014401</v>
       </c>
       <c r="O3" t="n">
-        <v>0.019352538560144</v>
+        <v>0.01935253856014401</v>
       </c>
       <c r="P3" t="n">
-        <v>0.019352538560144</v>
+        <v>0.01935253856014401</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.019352538560144</v>
+        <v>0.01935253856014401</v>
       </c>
       <c r="R3" t="n">
-        <v>0.019352538560144</v>
+        <v>0.01935253856014401</v>
       </c>
       <c r="S3" t="n">
-        <v>0.019352538560144</v>
+        <v>0.01935253856014401</v>
       </c>
       <c r="T3" t="n">
-        <v>0.019352538560144</v>
+        <v>0.01935253856014401</v>
       </c>
       <c r="U3" t="n">
-        <v>0.019352538560144</v>
+        <v>0.01935253856014401</v>
       </c>
       <c r="V3" t="n">
-        <v>0.01962193287548999</v>
+        <v>0.01962193287549</v>
       </c>
       <c r="W3" t="n">
-        <v>0.019352538560144</v>
+        <v>0.01935253856014401</v>
       </c>
       <c r="X3" t="n">
-        <v>0.019352538560144</v>
+        <v>0.01935253856014401</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.019352538560144</v>
+        <v>0.01935253856014401</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.019352538560144</v>
+        <v>0.01935253856014401</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.019352538560144</v>
+        <v>0.01935253856014401</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.019352538560144</v>
+        <v>0.01935253856014401</v>
       </c>
     </row>
     <row r="4">
@@ -762,67 +762,67 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4051656958603204</v>
+        <v>0.4051656958603205</v>
       </c>
       <c r="C4" t="n">
-        <v>0.08827100682018627</v>
+        <v>0.08827100682018635</v>
       </c>
       <c r="D4" t="n">
         <v>0.3336098917783584</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1642297773396481</v>
+        <v>0.1642297773396477</v>
       </c>
       <c r="F4" t="n">
-        <v>0.259236892826583</v>
+        <v>0.2592368928265824</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6612494821513238</v>
+        <v>0.6612494821513227</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3037526058346052</v>
+        <v>0.3037526058346055</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3711542188870923</v>
+        <v>0.3711542188870915</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4346017613351975</v>
+        <v>0.4346017613351976</v>
       </c>
       <c r="K4" t="n">
         <v>0.5543133095721685</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5547825272833818</v>
+        <v>0.5547825272833825</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8159926322291388</v>
+        <v>0.815992632229138</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5178801054120882</v>
+        <v>0.5178801054120877</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3507091055209436</v>
+        <v>0.3507091055209429</v>
       </c>
       <c r="P4" t="n">
-        <v>0.426428744488775</v>
+        <v>0.4264287444887747</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2263734711258452</v>
+        <v>0.2263734711258447</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2411717196975885</v>
+        <v>0.2411717196975888</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3551208231632211</v>
+        <v>0.3551208231632205</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3845311542128665</v>
+        <v>0.3845311542128664</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5178801054120882</v>
+        <v>0.5178801054120874</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1933935923579226</v>
+        <v>0.193393592357922</v>
       </c>
       <c r="W4" t="n">
         <v>0.2541344810156038</v>
@@ -831,16 +831,16 @@
         <v>0.3686955138564503</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3994917127866521</v>
+        <v>0.3994917127866506</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.236706988078106</v>
+        <v>0.2367069880781055</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.4043740225100186</v>
+        <v>0.4043740225100182</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8555613448048279</v>
+        <v>0.855561344804827</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01216827935555806</v>
+        <v>0.01216827935555808</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01216827935555805</v>
+        <v>0.01216827935555808</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01216827935555805</v>
+        <v>0.01216827935555808</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01216827935555805</v>
+        <v>0.01216827935555808</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01216827935555806</v>
+        <v>0.01216827935555808</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01216827935555805</v>
+        <v>0.01216827935555808</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01216827935555805</v>
+        <v>0.01216827935555808</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01216827935555805</v>
+        <v>0.01216827935555808</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01214255273478472</v>
+        <v>0.01214255273478474</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01216827935555805</v>
+        <v>0.01216827935555808</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01216827935555805</v>
+        <v>0.01216827935555808</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01216827935555805</v>
+        <v>0.01216827935555808</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01216827935555806</v>
+        <v>0.01216827935555808</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01216827935555806</v>
+        <v>0.01216827935555808</v>
       </c>
       <c r="P5" t="n">
-        <v>0.01216827935555806</v>
+        <v>0.01216827935555808</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01216827935555806</v>
+        <v>0.01216827935555808</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01216827935555805</v>
+        <v>0.01216827935555808</v>
       </c>
       <c r="S5" t="n">
-        <v>0.01216827935555805</v>
+        <v>0.01216827935555808</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01216827935555805</v>
+        <v>0.01216827935555808</v>
       </c>
       <c r="U5" t="n">
-        <v>0.01178025551659279</v>
+        <v>0.01178025551659281</v>
       </c>
       <c r="V5" t="n">
-        <v>0.01200447474277782</v>
+        <v>0.01200447474277781</v>
       </c>
       <c r="W5" t="n">
-        <v>0.01216827935555806</v>
+        <v>0.01216827935555808</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01216827935555806</v>
+        <v>0.01216827935555808</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.01178025551659279</v>
+        <v>0.01178025551659281</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.01216827935555805</v>
+        <v>0.01216827935555808</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.01216827935555805</v>
+        <v>0.01216827935555808</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.01216827935555806</v>
+        <v>0.01216827935555808</v>
       </c>
     </row>
     <row r="6">
@@ -938,82 +938,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01655098255370925</v>
+        <v>0.02620662800926959</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02620662800926957</v>
+        <v>0.02620662800926959</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01655098255370925</v>
+        <v>0.01655098255370926</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02620662800926957</v>
+        <v>0.01655098255370926</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01655098255370925</v>
+        <v>0.02620662800926959</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01655098255370925</v>
+        <v>0.02620662800926959</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02620662800926957</v>
+        <v>0.02620662800926959</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02620662800926957</v>
+        <v>0.01655098255370926</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01652525593293577</v>
+        <v>0.02618090138849621</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01655098255370925</v>
+        <v>0.01655098255370926</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02620662800926957</v>
+        <v>0.01655098255370926</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01655098255370925</v>
+        <v>0.01655098255370926</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01660149317886549</v>
+        <v>0.01660149317886546</v>
       </c>
       <c r="O6" t="n">
-        <v>0.02618776177761992</v>
+        <v>0.02618776177761996</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0261877727832376</v>
+        <v>0.02618777278323765</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01655098255370925</v>
+        <v>0.01655098255370926</v>
       </c>
       <c r="R6" t="n">
-        <v>0.02620662800926957</v>
+        <v>0.01655098255370926</v>
       </c>
       <c r="S6" t="n">
-        <v>0.02620662800926957</v>
+        <v>0.02620662800926959</v>
       </c>
       <c r="T6" t="n">
-        <v>0.01655098255370925</v>
+        <v>0.01655098255370926</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01655098255370925</v>
+        <v>0.01655098255370926</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0260428233964893</v>
+        <v>0.02604282339648929</v>
       </c>
       <c r="W6" t="n">
-        <v>0.01699457204380148</v>
+        <v>0.0261877664299737</v>
       </c>
       <c r="X6" t="n">
-        <v>0.02620662800926957</v>
+        <v>0.02620662800926959</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01691017268263736</v>
+        <v>0.01691017268263769</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.01655098255370925</v>
+        <v>0.01655098255370926</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.02620662800926957</v>
+        <v>0.01655098255370926</v>
       </c>
       <c r="AB6" t="n">
         <v>0.01675152510799897</v>
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01836858694724599</v>
+        <v>0.018368586947246</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01836858694724599</v>
+        <v>0.018368586947246</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01836858694724599</v>
+        <v>0.018368586947246</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01836858694724599</v>
+        <v>0.018368586947246</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01836858694724599</v>
+        <v>0.018368586947246</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01836858694724599</v>
+        <v>0.018368586947246</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01836858694724599</v>
+        <v>0.018368586947246</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01836858694724599</v>
+        <v>0.018368586947246</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01834286032647265</v>
+        <v>0.01834286032647264</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01836858694724599</v>
+        <v>0.018368586947246</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01836858694724599</v>
+        <v>0.018368586947246</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01836858694724599</v>
+        <v>0.018368586947246</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01836858694724599</v>
+        <v>0.018368586947246</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01836780671630152</v>
+        <v>0.01836780671630151</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01836780671630152</v>
+        <v>0.01836780671630151</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.01836858694724599</v>
+        <v>0.018368586947246</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01836858694724599</v>
+        <v>0.018368586947246</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01836858694724599</v>
+        <v>0.018368586947246</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01836858694724599</v>
+        <v>0.018368586947246</v>
       </c>
       <c r="U7" t="n">
         <v>0.01835895778626274</v>
       </c>
       <c r="V7" t="n">
-        <v>0.01820478233446575</v>
+        <v>0.01820478233446573</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01836858694724599</v>
+        <v>0.018368586947246</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01836858694724599</v>
+        <v>0.018368586947246</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01836858694724599</v>
+        <v>0.018368586947246</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.01836858694724599</v>
+        <v>0.018368586947246</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01836858694724599</v>
+        <v>0.018368586947246</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01836858694724599</v>
+        <v>0.018368586947246</v>
       </c>
     </row>
     <row r="8">
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02662426929110961</v>
+        <v>0.02662426929110966</v>
       </c>
       <c r="C8" t="n">
         <v>0.03829027390056613</v>
@@ -1123,13 +1123,13 @@
         <v>0.03829027390056613</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03829027390056613</v>
+        <v>0.03207847057197339</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02844169646558284</v>
+        <v>0.02844169646558286</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03829027390056613</v>
+        <v>0.04070929595317145</v>
       </c>
       <c r="H8" t="n">
         <v>0.03829027390056613</v>
@@ -1138,7 +1138,7 @@
         <v>0.03829027390056613</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03826454727979269</v>
+        <v>0.03826454727979273</v>
       </c>
       <c r="K8" t="n">
         <v>0.03829027390056613</v>
@@ -1147,19 +1147,19 @@
         <v>0.03829027390056613</v>
       </c>
       <c r="M8" t="n">
-        <v>0.03829027390056613</v>
+        <v>0.03829027390056604</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02924716864774655</v>
+        <v>0.02924716864774657</v>
       </c>
       <c r="O8" t="n">
-        <v>0.03173229249033363</v>
+        <v>0.03173229249033369</v>
       </c>
       <c r="P8" t="n">
-        <v>0.03112312858759445</v>
+        <v>0.03112312858759449</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.02433163312223481</v>
+        <v>0.02433163312223482</v>
       </c>
       <c r="R8" t="n">
         <v>0.03829027390056613</v>
@@ -1171,28 +1171,28 @@
         <v>0.03829027390056613</v>
       </c>
       <c r="U8" t="n">
-        <v>0.03110518280464715</v>
+        <v>0.03258939505055398</v>
       </c>
       <c r="V8" t="n">
-        <v>0.03812646928778581</v>
+        <v>0.03493041047865753</v>
       </c>
       <c r="W8" t="n">
-        <v>0.03829256660306303</v>
+        <v>0.03829256660306308</v>
       </c>
       <c r="X8" t="n">
-        <v>0.02540084562436908</v>
+        <v>0.0254008456243691</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.04987778521230205</v>
+        <v>0.04987778521230211</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.03829027390056613</v>
+        <v>0.02640756726628789</v>
       </c>
       <c r="AA8" t="n">
         <v>0.03829027390056613</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.05047639120903366</v>
+        <v>0.05047639120903373</v>
       </c>
     </row>
     <row r="9">
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.04147437298427204</v>
+        <v>0.04147437298427201</v>
       </c>
       <c r="C9" t="n">
         <v>0.05065891329493195</v>
@@ -1211,13 +1211,13 @@
         <v>0.05065891329493195</v>
       </c>
       <c r="E9" t="n">
-        <v>0.05065891329493195</v>
+        <v>0.04853915982411511</v>
       </c>
       <c r="F9" t="n">
-        <v>0.05065891329493195</v>
+        <v>0.02948603953427393</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05065891329493195</v>
+        <v>0.05065891455574938</v>
       </c>
       <c r="H9" t="n">
         <v>0.05065891329493195</v>
@@ -1226,7 +1226,7 @@
         <v>0.05065891329493195</v>
       </c>
       <c r="J9" t="n">
-        <v>0.05063318667415859</v>
+        <v>0.0506331866741586</v>
       </c>
       <c r="K9" t="n">
         <v>0.05065891329493195</v>
@@ -1241,13 +1241,13 @@
         <v>0.05065891329493195</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05370265960640703</v>
+        <v>0.05370265960640701</v>
       </c>
       <c r="P9" t="n">
-        <v>0.05436462193305405</v>
+        <v>0.05436462193305403</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.05065891455574941</v>
+        <v>0.05065891455574938</v>
       </c>
       <c r="R9" t="n">
         <v>0.05065891329493195</v>
@@ -1262,7 +1262,7 @@
         <v>0.05065891329493195</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0504951086821517</v>
+        <v>0.06109386178077986</v>
       </c>
       <c r="W9" t="n">
         <v>0.05065891329493195</v>
@@ -1274,7 +1274,7 @@
         <v>0.05065891329493195</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.05065891329493195</v>
+        <v>0.04512145270945137</v>
       </c>
       <c r="AA9" t="n">
         <v>0.05065891329493195</v>
@@ -1290,37 +1290,37 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01069630917730202</v>
+        <v>0.01069630917730203</v>
       </c>
       <c r="C10" t="n">
-        <v>0.01789227971151743</v>
+        <v>0.01789227971151744</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01318691936666639</v>
+        <v>0.0131869193666664</v>
       </c>
       <c r="E10" t="n">
-        <v>0.02852679448997849</v>
+        <v>0.02852679448997843</v>
       </c>
       <c r="F10" t="n">
         <v>0.01474120902811138</v>
       </c>
       <c r="G10" t="n">
-        <v>0.005456143942550022</v>
+        <v>0.005456143942550034</v>
       </c>
       <c r="H10" t="n">
-        <v>0.01401315759229182</v>
+        <v>0.01401315759229184</v>
       </c>
       <c r="I10" t="n">
         <v>0.01255145282745157</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01051789985243076</v>
+        <v>0.01051789985243078</v>
       </c>
       <c r="K10" t="n">
         <v>0.008844201830993288</v>
       </c>
       <c r="L10" t="n">
-        <v>0.008263802544459081</v>
+        <v>0.008263802544459098</v>
       </c>
       <c r="M10" t="n">
         <v>0.004105740366160971</v>
@@ -1329,46 +1329,46 @@
         <v>0.01170865635689385</v>
       </c>
       <c r="O10" t="n">
-        <v>0.01171654632688889</v>
+        <v>0.0117165463268889</v>
       </c>
       <c r="P10" t="n">
-        <v>0.01038129457712247</v>
+        <v>0.01038129457712245</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.01515518218614608</v>
+        <v>0.01515518218614609</v>
       </c>
       <c r="R10" t="n">
         <v>0.0150842478439738</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01205110955423234</v>
+        <v>0.01205110955423236</v>
       </c>
       <c r="T10" t="n">
-        <v>0.01223766246171117</v>
+        <v>0.01223766246171118</v>
       </c>
       <c r="U10" t="n">
-        <v>0.008803949465409973</v>
+        <v>0.00880394946540998</v>
       </c>
       <c r="V10" t="n">
-        <v>0.01569408441308532</v>
+        <v>0.01569408441308534</v>
       </c>
       <c r="W10" t="n">
-        <v>0.01446510792955013</v>
+        <v>0.01446510792955014</v>
       </c>
       <c r="X10" t="n">
-        <v>0.01241222099051283</v>
+        <v>0.01241222099051284</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.01152408594766493</v>
+        <v>0.01152408594766494</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.01456257383345109</v>
+        <v>0.0145625738334511</v>
       </c>
       <c r="AA10" t="n">
         <v>0.01147514108312133</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.003880637926446238</v>
+        <v>0.003880637926446261</v>
       </c>
     </row>
     <row r="11">
@@ -1378,85 +1378,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.01648264274594943</v>
+        <v>0.01648264274594944</v>
       </c>
       <c r="C11" t="n">
-        <v>0.01852264134804606</v>
+        <v>0.01852264134804608</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01718527856302379</v>
+        <v>0.01718527856302381</v>
       </c>
       <c r="E11" t="n">
-        <v>0.03016789101818285</v>
+        <v>0.03016789101818283</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01763100374521697</v>
+        <v>0.017631003745217</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01495228605696555</v>
+        <v>0.01495228605696556</v>
       </c>
       <c r="H11" t="n">
-        <v>0.01799181934493852</v>
+        <v>0.01799181934493853</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01732673901875951</v>
+        <v>0.01732673901875952</v>
       </c>
       <c r="J11" t="n">
-        <v>0.01637169554663799</v>
+        <v>0.016371695546638</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01563992800106303</v>
+        <v>0.01563992800106306</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01537584447606722</v>
+        <v>0.01537584447606724</v>
       </c>
       <c r="M11" t="n">
-        <v>0.01461357637970855</v>
+        <v>0.01461357637970858</v>
       </c>
       <c r="N11" t="n">
-        <v>0.01675953038560574</v>
+        <v>0.01675953038560575</v>
       </c>
       <c r="O11" t="n">
-        <v>0.01694685390031434</v>
+        <v>0.01694685390031436</v>
       </c>
       <c r="P11" t="n">
-        <v>0.01633931009897577</v>
+        <v>0.01633931009897578</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.01851144417455867</v>
+        <v>0.0185114441745587</v>
       </c>
       <c r="R11" t="n">
-        <v>0.01847916882281594</v>
+        <v>0.01847916882281595</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01709908123494538</v>
+        <v>0.0170990812349454</v>
       </c>
       <c r="T11" t="n">
-        <v>0.01718396340235706</v>
+        <v>0.01718396340235708</v>
       </c>
       <c r="U11" t="n">
-        <v>0.01562161304644598</v>
+        <v>0.01562161304644599</v>
       </c>
       <c r="V11" t="n">
-        <v>0.01807459974538327</v>
+        <v>0.01807459974538329</v>
       </c>
       <c r="W11" t="n">
-        <v>0.01819745818867133</v>
+        <v>0.01819745818867135</v>
       </c>
       <c r="X11" t="n">
-        <v>0.01726338808924685</v>
+        <v>0.01726338808924687</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.01685928381443262</v>
+        <v>0.01685928381443264</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.01756462997260526</v>
+        <v>0.01756462997260528</v>
       </c>
       <c r="AA11" t="n">
         <v>0.01683701374508726</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.01338149060655455</v>
+        <v>0.01338149060655458</v>
       </c>
     </row>
   </sheetData>
@@ -1622,28 +1622,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01655442928491939</v>
+        <v>0.01655442928491938</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01673178523090994</v>
+        <v>0.01673178523090995</v>
       </c>
       <c r="D2" t="n">
         <v>0.01663145551983868</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0301384148025764</v>
+        <v>0.03013841480257641</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01680242863818362</v>
+        <v>0.01680242863818361</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01605358519754135</v>
+        <v>0.01605358519754136</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01666473633415973</v>
+        <v>0.01666473633415974</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01665582399359501</v>
+        <v>0.016655823993595</v>
       </c>
       <c r="J2" t="n">
         <v>0.01673555931210815</v>
@@ -1664,28 +1664,28 @@
         <v>0.01686252999327875</v>
       </c>
       <c r="P2" t="n">
-        <v>0.01675800145715145</v>
+        <v>0.01675800145715144</v>
       </c>
       <c r="Q2" t="n">
         <v>0.01661509701742528</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01686163832716437</v>
+        <v>0.01686163832716438</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01683631967840701</v>
+        <v>0.01683631967840702</v>
       </c>
       <c r="T2" t="n">
         <v>0.01672130611043378</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01675080417561687</v>
+        <v>0.01675080417561688</v>
       </c>
       <c r="V2" t="n">
-        <v>0.01628589242725457</v>
+        <v>0.01628589242725455</v>
       </c>
       <c r="W2" t="n">
-        <v>0.01694687313989553</v>
+        <v>0.01694687313989552</v>
       </c>
       <c r="X2" t="n">
         <v>0.0172197749653724</v>
@@ -1700,7 +1700,7 @@
         <v>0.01705549449964071</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.01592235621016882</v>
+        <v>0.0159223562101688</v>
       </c>
     </row>
     <row r="3">
@@ -1710,16 +1710,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01686324715592903</v>
+        <v>0.01686324715592904</v>
       </c>
       <c r="C3" t="n">
         <v>0.01695884199141053</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01686324715592903</v>
+        <v>0.01686324715592904</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03062540641792296</v>
+        <v>0.03062540641792295</v>
       </c>
       <c r="F3" t="n">
         <v>0.01692507342164109</v>
@@ -1728,67 +1728,67 @@
         <v>0.01614369304746751</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01686324715592903</v>
+        <v>0.01686324715592904</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01686324715592903</v>
+        <v>0.01686324715592904</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0168574306542875</v>
+        <v>0.01685743065428751</v>
       </c>
       <c r="K3" t="n">
         <v>0.01689550760470439</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01686324715592903</v>
+        <v>0.01686324715592904</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01686324715592903</v>
+        <v>0.01686324715592904</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01686324715592903</v>
+        <v>0.01686324715592904</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01686324715592903</v>
+        <v>0.01686324715592904</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01686324715592903</v>
+        <v>0.01686324715592904</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01686324715592903</v>
+        <v>0.01686324715592904</v>
       </c>
       <c r="R3" t="n">
         <v>0.01667904116133525</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01686324715592903</v>
+        <v>0.01686324715592904</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01686324715592903</v>
+        <v>0.01686324715592904</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01686324715592903</v>
+        <v>0.01686324715592904</v>
       </c>
       <c r="V3" t="n">
         <v>0.01638971193570019</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01686324715592903</v>
+        <v>0.01686324715592904</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01659934619108268</v>
+        <v>0.01659934619108269</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01686324715592903</v>
+        <v>0.01686324715592904</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01686999452198791</v>
+        <v>0.01686999452198792</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.01686324715592903</v>
+        <v>0.01686324715592904</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01616146702951217</v>
+        <v>0.01616146702951218</v>
       </c>
     </row>
     <row r="4">
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02762596628780544</v>
+        <v>0.02762596628780547</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0513894564221966</v>
+        <v>0.05138945642219666</v>
       </c>
       <c r="D4" t="n">
-        <v>0.04877879935406351</v>
+        <v>0.04877879935406357</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03504056716191095</v>
+        <v>0.03504056716191104</v>
       </c>
       <c r="F4" t="n">
-        <v>0.07861005011863523</v>
+        <v>0.07861005011863513</v>
       </c>
       <c r="G4" t="n">
-        <v>0.06250584829852024</v>
+        <v>0.06250584829851992</v>
       </c>
       <c r="H4" t="n">
-        <v>0.06055218038129247</v>
+        <v>0.06055218038129242</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05631311406135097</v>
+        <v>0.05631311406135088</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0727142826254976</v>
+        <v>0.07271428262549759</v>
       </c>
       <c r="K4" t="n">
         <v>0.07436518108139233</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1188804527137261</v>
+        <v>0.1188804527137259</v>
       </c>
       <c r="M4" t="n">
-        <v>0.05532740127946098</v>
+        <v>0.05532740127946096</v>
       </c>
       <c r="N4" t="n">
         <v>0.07476890443344904</v>
       </c>
       <c r="O4" t="n">
-        <v>0.09602503222091542</v>
+        <v>0.09602503222091534</v>
       </c>
       <c r="P4" t="n">
-        <v>0.07327697541276118</v>
+        <v>0.07327697541276115</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.04331086215234196</v>
+        <v>0.04331086215234198</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1574188222035166</v>
+        <v>0.1574188222035165</v>
       </c>
       <c r="S4" t="n">
-        <v>0.09108599763725243</v>
+        <v>0.09108599763725229</v>
       </c>
       <c r="T4" t="n">
-        <v>0.07373849627976282</v>
+        <v>0.07373849627976292</v>
       </c>
       <c r="U4" t="n">
-        <v>0.07188377808514683</v>
+        <v>0.0718837780851467</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0723377354161937</v>
+        <v>0.07233773541619379</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1276531280495307</v>
+        <v>0.1276531280495306</v>
       </c>
       <c r="X4" t="n">
-        <v>0.2501661993786516</v>
+        <v>0.2501661993786509</v>
       </c>
       <c r="Y4" t="n">
         <v>0.1592584077747666</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.05485315980595046</v>
+        <v>0.05485315980595048</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.1569983605996296</v>
+        <v>0.1569983605996297</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.03353498224071623</v>
+        <v>0.03353498224071635</v>
       </c>
     </row>
     <row r="5">
@@ -1886,85 +1886,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.007359973922821489</v>
+        <v>0.007359973922821499</v>
       </c>
       <c r="C5" t="n">
-        <v>0.007359973922821495</v>
+        <v>0.007359973922821508</v>
       </c>
       <c r="D5" t="n">
-        <v>0.007359973922821495</v>
+        <v>0.007359973922821508</v>
       </c>
       <c r="E5" t="n">
-        <v>0.007359973922821495</v>
+        <v>0.007359973922821508</v>
       </c>
       <c r="F5" t="n">
-        <v>0.007359973922821486</v>
+        <v>0.0073599739228215</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007359973922821495</v>
+        <v>0.007359973922821508</v>
       </c>
       <c r="H5" t="n">
-        <v>0.007359973922821495</v>
+        <v>0.007359973922821508</v>
       </c>
       <c r="I5" t="n">
-        <v>0.007359973922821495</v>
+        <v>0.007359973922821508</v>
       </c>
       <c r="J5" t="n">
-        <v>0.007341997807024963</v>
+        <v>0.007341997807024967</v>
       </c>
       <c r="K5" t="n">
-        <v>0.007359973922821495</v>
+        <v>0.007359973922821508</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007359973922821495</v>
+        <v>0.007359973922821508</v>
       </c>
       <c r="M5" t="n">
-        <v>0.007359973922821495</v>
+        <v>0.007359973922821508</v>
       </c>
       <c r="N5" t="n">
         <v>0.07476890443344904</v>
       </c>
       <c r="O5" t="n">
-        <v>0.007359973922821488</v>
+        <v>0.0073599739228215</v>
       </c>
       <c r="P5" t="n">
-        <v>0.007359973922821488</v>
+        <v>0.0073599739228215</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.007359973922821488</v>
+        <v>0.0073599739228215</v>
       </c>
       <c r="R5" t="n">
-        <v>0.007359973922821495</v>
+        <v>0.007359973922821508</v>
       </c>
       <c r="S5" t="n">
-        <v>0.007359973922821495</v>
+        <v>0.007359973922821508</v>
       </c>
       <c r="T5" t="n">
-        <v>0.007359973922821495</v>
+        <v>0.007359973922821508</v>
       </c>
       <c r="U5" t="n">
-        <v>0.00710992336563279</v>
+        <v>0.007109923365632789</v>
       </c>
       <c r="V5" t="n">
-        <v>0.007244540683732413</v>
+        <v>0.007244540683732406</v>
       </c>
       <c r="W5" t="n">
-        <v>0.007359973922821492</v>
+        <v>0.007359973922821509</v>
       </c>
       <c r="X5" t="n">
-        <v>0.007359973922821488</v>
+        <v>0.0073599739228215</v>
       </c>
       <c r="Y5" t="n">
         <v>0.00710992336563279</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.007359973922821495</v>
+        <v>0.007359973922821508</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.007359973922821495</v>
+        <v>0.007359973922821508</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.007359973922821488</v>
+        <v>0.0073599739228215</v>
       </c>
     </row>
     <row r="6">
@@ -1974,85 +1974,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01682573316854054</v>
+        <v>0.01093485872280391</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01682573316854054</v>
+        <v>0.01093485872280391</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01682573316854054</v>
+        <v>0.0168257331685406</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01682573316854054</v>
+        <v>0.01093485872280391</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01682573316854054</v>
+        <v>0.01093485872280391</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01093485872280388</v>
+        <v>0.0168257331685406</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01093485872280388</v>
+        <v>0.0168257331685406</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01093485872280388</v>
+        <v>0.0168257331685406</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01091688260700733</v>
+        <v>0.01680775705274403</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01682573316854054</v>
+        <v>0.01093485872280391</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01093485872280388</v>
+        <v>0.0168257331685406</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01093485872280388</v>
+        <v>0.0168257331685406</v>
       </c>
       <c r="N6" t="n">
         <v>0.07476890443344904</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01709328391214284</v>
+        <v>0.01709328391214287</v>
       </c>
       <c r="P6" t="n">
-        <v>0.01072404645372659</v>
+        <v>0.01690400303534717</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01682573316854054</v>
+        <v>0.0168257331685406</v>
       </c>
       <c r="R6" t="n">
-        <v>0.01093485872280388</v>
+        <v>0.0168257331685406</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01093485872280388</v>
+        <v>0.0168257331685406</v>
       </c>
       <c r="T6" t="n">
-        <v>0.01682573316854054</v>
+        <v>0.01093485872280391</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01093485872280388</v>
+        <v>0.0168257331685406</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0108194254837148</v>
+        <v>0.01671029992945149</v>
       </c>
       <c r="W6" t="n">
-        <v>0.01131744000390634</v>
+        <v>0.01131744000390635</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01093485872280388</v>
+        <v>0.01093485872280391</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01136384357272531</v>
+        <v>0.0113638435727254</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.01682573316854054</v>
+        <v>0.01093485872280391</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.01093485872280388</v>
+        <v>0.01093485872280391</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.01093251608217372</v>
+        <v>0.01093251608217376</v>
       </c>
     </row>
     <row r="7">
@@ -2119,10 +2119,10 @@
         <v>0.01108485729109595</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01107673674702552</v>
+        <v>0.01107673674702553</v>
       </c>
       <c r="V7" t="n">
-        <v>0.01096942405200686</v>
+        <v>0.01096942405200687</v>
       </c>
       <c r="W7" t="n">
         <v>0.01108485729109595</v>
@@ -2150,85 +2150,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01687638786835714</v>
+        <v>0.01687638786835719</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0246266651773392</v>
+        <v>0.02462666517733934</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0246266651773392</v>
+        <v>0.02462666517733934</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0246266651773392</v>
+        <v>0.0204998711293686</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01808379049357587</v>
+        <v>0.01808379049357594</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0246266651773392</v>
+        <v>0.02623373566565129</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0246266651773392</v>
+        <v>0.02462666517733934</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0246266651773392</v>
+        <v>0.02462666517733934</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02460868906154271</v>
+        <v>0.02460868906154283</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0246266651773392</v>
+        <v>0.02462666517733934</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0246266651773392</v>
+        <v>0.02462666517733934</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0246266651773392</v>
+        <v>0.02462666517733864</v>
       </c>
       <c r="N8" t="n">
         <v>0.07476890443344904</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02026988869589075</v>
+        <v>0.02026988869589084</v>
       </c>
       <c r="P8" t="n">
-        <v>0.01986519237257598</v>
+        <v>0.01986519237257602</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01535328148593725</v>
+        <v>0.0153532814859373</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0246266651773392</v>
+        <v>0.02462666517733934</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0246266651773392</v>
+        <v>0.02462666517733934</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0246266651773392</v>
+        <v>0.02462666517733934</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01985211878024941</v>
+        <v>0.02083807619156374</v>
       </c>
       <c r="V8" t="n">
-        <v>0.02451123193825015</v>
+        <v>0.02238658683237474</v>
       </c>
       <c r="W8" t="n">
-        <v>0.02462818832796883</v>
+        <v>0.02462818832796887</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01606360980077431</v>
+        <v>0.01606360980077436</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0323226980539256</v>
+        <v>0.03232269805392571</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0246266651773392</v>
+        <v>0.01673242248841506</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.0246266651773392</v>
+        <v>0.02462666517733934</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.03272247789336476</v>
+        <v>0.0327224778933649</v>
       </c>
     </row>
     <row r="9">
@@ -2241,82 +2241,82 @@
         <v>0.01819474594688021</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02193267749913864</v>
+        <v>0.02193267749913867</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02193267749913864</v>
+        <v>0.02193267749913867</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02193267749913864</v>
+        <v>0.02106998032494077</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02193267749913864</v>
+        <v>0.01331572139136259</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02193267749913864</v>
+        <v>0.02193268033495099</v>
       </c>
       <c r="H9" t="n">
-        <v>0.02193267749913864</v>
+        <v>0.02193267749913867</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02193267749913864</v>
+        <v>0.02193267749913867</v>
       </c>
       <c r="J9" t="n">
-        <v>0.02191470138334211</v>
+        <v>0.02191470138334209</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02193267749913864</v>
+        <v>0.02193267749913867</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02193267749913864</v>
+        <v>0.02193267749913867</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02193267749913864</v>
+        <v>0.02193267749913867</v>
       </c>
       <c r="N9" t="n">
         <v>0.07476890443344904</v>
       </c>
       <c r="O9" t="n">
-        <v>0.02317142689675122</v>
+        <v>0.02317142689675124</v>
       </c>
       <c r="P9" t="n">
-        <v>0.02344083302063023</v>
+        <v>0.02344083302063026</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.02193268033495097</v>
+        <v>0.02193268033495099</v>
       </c>
       <c r="R9" t="n">
-        <v>0.02193267749913864</v>
+        <v>0.02193267749913867</v>
       </c>
       <c r="S9" t="n">
-        <v>0.02193267749913864</v>
+        <v>0.02193267749913867</v>
       </c>
       <c r="T9" t="n">
-        <v>0.02193267749913864</v>
+        <v>0.02193267749913867</v>
       </c>
       <c r="U9" t="n">
-        <v>0.02193267749913864</v>
+        <v>0.02193267749913867</v>
       </c>
       <c r="V9" t="n">
-        <v>0.02181724426004955</v>
+        <v>0.02613073969270598</v>
       </c>
       <c r="W9" t="n">
-        <v>0.02193267749913864</v>
+        <v>0.02193267749913867</v>
       </c>
       <c r="X9" t="n">
-        <v>0.02193267749913864</v>
+        <v>0.02193267749913867</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.02193267749913864</v>
+        <v>0.02193267749913867</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.02193267749913864</v>
+        <v>0.0196790382890391</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.02193267749913864</v>
+        <v>0.02193267749913867</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.02193267749913864</v>
+        <v>0.02193267749913867</v>
       </c>
     </row>
     <row r="10">
@@ -2326,28 +2326,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01638339926101105</v>
+        <v>0.01638339926101106</v>
       </c>
       <c r="C10" t="n">
-        <v>0.01595815564932333</v>
+        <v>0.01595815564932331</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01593971585687328</v>
+        <v>0.01593971585687329</v>
       </c>
       <c r="E10" t="n">
-        <v>0.02991200422923433</v>
+        <v>0.02991200422923431</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01533881726433329</v>
+        <v>0.0153388172643333</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01473238352127479</v>
+        <v>0.01473238352127481</v>
       </c>
       <c r="H10" t="n">
-        <v>0.01575236505895436</v>
+        <v>0.01575236505895437</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01579898590400361</v>
+        <v>0.01579898590400362</v>
       </c>
       <c r="J10" t="n">
         <v>0.01527686698406159</v>
@@ -2356,22 +2356,22 @@
         <v>0.01525611237190064</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01402917269277182</v>
+        <v>0.01402917269277183</v>
       </c>
       <c r="M10" t="n">
         <v>0.0158079547557886</v>
       </c>
       <c r="N10" t="n">
-        <v>0.01535837682366118</v>
+        <v>0.01535837682366119</v>
       </c>
       <c r="O10" t="n">
-        <v>0.01454792828595332</v>
+        <v>0.01454792828595333</v>
       </c>
       <c r="P10" t="n">
-        <v>0.01516895417442305</v>
+        <v>0.01516895417442306</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.01603340150100862</v>
+        <v>0.01603340150100863</v>
       </c>
       <c r="R10" t="n">
         <v>0.0134340613893173</v>
@@ -2389,19 +2389,19 @@
         <v>0.01473000191175278</v>
       </c>
       <c r="W10" t="n">
-        <v>0.01407106771337269</v>
+        <v>0.0140710677133727</v>
       </c>
       <c r="X10" t="n">
         <v>0.01081154644846449</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.01339892831664428</v>
+        <v>0.01339892831664429</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.01562403821270587</v>
+        <v>0.01562403821270588</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.01343278415790198</v>
+        <v>0.01343278415790199</v>
       </c>
       <c r="AB10" t="n">
         <v>0.01563516473704181</v>
@@ -2420,28 +2420,28 @@
         <v>0.0162764697562621</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01621124583564866</v>
+        <v>0.01621124583564867</v>
       </c>
       <c r="E11" t="n">
         <v>0.02981381453324524</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01608067703151015</v>
+        <v>0.01608067703151014</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01541143486554706</v>
+        <v>0.01541143486554707</v>
       </c>
       <c r="H11" t="n">
         <v>0.01615928143986504</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01617158173236955</v>
+        <v>0.01617158173236954</v>
       </c>
       <c r="J11" t="n">
         <v>0.01601639780519778</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01603682068452177</v>
+        <v>0.01603682068452176</v>
       </c>
       <c r="L11" t="n">
         <v>0.01566365557491149</v>
@@ -2456,43 +2456,43 @@
         <v>0.01580905252895635</v>
       </c>
       <c r="P11" t="n">
-        <v>0.01598709275117487</v>
+        <v>0.01598709275117486</v>
       </c>
       <c r="Q11" t="n">
         <v>0.0162375145998753</v>
       </c>
       <c r="R11" t="n">
-        <v>0.01538516218975924</v>
+        <v>0.01538516218975925</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01585798011929786</v>
+        <v>0.01585798011929785</v>
       </c>
       <c r="T11" t="n">
         <v>0.016062048004173</v>
       </c>
       <c r="U11" t="n">
-        <v>0.01600488510345586</v>
+        <v>0.01600488510345587</v>
       </c>
       <c r="V11" t="n">
-        <v>0.0155307190771765</v>
+        <v>0.01553071907717649</v>
       </c>
       <c r="W11" t="n">
-        <v>0.01567642259538446</v>
+        <v>0.01567642259538445</v>
       </c>
       <c r="X11" t="n">
         <v>0.01458630763785772</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.01548543217029356</v>
+        <v>0.01548543217029357</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.01612269032302412</v>
+        <v>0.01612269032302413</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.01549462290330147</v>
+        <v>0.01549462290330148</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.01568288698986892</v>
+        <v>0.01568288698986891</v>
       </c>
     </row>
   </sheetData>
@@ -2658,16 +2658,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01949418417658755</v>
+        <v>0.01949418417658754</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01858988736383843</v>
+        <v>0.01858988736383842</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01924892008570208</v>
+        <v>0.01924892008570209</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03122443543630904</v>
+        <v>0.03122443543630909</v>
       </c>
       <c r="F2" t="n">
         <v>0.01883684839496588</v>
@@ -2676,67 +2676,67 @@
         <v>0.01968439530828012</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01949418417658755</v>
+        <v>0.01949418417658754</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01949418417658755</v>
+        <v>0.01949418417658754</v>
       </c>
       <c r="J2" t="n">
         <v>0.01944730622133877</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01951039684922096</v>
+        <v>0.01951039684922095</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01949418417658755</v>
+        <v>0.01949418417658754</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0201195740971788</v>
+        <v>0.02011957409717881</v>
       </c>
       <c r="N2" t="n">
-        <v>0.01917279219484106</v>
+        <v>0.01917279219484105</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01949418417658755</v>
+        <v>0.01949418417658754</v>
       </c>
       <c r="P2" t="n">
-        <v>0.01949418417658755</v>
+        <v>0.01949418417658754</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.01949418417658755</v>
+        <v>0.01949418417658754</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01949722273539412</v>
+        <v>0.01949722273539411</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01949418417658755</v>
+        <v>0.01949418417658754</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01949418417658755</v>
+        <v>0.01949418417658754</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01949418417658755</v>
+        <v>0.01949418417658754</v>
       </c>
       <c r="V2" t="n">
         <v>0.01865542273483732</v>
       </c>
       <c r="W2" t="n">
-        <v>0.01949418417658755</v>
+        <v>0.01949418417658754</v>
       </c>
       <c r="X2" t="n">
         <v>0.01945011441141242</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.01949418417658755</v>
+        <v>0.01949418417658754</v>
       </c>
       <c r="Z2" t="n">
         <v>0.01889459557580987</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.01949418417658755</v>
+        <v>0.01949418417658754</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.01885287977642297</v>
+        <v>0.01885287977642296</v>
       </c>
     </row>
     <row r="3">
@@ -2746,85 +2746,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01866762664641942</v>
+        <v>0.01866762664641941</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01875900856251756</v>
+        <v>0.01875900856251755</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01866762664641942</v>
+        <v>0.01866762664641941</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03139494419479147</v>
+        <v>0.03139494419479151</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01870063421268165</v>
+        <v>0.01870063421268164</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01831475137823258</v>
+        <v>0.01831475137823257</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01866762664641942</v>
+        <v>0.01866762664641941</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01866762664641942</v>
+        <v>0.01866762664641941</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01862074333813744</v>
+        <v>0.01862074333813743</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01868536802111277</v>
+        <v>0.01868536802111275</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01866762664641942</v>
+        <v>0.01866762664641941</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01866762664641942</v>
+        <v>0.01866762664641941</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01866762664641942</v>
+        <v>0.01866762664641941</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01866762664641942</v>
+        <v>0.01866762664641941</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01866762664641942</v>
+        <v>0.01866762664641941</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01866762664641942</v>
+        <v>0.01866762664641941</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01867095160439537</v>
+        <v>0.01867095160439535</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01866762664641942</v>
+        <v>0.01866762664641941</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01866762664641942</v>
+        <v>0.01866762664641941</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01866762664641942</v>
+        <v>0.01866762664641941</v>
       </c>
       <c r="V3" t="n">
-        <v>0.01865910753722601</v>
+        <v>0.01865910753722603</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01866762664641942</v>
+        <v>0.01866762664641941</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01861940099373017</v>
+        <v>0.01861940099373016</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01866762664641942</v>
+        <v>0.01866762664641941</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01867170492099846</v>
+        <v>0.01867170492099845</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.01866762664641942</v>
+        <v>0.01866762664641941</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01796584652000256</v>
+        <v>0.01796584652000255</v>
       </c>
     </row>
     <row r="4">
@@ -2834,85 +2834,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3079693183474612</v>
+        <v>0.3079693183474606</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0801936685442115</v>
+        <v>0.08019366854421142</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2934631088498614</v>
+        <v>0.2934631088498608</v>
       </c>
       <c r="E4" t="n">
-        <v>0.127428477894433</v>
+        <v>0.1274284778944331</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1676630024888625</v>
+        <v>0.1676630024888628</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4606196491416328</v>
+        <v>0.4606196491416324</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1330737225454304</v>
+        <v>0.1330737225454307</v>
       </c>
       <c r="I4" t="n">
-        <v>0.209308287372014</v>
+        <v>0.2093082873720141</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3382797417087485</v>
+        <v>0.3382797417087484</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4118769360948792</v>
+        <v>0.4118769360948796</v>
       </c>
       <c r="L4" t="n">
-        <v>0.492680218148995</v>
+        <v>0.4926802181489956</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5436249860297485</v>
+        <v>0.5436249860297493</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4338108037294605</v>
+        <v>0.43381080372946</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2684331293687711</v>
+        <v>0.2684331293687712</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4746642301535661</v>
+        <v>0.4746642301535663</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1695642258852447</v>
+        <v>0.1695642258852448</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1309599049629333</v>
+        <v>0.1309599049629334</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3209777733012204</v>
+        <v>0.3209777733012213</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2654996805430132</v>
+        <v>0.2654996805430129</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4338108037294605</v>
+        <v>0.43381080372946</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1127114446038826</v>
+        <v>0.1127114446038825</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2773064631313253</v>
+        <v>0.2773064631313252</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3646256888786259</v>
+        <v>0.3646256888786264</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3213760818622846</v>
+        <v>0.3213760818622848</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.1743036765002438</v>
+        <v>0.1743036765002436</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.30087909826757</v>
+        <v>0.3008790982675705</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.7795445088194741</v>
+        <v>0.7795445088194729</v>
       </c>
     </row>
     <row r="5">
@@ -2922,85 +2922,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01075615736943222</v>
+        <v>0.01075615736943219</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01075615736943221</v>
+        <v>0.0107561573694322</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01075615736943221</v>
+        <v>0.0107561573694322</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01075615736943221</v>
+        <v>0.0107561573694322</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01075615736943222</v>
+        <v>0.01075615736943219</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01075615736943221</v>
+        <v>0.0107561573694322</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01075615736943221</v>
+        <v>0.0107561573694322</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01075615736943221</v>
+        <v>0.0107561573694322</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01072926831802866</v>
+        <v>0.01072926831802865</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01075615736943221</v>
+        <v>0.0107561573694322</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01075615736943221</v>
+        <v>0.0107561573694322</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01075615736943221</v>
+        <v>0.0107561573694322</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01075615736943222</v>
+        <v>0.01075615736943219</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01075615736943222</v>
+        <v>0.01075615736943219</v>
       </c>
       <c r="P5" t="n">
-        <v>0.01075615736943222</v>
+        <v>0.01075615736943219</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01075615736943222</v>
+        <v>0.01075615736943219</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01075615736943221</v>
+        <v>0.0107561573694322</v>
       </c>
       <c r="S5" t="n">
-        <v>0.01075615736943221</v>
+        <v>0.0107561573694322</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01075615736943221</v>
+        <v>0.0107561573694322</v>
       </c>
       <c r="U5" t="n">
-        <v>0.01047542706259524</v>
+        <v>0.01047542706259521</v>
       </c>
       <c r="V5" t="n">
-        <v>0.01058390977272531</v>
+        <v>0.01058390977272526</v>
       </c>
       <c r="W5" t="n">
-        <v>0.01075615736943222</v>
+        <v>0.0107561573694322</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01075615736943222</v>
+        <v>0.01075615736943219</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.01047542706259524</v>
+        <v>0.01047542706259521</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.01075615736943221</v>
+        <v>0.0107561573694322</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.01075615736943221</v>
+        <v>0.0107561573694322</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.01075615736943222</v>
+        <v>0.01075615736943219</v>
       </c>
     </row>
     <row r="6">
@@ -3010,85 +3010,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0230785922385862</v>
+        <v>0.01484426907449278</v>
       </c>
       <c r="C6" t="n">
         <v>0.0230785922385862</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01484426907449279</v>
+        <v>0.0230785922385862</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01484426907449279</v>
+        <v>0.01484426907449278</v>
       </c>
       <c r="F6" t="n">
+        <v>0.01484426907449278</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.01484426907449278</v>
+      </c>
+      <c r="H6" t="n">
         <v>0.0230785922385862</v>
       </c>
-      <c r="G6" t="n">
+      <c r="I6" t="n">
+        <v>0.01484426907449278</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.02305170318718263</v>
+      </c>
+      <c r="K6" t="n">
         <v>0.0230785922385862</v>
       </c>
-      <c r="H6" t="n">
-        <v>0.01484426907449279</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.01484426907449279</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.02305170318718266</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.01484426907449279</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.01484426907449279</v>
+        <v>0.01484426907449278</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01484426907449279</v>
+        <v>0.01484426907449278</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01487582497781343</v>
+        <v>0.01487582497781354</v>
       </c>
       <c r="O6" t="n">
-        <v>0.02302719200194673</v>
+        <v>0.02302719200194677</v>
       </c>
       <c r="P6" t="n">
-        <v>0.02302720114931948</v>
+        <v>0.02302720114931954</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01484426907449279</v>
+        <v>0.0230785922385862</v>
       </c>
       <c r="R6" t="n">
-        <v>0.01484426907449279</v>
+        <v>0.0230785922385862</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01484426907449279</v>
+        <v>0.0230785922385862</v>
       </c>
       <c r="T6" t="n">
+        <v>0.01484426907449278</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.01484426907449278</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.02290634464187925</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.02302711149527737</v>
+      </c>
+      <c r="X6" t="n">
         <v>0.0230785922385862</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0.0230785922385862</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0.02290634464187928</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0.02302711149527735</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0.01484426907449279</v>
       </c>
       <c r="Y6" t="n">
         <v>0.01516005845882627</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.01484426907449279</v>
+        <v>0.0230785922385862</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0230785922385862</v>
+        <v>0.01484426907449278</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.01503408872875391</v>
+        <v>0.01503408872875393</v>
       </c>
     </row>
     <row r="7">
@@ -3098,85 +3098,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01594313593511338</v>
+        <v>0.01594313593511337</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01594313593511338</v>
+        <v>0.01594313593511337</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01594313593511338</v>
+        <v>0.01594313593511337</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01594313593511338</v>
+        <v>0.01594313593511337</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01594313593511338</v>
+        <v>0.01594313593511337</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01594313593511338</v>
+        <v>0.01594313593511337</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01594313593511338</v>
+        <v>0.01594313593511337</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01594313593511338</v>
+        <v>0.01594313593511337</v>
       </c>
       <c r="J7" t="n">
         <v>0.01591624688370982</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01594313593511338</v>
+        <v>0.01594313593511337</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01594313593511338</v>
+        <v>0.01594313593511337</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01594313593511338</v>
+        <v>0.01594313593511337</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01594313593511338</v>
+        <v>0.01594313593511337</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01594241230902073</v>
+        <v>0.01594241230902071</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01594241230902073</v>
+        <v>0.01594241230902071</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.01594313593511338</v>
+        <v>0.01594313593511337</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01594313593511338</v>
+        <v>0.01594313593511337</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01594313593511338</v>
+        <v>0.01594313593511337</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01594313593511338</v>
+        <v>0.01594313593511337</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0159347041914546</v>
+        <v>0.01593470419145462</v>
       </c>
       <c r="V7" t="n">
-        <v>0.01577088833840644</v>
+        <v>0.01577088833840641</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01594313593511338</v>
+        <v>0.01594313593511337</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01594313593511338</v>
+        <v>0.01594313593511337</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01594313593511338</v>
+        <v>0.01594313593511337</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.01594313593511338</v>
+        <v>0.01594313593511337</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01594313593511338</v>
+        <v>0.01594313593511337</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01594313593511338</v>
+        <v>0.01594313593511337</v>
       </c>
     </row>
     <row r="8">
@@ -3186,46 +3186,46 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02318076584146376</v>
+        <v>0.02318076584146377</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03322525098482098</v>
+        <v>0.03322525098482101</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03322525098482098</v>
+        <v>0.03322525098482101</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03322525098482098</v>
+        <v>0.02787685894003642</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02474557923424777</v>
+        <v>0.02474557923424776</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03322525098482098</v>
+        <v>0.03530804041293188</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03322525098482098</v>
+        <v>0.03322525098482101</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03322525098482098</v>
+        <v>0.03322525098482101</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03319836193341746</v>
+        <v>0.03319836193341745</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03322525098482098</v>
+        <v>0.03322525098482101</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03322525098482098</v>
+        <v>0.03322525098482101</v>
       </c>
       <c r="M8" t="n">
-        <v>0.03322525098482098</v>
+        <v>0.03322525098482029</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02543909459259339</v>
+        <v>0.02543909459259338</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02757879797452847</v>
+        <v>0.02757879797452843</v>
       </c>
       <c r="P8" t="n">
         <v>0.02705430497320923</v>
@@ -3234,37 +3234,37 @@
         <v>0.02120679525697645</v>
       </c>
       <c r="R8" t="n">
-        <v>0.03322525098482098</v>
+        <v>0.03322525098482101</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03322525098482098</v>
+        <v>0.03322525098482101</v>
       </c>
       <c r="T8" t="n">
-        <v>0.03322525098482098</v>
+        <v>0.03322525098482101</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0270387886977958</v>
+        <v>0.02831669824585974</v>
       </c>
       <c r="V8" t="n">
-        <v>0.03305300338811403</v>
+        <v>0.03030110543704482</v>
       </c>
       <c r="W8" t="n">
         <v>0.03322722501255519</v>
       </c>
       <c r="X8" t="n">
-        <v>0.02212739227820442</v>
+        <v>0.02212739227820443</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.04320203484037904</v>
+        <v>0.04320203484037902</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.03322525098482098</v>
+        <v>0.02299418437318869</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.03322525098482098</v>
+        <v>0.03322525098482101</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.04371755562195474</v>
+        <v>0.04371755562195469</v>
       </c>
     </row>
     <row r="9">
@@ -3274,85 +3274,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03247938582652116</v>
+        <v>0.03247938582652117</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03942286241835046</v>
+        <v>0.03942286241835048</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03942286241835046</v>
+        <v>0.03942286241835048</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03942286241835046</v>
+        <v>0.0378203377744116</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03942286241835046</v>
+        <v>0.02341625139044365</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03942286241835046</v>
+        <v>0.03942286427940433</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03942286241835046</v>
+        <v>0.03942286241835048</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03942286241835046</v>
+        <v>0.03942286241835048</v>
       </c>
       <c r="J9" t="n">
         <v>0.03939597336694695</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03942286241835046</v>
+        <v>0.03942286241835048</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03942286241835046</v>
+        <v>0.03942286241835048</v>
       </c>
       <c r="M9" t="n">
-        <v>0.03942286241835046</v>
+        <v>0.03942286241835048</v>
       </c>
       <c r="N9" t="n">
-        <v>0.03942286241835046</v>
+        <v>0.03942286241835048</v>
       </c>
       <c r="O9" t="n">
         <v>0.04172392394698164</v>
       </c>
       <c r="P9" t="n">
-        <v>0.04222436494514387</v>
+        <v>0.04222436494514391</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03942286427940432</v>
+        <v>0.03942286427940433</v>
       </c>
       <c r="R9" t="n">
-        <v>0.03942286241835046</v>
+        <v>0.03942286241835048</v>
       </c>
       <c r="S9" t="n">
-        <v>0.03942286241835046</v>
+        <v>0.03942286241835048</v>
       </c>
       <c r="T9" t="n">
-        <v>0.03942286241835046</v>
+        <v>0.03942286241835048</v>
       </c>
       <c r="U9" t="n">
-        <v>0.03942286241835046</v>
+        <v>0.03942286241835048</v>
       </c>
       <c r="V9" t="n">
-        <v>0.03925061482164353</v>
+        <v>0.04726323204514753</v>
       </c>
       <c r="W9" t="n">
-        <v>0.03942286241835046</v>
+        <v>0.03942286241835048</v>
       </c>
       <c r="X9" t="n">
-        <v>0.03942286241835046</v>
+        <v>0.03942286241835048</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.03942286241835046</v>
+        <v>0.03942286241835048</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.03942286241835046</v>
+        <v>0.03523656421051065</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.03942286241835046</v>
+        <v>0.03942286241835048</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.03942286241835046</v>
+        <v>0.03942286241835048</v>
       </c>
     </row>
     <row r="10">
@@ -3362,49 +3362,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01163378749778923</v>
+        <v>0.01163378749778922</v>
       </c>
       <c r="C10" t="n">
         <v>0.01731541105682374</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0128762582134149</v>
+        <v>0.01287625821341489</v>
       </c>
       <c r="E10" t="n">
-        <v>0.028798790120684</v>
+        <v>0.02879879012068404</v>
       </c>
       <c r="F10" t="n">
         <v>0.01551532952712095</v>
       </c>
       <c r="G10" t="n">
-        <v>0.007929309515744519</v>
+        <v>0.007929309515744516</v>
       </c>
       <c r="H10" t="n">
         <v>0.01628363499079032</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01465932823081628</v>
+        <v>0.01465932823081627</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01131900302735577</v>
+        <v>0.01131900302735576</v>
       </c>
       <c r="K10" t="n">
         <v>0.009778543009183072</v>
       </c>
       <c r="L10" t="n">
-        <v>0.008146391640603436</v>
+        <v>0.008146391640603431</v>
       </c>
       <c r="M10" t="n">
-        <v>0.007817736275557272</v>
+        <v>0.007817736275557251</v>
       </c>
       <c r="N10" t="n">
         <v>0.01329953192108237</v>
       </c>
       <c r="O10" t="n">
-        <v>0.01240842399519503</v>
+        <v>0.01240842399519502</v>
       </c>
       <c r="P10" t="n">
-        <v>0.007899213743979479</v>
+        <v>0.007899213743979455</v>
       </c>
       <c r="Q10" t="n">
         <v>0.01533173323765961</v>
@@ -3413,34 +3413,34 @@
         <v>0.01628917673831633</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01154145797137541</v>
+        <v>0.01154145797137538</v>
       </c>
       <c r="T10" t="n">
         <v>0.01344619621897714</v>
       </c>
       <c r="U10" t="n">
-        <v>0.009219631866435195</v>
+        <v>0.009219631866435186</v>
       </c>
       <c r="V10" t="n">
-        <v>0.01624554977763362</v>
+        <v>0.01624554977763364</v>
       </c>
       <c r="W10" t="n">
-        <v>0.01291256375670903</v>
+        <v>0.01291256375670902</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0112201937348152</v>
+        <v>0.01122019373481518</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.01189074647153164</v>
+        <v>0.01189074647153163</v>
       </c>
       <c r="Z10" t="n">
         <v>0.01492388211307813</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.01239512479623333</v>
+        <v>0.01239512479623334</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.002908839994541255</v>
+        <v>0.002908839994541265</v>
       </c>
     </row>
     <row r="11">
@@ -3450,22 +3450,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.01629376494844544</v>
+        <v>0.01629376494844543</v>
       </c>
       <c r="C11" t="n">
-        <v>0.01793304589827545</v>
+        <v>0.01793304589827544</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01661382899268891</v>
+        <v>0.0166138289926889</v>
       </c>
       <c r="E11" t="n">
-        <v>0.03004317705913802</v>
+        <v>0.03004317705913804</v>
       </c>
       <c r="F11" t="n">
-        <v>0.017387524612072</v>
+        <v>0.01738752461207199</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0149589861644086</v>
+        <v>0.01495898616440856</v>
       </c>
       <c r="H11" t="n">
         <v>0.01840946037594567</v>
@@ -3474,52 +3474,52 @@
         <v>0.01767039562379899</v>
       </c>
       <c r="J11" t="n">
-        <v>0.01612499111066739</v>
+        <v>0.01612499111066738</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0154577630844258</v>
+        <v>0.01545776308442579</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01470698871975474</v>
+        <v>0.01470698871975473</v>
       </c>
       <c r="M11" t="n">
-        <v>0.01518283940188747</v>
+        <v>0.01518283940188746</v>
       </c>
       <c r="N11" t="n">
-        <v>0.01673029198770984</v>
+        <v>0.01673029198770982</v>
       </c>
       <c r="O11" t="n">
         <v>0.01664622702338511</v>
       </c>
       <c r="P11" t="n">
-        <v>0.01459452198908162</v>
+        <v>0.0145945219890816</v>
       </c>
       <c r="Q11" t="n">
         <v>0.01797634204474029</v>
       </c>
       <c r="R11" t="n">
-        <v>0.01841350758106203</v>
+        <v>0.01841350758106201</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01625175471969041</v>
+        <v>0.0162517547196904</v>
       </c>
       <c r="T11" t="n">
         <v>0.01711841669238983</v>
       </c>
       <c r="U11" t="n">
-        <v>0.01519531644272185</v>
+        <v>0.01519531644272186</v>
       </c>
       <c r="V11" t="n">
         <v>0.01755724626267059</v>
       </c>
       <c r="W11" t="n">
-        <v>0.01687561222147209</v>
+        <v>0.01687561222147208</v>
       </c>
       <c r="X11" t="n">
-        <v>0.01608345152873166</v>
+        <v>0.01608345152873165</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.0164106821003779</v>
+        <v>0.01641068210037789</v>
       </c>
       <c r="Z11" t="n">
         <v>0.0171893242546035</v>
@@ -3694,85 +3694,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01928648961536442</v>
+        <v>0.01928648961536444</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01847447666512789</v>
+        <v>0.0184744766651279</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01933776595359759</v>
+        <v>0.01933776595359761</v>
       </c>
       <c r="E2" t="n">
         <v>0.03115932954727105</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0187887744316054</v>
+        <v>0.01878877443160541</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0194100074329777</v>
+        <v>0.01941000743297771</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01928648961536442</v>
+        <v>0.01928648961536444</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01928648961536442</v>
+        <v>0.01928648961536444</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01924737843433149</v>
+        <v>0.01924737843433148</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01930948610486009</v>
+        <v>0.0193094861048601</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01928648961536442</v>
+        <v>0.01928648961536444</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01940344867252753</v>
+        <v>0.01940344867252755</v>
       </c>
       <c r="N2" t="n">
-        <v>0.01881081027577341</v>
+        <v>0.01881081027577343</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01928648961536442</v>
+        <v>0.01928648961536444</v>
       </c>
       <c r="P2" t="n">
-        <v>0.01928648961536442</v>
+        <v>0.01928648961536444</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.01928648961536442</v>
+        <v>0.01928648961536444</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01919916613667342</v>
+        <v>0.01919916613667344</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01928648961536442</v>
+        <v>0.01928648961536444</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01928648961536442</v>
+        <v>0.01928648961536444</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01928648961536442</v>
+        <v>0.01928648961536444</v>
       </c>
       <c r="V2" t="n">
-        <v>0.01864330179627047</v>
+        <v>0.01864330179627048</v>
       </c>
       <c r="W2" t="n">
-        <v>0.01928648961536442</v>
+        <v>0.01928648961536444</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0187604574093703</v>
+        <v>0.01876045740937032</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.01928648961536442</v>
+        <v>0.01928648961536444</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.01878612149311819</v>
+        <v>0.01878612149311821</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.01928648961536442</v>
+        <v>0.01928648961536444</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.01864518521519985</v>
+        <v>0.01864518521519987</v>
       </c>
     </row>
     <row r="3">
@@ -3782,85 +3782,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01857288235246704</v>
+        <v>0.01857288235246705</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01866885235846219</v>
+        <v>0.0186688523584622</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01857288235246704</v>
+        <v>0.01857288235246705</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03132375702521918</v>
+        <v>0.0313237570252192</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01861946672714579</v>
+        <v>0.0186194667271458</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01815347754909177</v>
+        <v>0.01815347754909178</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01857288235246704</v>
+        <v>0.01857288235246705</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01857288235246704</v>
+        <v>0.01857288235246705</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01853376670862342</v>
+        <v>0.01853376670862343</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01859804729281658</v>
+        <v>0.01859804729281659</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01857288235246704</v>
+        <v>0.01857288235246705</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01857288235246704</v>
+        <v>0.01857288235246705</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01857288235246704</v>
+        <v>0.01857288235246705</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01857288235246704</v>
+        <v>0.01857288235246705</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01857288235246704</v>
+        <v>0.01857288235246705</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01857288235246704</v>
+        <v>0.01857288235246705</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01847732396778892</v>
+        <v>0.01847732396778893</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01857288235246704</v>
+        <v>0.01857288235246705</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01857288235246704</v>
+        <v>0.01857288235246705</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01857288235246704</v>
+        <v>0.01857288235246705</v>
       </c>
       <c r="V3" t="n">
-        <v>0.01853783283898122</v>
+        <v>0.01853783283898123</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01857288235246704</v>
+        <v>0.01857288235246705</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01799724469449534</v>
+        <v>0.01799724469449536</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01857288235246704</v>
+        <v>0.01857288235246705</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01857973981482999</v>
+        <v>0.01857973981483</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.01857288235246704</v>
+        <v>0.01857288235246705</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01787110222605017</v>
+        <v>0.01787110222605019</v>
       </c>
     </row>
     <row r="4">
@@ -3870,85 +3870,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2313789429946215</v>
+        <v>0.2313789429946217</v>
       </c>
       <c r="C4" t="n">
-        <v>0.06725403759073814</v>
+        <v>0.06725403759073821</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3190494569092608</v>
+        <v>0.319049456909262</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1206106806162096</v>
+        <v>0.1206106806162099</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1629450609623594</v>
+        <v>0.1629450609623591</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3942639065835358</v>
+        <v>0.3942639065835362</v>
       </c>
       <c r="H4" t="n">
-        <v>0.08660271519177112</v>
+        <v>0.08660271519177105</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2714937648569307</v>
+        <v>0.2714937648569308</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2841227490419779</v>
+        <v>0.284122749041978</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2891352395144609</v>
+        <v>0.2891352395144611</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3887870172373331</v>
+        <v>0.3887870172373333</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3416422077653249</v>
+        <v>0.3416422077653252</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3891342094702873</v>
+        <v>0.389134209470289</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2025923168939124</v>
+        <v>0.2025923168939129</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4313554245608845</v>
+        <v>0.4313554245608871</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1409898681264574</v>
+        <v>0.1409898681264576</v>
       </c>
       <c r="R4" t="n">
-        <v>0.07986449185960383</v>
+        <v>0.07986449185960384</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2750856120008892</v>
+        <v>0.2750856120008897</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2126481014975269</v>
+        <v>0.2126481014975277</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3891342094702872</v>
+        <v>0.389134209470289</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1279548700806595</v>
+        <v>0.1279548700806599</v>
       </c>
       <c r="W4" t="n">
-        <v>0.255042317606436</v>
+        <v>0.2550423176064355</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3914477283705457</v>
+        <v>0.3914477283705471</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4847503580198008</v>
+        <v>0.4847503580198013</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.1499501658435274</v>
+        <v>0.1499501658435273</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.2910579845700758</v>
+        <v>0.291057984570076</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.6841663885147523</v>
+        <v>0.6841663885147524</v>
       </c>
     </row>
     <row r="5">
@@ -3958,7 +3958,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01014197449933463</v>
+        <v>0.01014197449933461</v>
       </c>
       <c r="C5" t="n">
         <v>0.01014197449933462</v>
@@ -3970,7 +3970,7 @@
         <v>0.01014197449933462</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01014197449933463</v>
+        <v>0.01014197449933461</v>
       </c>
       <c r="G5" t="n">
         <v>0.01014197449933462</v>
@@ -3994,16 +3994,16 @@
         <v>0.01014197449933462</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01014197449933463</v>
+        <v>0.01014197449933461</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01014197449933463</v>
+        <v>0.01014197449933461</v>
       </c>
       <c r="P5" t="n">
-        <v>0.01014197449933463</v>
+        <v>0.01014197449933461</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01014197449933463</v>
+        <v>0.01014197449933461</v>
       </c>
       <c r="R5" t="n">
         <v>0.01014197449933462</v>
@@ -4018,13 +4018,13 @@
         <v>0.009905189034575664</v>
       </c>
       <c r="V5" t="n">
-        <v>0.009985958267997483</v>
+        <v>0.009985958267997471</v>
       </c>
       <c r="W5" t="n">
-        <v>0.01014197449933463</v>
+        <v>0.01014197449933462</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01014197449933463</v>
+        <v>0.01014197449933461</v>
       </c>
       <c r="Y5" t="n">
         <v>0.009905189034575664</v>
@@ -4036,7 +4036,7 @@
         <v>0.01014197449933462</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.01014197449933463</v>
+        <v>0.01014197449933461</v>
       </c>
     </row>
     <row r="6">
@@ -4046,55 +4046,55 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02152970101721927</v>
+        <v>0.0140370243820499</v>
       </c>
       <c r="C6" t="n">
         <v>0.0140370243820499</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02152970101721927</v>
+        <v>0.02152970101721929</v>
       </c>
       <c r="E6" t="n">
         <v>0.0140370243820499</v>
       </c>
       <c r="F6" t="n">
+        <v>0.02152970101721929</v>
+      </c>
+      <c r="G6" t="n">
         <v>0.0140370243820499</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.02152970101721927</v>
       </c>
       <c r="H6" t="n">
         <v>0.0140370243820499</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02152970101721927</v>
+        <v>0.0140370243820499</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02150533115182752</v>
+        <v>0.02150533115182754</v>
       </c>
       <c r="K6" t="n">
+        <v>0.02152970101721929</v>
+      </c>
+      <c r="L6" t="n">
         <v>0.0140370243820499</v>
       </c>
-      <c r="L6" t="n">
-        <v>0.02152970101721927</v>
-      </c>
       <c r="M6" t="n">
-        <v>0.02152970101721927</v>
+        <v>0.02152970101721929</v>
       </c>
       <c r="N6" t="n">
         <v>0.01407009775337129</v>
       </c>
       <c r="O6" t="n">
-        <v>0.02148778721653827</v>
+        <v>0.0140700977533713</v>
       </c>
       <c r="P6" t="n">
-        <v>0.02148774431377101</v>
+        <v>0.02148774431377104</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.02152970101721927</v>
+        <v>0.02152970101721929</v>
       </c>
       <c r="R6" t="n">
-        <v>0.02152970101721927</v>
+        <v>0.02152970101721929</v>
       </c>
       <c r="S6" t="n">
         <v>0.0140370243820499</v>
@@ -4103,13 +4103,13 @@
         <v>0.0140370243820499</v>
       </c>
       <c r="U6" t="n">
-        <v>0.02152970101721927</v>
+        <v>0.0140370243820499</v>
       </c>
       <c r="V6" t="n">
-        <v>0.02137368478588214</v>
+        <v>0.02137368478588216</v>
       </c>
       <c r="W6" t="n">
-        <v>0.02148772737939896</v>
+        <v>0.01442995484006466</v>
       </c>
       <c r="X6" t="n">
         <v>0.0140370243820499</v>
@@ -4118,13 +4118,13 @@
         <v>0.0143424904066985</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.02152970101721927</v>
+        <v>0.0140370243820499</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0140370243820499</v>
+        <v>0.02152970101721929</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.01419998313353979</v>
+        <v>0.0141999831335398</v>
       </c>
     </row>
     <row r="7">
@@ -4134,43 +4134,43 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01476365100132615</v>
+        <v>0.01476365100132616</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01476365100132615</v>
+        <v>0.01476365100132616</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01476365100132615</v>
+        <v>0.01476365100132616</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01476365100132615</v>
+        <v>0.01476365100132616</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01476365100132615</v>
+        <v>0.01476365100132616</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01476365100132615</v>
+        <v>0.01476365100132616</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01476365100132615</v>
+        <v>0.01476365100132616</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01476365100132615</v>
+        <v>0.01476365100132616</v>
       </c>
       <c r="J7" t="n">
         <v>0.01473928113593439</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01476365100132615</v>
+        <v>0.01476365100132616</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01476365100132615</v>
+        <v>0.01476365100132616</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01476365100132615</v>
+        <v>0.01476365100132616</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01476365100132615</v>
+        <v>0.01476365100132616</v>
       </c>
       <c r="O7" t="n">
         <v>0.01476297585895609</v>
@@ -4179,40 +4179,40 @@
         <v>0.01476297585895609</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.01476365100132615</v>
+        <v>0.01476365100132616</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01476365100132615</v>
+        <v>0.01476365100132616</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01476365100132615</v>
+        <v>0.01476365100132616</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01476365100132615</v>
+        <v>0.01476365100132616</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01475537650039012</v>
+        <v>0.01475537650039011</v>
       </c>
       <c r="V7" t="n">
-        <v>0.01460763476998904</v>
+        <v>0.01460763476998902</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01476365100132615</v>
+        <v>0.01476365100132616</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01476365100132615</v>
+        <v>0.01476365100132616</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01476365100132615</v>
+        <v>0.01476365100132616</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.01476365100132615</v>
+        <v>0.01476365100132616</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01476365100132615</v>
+        <v>0.01476365100132616</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01476365100132615</v>
+        <v>0.01476365100132616</v>
       </c>
     </row>
     <row r="8">
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02136787292416567</v>
+        <v>0.02136787292416569</v>
       </c>
       <c r="C8" t="n">
         <v>0.0304578869381291</v>
@@ -4231,13 +4231,13 @@
         <v>0.0304578869381291</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0304578869381291</v>
+        <v>0.02561772261459238</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02278399087014423</v>
+        <v>0.02278399087014424</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0304578869381291</v>
+        <v>0.03234276055976601</v>
       </c>
       <c r="H8" t="n">
         <v>0.0304578869381291</v>
@@ -4246,7 +4246,7 @@
         <v>0.0304578869381291</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03043351707273732</v>
+        <v>0.03043351707273735</v>
       </c>
       <c r="K8" t="n">
         <v>0.0304578869381291</v>
@@ -4255,19 +4255,19 @@
         <v>0.0304578869381291</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0304578869381291</v>
+        <v>0.03045788693812848</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02341160535075049</v>
+        <v>0.02341160535075051</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02534798471213699</v>
+        <v>0.02534798471213702</v>
       </c>
       <c r="P8" t="n">
-        <v>0.02487333134124579</v>
+        <v>0.02487333134124583</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01958147770132215</v>
+        <v>0.01958147770132214</v>
       </c>
       <c r="R8" t="n">
         <v>0.0304578869381291</v>
@@ -4279,28 +4279,28 @@
         <v>0.0304578869381291</v>
       </c>
       <c r="U8" t="n">
-        <v>0.02485883562968393</v>
+        <v>0.0260152831038561</v>
       </c>
       <c r="V8" t="n">
-        <v>0.03030187070679194</v>
+        <v>0.02781093707162699</v>
       </c>
       <c r="W8" t="n">
-        <v>0.03045967338503728</v>
+        <v>0.03045967338503729</v>
       </c>
       <c r="X8" t="n">
-        <v>0.02041459554703733</v>
+        <v>0.02041459554703735</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.03948580606298355</v>
+        <v>0.03948580606298359</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0304578869381291</v>
+        <v>0.02119902124714052</v>
       </c>
       <c r="AA8" t="n">
         <v>0.0304578869381291</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.03995316666911952</v>
+        <v>0.03995316666911958</v>
       </c>
     </row>
     <row r="9">
@@ -4310,85 +4310,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02855199109155473</v>
+        <v>0.02855199109155477</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03449525289510146</v>
+        <v>0.03449525289510143</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03449525289510146</v>
+        <v>0.03449525289510143</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03449525289510146</v>
+        <v>0.03312357499175501</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03449525289510146</v>
+        <v>0.0207944078222111</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03449525289510146</v>
+        <v>0.03449525637764776</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03449525289510146</v>
+        <v>0.03449525289510143</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03449525289510146</v>
+        <v>0.03449525289510143</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03447088302970965</v>
+        <v>0.03447088302970968</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03449525289510146</v>
+        <v>0.03449525289510143</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03449525289510146</v>
+        <v>0.03449525289510143</v>
       </c>
       <c r="M9" t="n">
-        <v>0.03449525289510146</v>
+        <v>0.03449525289510143</v>
       </c>
       <c r="N9" t="n">
-        <v>0.03449525289510146</v>
+        <v>0.03449525289510143</v>
       </c>
       <c r="O9" t="n">
-        <v>0.03646484671141824</v>
+        <v>0.03646484671141827</v>
       </c>
       <c r="P9" t="n">
-        <v>0.03689319881653352</v>
+        <v>0.03689319881653351</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03449525637764773</v>
+        <v>0.03449525637764776</v>
       </c>
       <c r="R9" t="n">
-        <v>0.03449525289510146</v>
+        <v>0.03449525289510143</v>
       </c>
       <c r="S9" t="n">
-        <v>0.03449525289510146</v>
+        <v>0.03449525289510143</v>
       </c>
       <c r="T9" t="n">
-        <v>0.03449525289510146</v>
+        <v>0.03449525289510143</v>
       </c>
       <c r="U9" t="n">
-        <v>0.03449525289510146</v>
+        <v>0.03449525289510143</v>
       </c>
       <c r="V9" t="n">
-        <v>0.03433923666376432</v>
+        <v>0.0411976323574307</v>
       </c>
       <c r="W9" t="n">
-        <v>0.03449525289510146</v>
+        <v>0.03449525289510143</v>
       </c>
       <c r="X9" t="n">
-        <v>0.03449525289510146</v>
+        <v>0.03449525289510143</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.03449525289510146</v>
+        <v>0.03449525289510143</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.03449525289510146</v>
+        <v>0.0309119959059035</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.03449525289510146</v>
+        <v>0.03449525289510143</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.03449525289510146</v>
+        <v>0.03449525289510143</v>
       </c>
     </row>
     <row r="10">
@@ -4398,76 +4398,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01305783947366913</v>
+        <v>0.01305783947366914</v>
       </c>
       <c r="C10" t="n">
-        <v>0.01737650892020064</v>
+        <v>0.01737650892020065</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01171159521598334</v>
+        <v>0.01171159521598333</v>
       </c>
       <c r="E10" t="n">
-        <v>0.02869516750364307</v>
+        <v>0.02869516750364303</v>
       </c>
       <c r="F10" t="n">
         <v>0.01523988173367282</v>
       </c>
       <c r="G10" t="n">
-        <v>0.00848023546904597</v>
+        <v>0.008480235469045996</v>
       </c>
       <c r="H10" t="n">
         <v>0.0169922018657437</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01287754737587233</v>
+        <v>0.01287754737587232</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01190668290345977</v>
+        <v>0.01190668290345975</v>
       </c>
       <c r="K10" t="n">
-        <v>0.01164967428309726</v>
+        <v>0.01164967428309724</v>
       </c>
       <c r="L10" t="n">
-        <v>0.009659356937753482</v>
+        <v>0.009659356937753513</v>
       </c>
       <c r="M10" t="n">
         <v>0.01135438430984864</v>
       </c>
       <c r="N10" t="n">
-        <v>0.01478225284788721</v>
+        <v>0.01478225284788722</v>
       </c>
       <c r="O10" t="n">
         <v>0.01351953923651471</v>
       </c>
       <c r="P10" t="n">
-        <v>0.007945180549615363</v>
+        <v>0.00794518054961532</v>
       </c>
       <c r="Q10" t="n">
         <v>0.01556670779184378</v>
       </c>
       <c r="R10" t="n">
-        <v>0.01700493836638988</v>
+        <v>0.01700493836638989</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01198574379822011</v>
+        <v>0.01198574379822008</v>
       </c>
       <c r="T10" t="n">
-        <v>0.01413284313566799</v>
+        <v>0.01413284313566798</v>
       </c>
       <c r="U10" t="n">
-        <v>0.009378229545071365</v>
+        <v>0.009378229545071342</v>
       </c>
       <c r="V10" t="n">
-        <v>0.01548552389742162</v>
+        <v>0.01548552389742163</v>
       </c>
       <c r="W10" t="n">
-        <v>0.01290123961416343</v>
+        <v>0.01290123961416344</v>
       </c>
       <c r="X10" t="n">
-        <v>0.009393260162358344</v>
+        <v>0.009393260162358313</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.007467230896351828</v>
+        <v>0.007467230896351817</v>
       </c>
       <c r="Z10" t="n">
         <v>0.01493414644468215</v>
@@ -4476,7 +4476,7 @@
         <v>0.01207199213485644</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.003759958958817847</v>
+        <v>0.003759958958817841</v>
       </c>
     </row>
     <row r="11">
@@ -4486,61 +4486,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.01677712753011254</v>
+        <v>0.01677712753011255</v>
       </c>
       <c r="C11" t="n">
-        <v>0.01788645628226468</v>
+        <v>0.0178864562822647</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01621585844087277</v>
+        <v>0.01621585844087279</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02996331293813606</v>
+        <v>0.02996331293813603</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01725105248947685</v>
+        <v>0.01725105248947686</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01500865145976346</v>
+        <v>0.01500865145976347</v>
       </c>
       <c r="H11" t="n">
-        <v>0.01856727495657548</v>
+        <v>0.0185672749565755</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01669509405105818</v>
+        <v>0.01669509405105819</v>
       </c>
       <c r="J11" t="n">
-        <v>0.01623203418371901</v>
+        <v>0.01623203418371902</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01614795424228684</v>
+        <v>0.01614795424228685</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01523080714594971</v>
+        <v>0.01523080714594972</v>
       </c>
       <c r="M11" t="n">
-        <v>0.01611900905914784</v>
+        <v>0.01611900905914785</v>
       </c>
       <c r="N11" t="n">
-        <v>0.01708606177117011</v>
+        <v>0.01708606177117013</v>
       </c>
       <c r="O11" t="n">
-        <v>0.01698720239355714</v>
+        <v>0.01698720239355715</v>
       </c>
       <c r="P11" t="n">
         <v>0.01445085142659082</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.01791867061017096</v>
+        <v>0.01791867061017097</v>
       </c>
       <c r="R11" t="n">
-        <v>0.01852922599582236</v>
+        <v>0.01852922599582238</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01628932058121702</v>
+        <v>0.01628932058121704</v>
       </c>
       <c r="T11" t="n">
-        <v>0.01726625762215542</v>
+        <v>0.01726625762215543</v>
       </c>
       <c r="U11" t="n">
         <v>0.01510289328637949</v>
@@ -4549,22 +4549,22 @@
         <v>0.01725449150072942</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0167058740949833</v>
+        <v>0.01670587409498333</v>
       </c>
       <c r="X11" t="n">
-        <v>0.01484561702797616</v>
+        <v>0.01484561702797617</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.01423338281122077</v>
+        <v>0.01423338281122075</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.0171273648918842</v>
+        <v>0.01712736489188421</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.01632856384924371</v>
+        <v>0.01632856384924374</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.01222457005906377</v>
+        <v>0.01222457005906378</v>
       </c>
     </row>
   </sheetData>
@@ -4733,19 +4733,19 @@
         <v>0.01928468937668353</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01854389777215644</v>
+        <v>0.01854389777215643</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01906622841384772</v>
+        <v>0.01906622841384771</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03145726133952076</v>
+        <v>0.03145726133952073</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01900651425795674</v>
+        <v>0.01900651425795673</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01904875094817184</v>
+        <v>0.01904875094817183</v>
       </c>
       <c r="H2" t="n">
         <v>0.01928468937668353</v>
@@ -4754,7 +4754,7 @@
         <v>0.01928468937668353</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0192645864918659</v>
+        <v>0.01926458649186591</v>
       </c>
       <c r="K2" t="n">
         <v>0.01931416989378103</v>
@@ -4763,10 +4763,10 @@
         <v>0.01928468937668353</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01932670213877564</v>
+        <v>0.01932670213877563</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0186888064738657</v>
+        <v>0.01868880647386569</v>
       </c>
       <c r="O2" t="n">
         <v>0.01928468937668353</v>
@@ -4790,19 +4790,19 @@
         <v>0.01928468937668353</v>
       </c>
       <c r="V2" t="n">
-        <v>0.01863406728076176</v>
+        <v>0.01863406728076175</v>
       </c>
       <c r="W2" t="n">
         <v>0.01928468937668353</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01904353011765619</v>
+        <v>0.01904353011765618</v>
       </c>
       <c r="Y2" t="n">
         <v>0.01928468937668353</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.01881691328089196</v>
+        <v>0.01881691328089195</v>
       </c>
       <c r="AA2" t="n">
         <v>0.01928468937668353</v>
@@ -4827,7 +4827,7 @@
         <v>0.01866187351600162</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03175819623634107</v>
+        <v>0.03175819623634105</v>
       </c>
       <c r="F3" t="n">
         <v>0.01872369978171367</v>
@@ -4842,7 +4842,7 @@
         <v>0.01866187351600162</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01864176834439971</v>
+        <v>0.01864176834439972</v>
       </c>
       <c r="K3" t="n">
         <v>0.01869413396477698</v>
@@ -4878,13 +4878,13 @@
         <v>0.01866187351600162</v>
       </c>
       <c r="V3" t="n">
-        <v>0.01820379155338899</v>
+        <v>0.01820379155338898</v>
       </c>
       <c r="W3" t="n">
         <v>0.01866187351600162</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01839797255115527</v>
+        <v>0.01839797255115526</v>
       </c>
       <c r="Y3" t="n">
         <v>0.01866187351600162</v>
@@ -4896,7 +4896,7 @@
         <v>0.01866187351600162</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01796009338958476</v>
+        <v>0.01796009338958475</v>
       </c>
     </row>
     <row r="4">
@@ -4906,58 +4906,58 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1958435854889752</v>
+        <v>0.1958435854889755</v>
       </c>
       <c r="C4" t="n">
-        <v>0.06100131166965754</v>
+        <v>0.0610013116696576</v>
       </c>
       <c r="D4" t="n">
         <v>0.2147106614634873</v>
       </c>
       <c r="E4" t="n">
-        <v>0.08263712269142502</v>
+        <v>0.08263712269142512</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1898986814827694</v>
+        <v>0.1898986814827693</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3401170564149699</v>
+        <v>0.3401170564149703</v>
       </c>
       <c r="H4" t="n">
-        <v>0.08746694813111526</v>
+        <v>0.0874669481311154</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2556907950567833</v>
+        <v>0.2556907950567837</v>
       </c>
       <c r="J4" t="n">
-        <v>0.254984279731849</v>
+        <v>0.2549842797318492</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3387579556921966</v>
+        <v>0.3387579556921975</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3198690935177599</v>
+        <v>0.3198690935177603</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2843945968018469</v>
+        <v>0.2843945968018471</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4085452525849253</v>
+        <v>0.4085452525849251</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1690785081872954</v>
+        <v>0.1690785081872952</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3750584331914771</v>
+        <v>0.3750584331914776</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1405923408596157</v>
+        <v>0.1405923408596158</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1245982918153735</v>
+        <v>0.1245982918153738</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2553942191007073</v>
+        <v>0.2553942191007078</v>
       </c>
       <c r="T4" t="n">
         <v>0.2271302865847377</v>
@@ -4969,22 +4969,22 @@
         <v>0.1958454469852426</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1956907843819707</v>
+        <v>0.1956907843819706</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3988212450629402</v>
+        <v>0.3988212450629421</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.8009147934278613</v>
+        <v>0.8009147934278614</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.129501386677473</v>
+        <v>0.1295013866774731</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.317269556409261</v>
+        <v>0.3172695564092616</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.616842975598774</v>
+        <v>0.6168429755987743</v>
       </c>
     </row>
     <row r="5">
@@ -5082,7 +5082,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01581930983885323</v>
+        <v>0.02370948256686383</v>
       </c>
       <c r="C6" t="n">
         <v>0.01581930983885323</v>
@@ -5091,76 +5091,76 @@
         <v>0.01581930983885323</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01581930983885323</v>
+        <v>0.02370948256686383</v>
       </c>
       <c r="F6" t="n">
         <v>0.01581930983885323</v>
       </c>
       <c r="G6" t="n">
+        <v>0.02370948256686383</v>
+      </c>
+      <c r="H6" t="n">
         <v>0.01581930983885323</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.02370948256686382</v>
       </c>
       <c r="I6" t="n">
         <v>0.01581930983885323</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01579830853662538</v>
+        <v>0.02368848126463598</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02370948256686382</v>
+        <v>0.02370948256686383</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01581930983885323</v>
+        <v>0.02370948256686383</v>
       </c>
       <c r="M6" t="n">
         <v>0.01581930983885323</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01588266708132527</v>
+        <v>0.01588266708132513</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01588266708132527</v>
+        <v>0.0237255690237224</v>
       </c>
       <c r="P6" t="n">
-        <v>0.02372551044980922</v>
+        <v>0.01538058726527313</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.02370948256686382</v>
+        <v>0.02370948256686383</v>
       </c>
       <c r="R6" t="n">
-        <v>0.02370948256686382</v>
+        <v>0.02370948256686383</v>
       </c>
       <c r="S6" t="n">
-        <v>0.02370948256686382</v>
+        <v>0.02370948256686383</v>
       </c>
       <c r="T6" t="n">
+        <v>0.02370948256686383</v>
+      </c>
+      <c r="U6" t="n">
         <v>0.01581930983885323</v>
       </c>
-      <c r="U6" t="n">
-        <v>0.02370948256686382</v>
-      </c>
       <c r="V6" t="n">
-        <v>0.02357486106235859</v>
+        <v>0.01568468833434801</v>
       </c>
       <c r="W6" t="n">
-        <v>0.023725540447888</v>
+        <v>0.02372554044788798</v>
       </c>
       <c r="X6" t="n">
         <v>0.01581930983885323</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01625116058165153</v>
+        <v>0.01625116058165145</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.02370948256686382</v>
+        <v>0.02370948256686383</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.02370948256686382</v>
+        <v>0.02370948256686383</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.01597629150442558</v>
+        <v>0.01597629150442557</v>
       </c>
     </row>
     <row r="7">
@@ -5170,85 +5170,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01489860944064856</v>
+        <v>0.01489860944064855</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01489860944064856</v>
+        <v>0.01489860944064855</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01489860944064856</v>
+        <v>0.01489860944064855</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01489860944064856</v>
+        <v>0.01489860944064855</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01489860944064856</v>
+        <v>0.01489860944064855</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01489860944064856</v>
+        <v>0.01489860944064855</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01489860944064856</v>
+        <v>0.01489860944064855</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01489860944064856</v>
+        <v>0.01489860944064855</v>
       </c>
       <c r="J7" t="n">
         <v>0.0148776081384207</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01489860944064856</v>
+        <v>0.01489860944064855</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01489860944064856</v>
+        <v>0.01489860944064855</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01489860944064856</v>
+        <v>0.01489860944064855</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01489860944064856</v>
+        <v>0.01489860944064855</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01489792523864268</v>
+        <v>0.01489792523864267</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01489792523864268</v>
+        <v>0.01489792523864267</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.01489860944064856</v>
+        <v>0.01489860944064855</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01489860944064856</v>
+        <v>0.01489860944064855</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01489860944064856</v>
+        <v>0.01489860944064855</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01489860944064856</v>
+        <v>0.01489860944064855</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01489143201416598</v>
+        <v>0.01489143201416597</v>
       </c>
       <c r="V7" t="n">
-        <v>0.01476398793614333</v>
+        <v>0.01476398793614332</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01489860944064856</v>
+        <v>0.01489860944064855</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01489860944064856</v>
+        <v>0.01489860944064855</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01489860944064856</v>
+        <v>0.01489860944064855</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.01489860944064856</v>
+        <v>0.01489860944064855</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01489860944064856</v>
+        <v>0.01489860944064855</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01489860944064856</v>
+        <v>0.01489860944064855</v>
       </c>
     </row>
     <row r="8">
@@ -5258,85 +5258,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02197792233019697</v>
+        <v>0.02197792233019695</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03146339530433961</v>
+        <v>0.03146339530433958</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03146339530433961</v>
+        <v>0.03146339530433958</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03146339530433961</v>
+        <v>0.02641266074981562</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02345564816033276</v>
+        <v>0.02345564816033273</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03146339530433961</v>
+        <v>0.03343026991754661</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03146339530433961</v>
+        <v>0.03146339530433958</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03146339530433961</v>
+        <v>0.03146339530433958</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03144239400211175</v>
+        <v>0.03144239400211172</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03146339530433961</v>
+        <v>0.03146339530433958</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03146339530433961</v>
+        <v>0.03146339530433958</v>
       </c>
       <c r="M8" t="n">
-        <v>0.03146339530433961</v>
+        <v>0.03146339530433922</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02411056686396471</v>
+        <v>0.02411056686396469</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02613118796224545</v>
+        <v>0.02613118796224544</v>
       </c>
       <c r="P8" t="n">
-        <v>0.02563588490607665</v>
+        <v>0.02563588490607664</v>
       </c>
       <c r="Q8" t="n">
         <v>0.02011381039576052</v>
       </c>
       <c r="R8" t="n">
-        <v>0.03146339530433961</v>
+        <v>0.03146339530433958</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03146339530433961</v>
+        <v>0.03146339530433958</v>
       </c>
       <c r="T8" t="n">
-        <v>0.03146339530433961</v>
+        <v>0.03146339530433958</v>
       </c>
       <c r="U8" t="n">
-        <v>0.02562180406604205</v>
+        <v>0.02682863045648079</v>
       </c>
       <c r="V8" t="n">
-        <v>0.03132877379983438</v>
+        <v>0.02873070076407074</v>
       </c>
       <c r="W8" t="n">
-        <v>0.031465259470236</v>
+        <v>0.03146525947023595</v>
       </c>
       <c r="X8" t="n">
-        <v>0.02098317284095259</v>
+        <v>0.02098317284095256</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.04088597673767</v>
+        <v>0.04088597673766995</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.03146339530433961</v>
+        <v>0.02180172479994785</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.03146339530433961</v>
+        <v>0.03146339530433958</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.04137176498697198</v>
+        <v>0.04137176498697194</v>
       </c>
     </row>
     <row r="9">
@@ -5346,85 +5346,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02753567140708999</v>
+        <v>0.02753567140708996</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03320127765286395</v>
+        <v>0.03320127765286391</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03320127765286395</v>
+        <v>0.03320127765286391</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03320127765286395</v>
+        <v>0.03189368140306739</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03320127765286395</v>
+        <v>0.0201405046179719</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03320127765286395</v>
+        <v>0.03320128098376308</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03320127765286395</v>
+        <v>0.03320127765286391</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03320127765286395</v>
+        <v>0.03320127765286391</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03318027635063603</v>
+        <v>0.03318027635063601</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03320127765286395</v>
+        <v>0.03320127765286391</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03320127765286395</v>
+        <v>0.03320127765286391</v>
       </c>
       <c r="M9" t="n">
-        <v>0.03320127765286395</v>
+        <v>0.03320127765286391</v>
       </c>
       <c r="N9" t="n">
-        <v>0.03320127765286395</v>
+        <v>0.03320127765286391</v>
       </c>
       <c r="O9" t="n">
         <v>0.035078856578991</v>
       </c>
       <c r="P9" t="n">
-        <v>0.03548719705718021</v>
+        <v>0.03548719705718022</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0332012809837631</v>
+        <v>0.03320128098376308</v>
       </c>
       <c r="R9" t="n">
-        <v>0.03320127765286395</v>
+        <v>0.03320127765286391</v>
       </c>
       <c r="S9" t="n">
-        <v>0.03320127765286395</v>
+        <v>0.03320127765286391</v>
       </c>
       <c r="T9" t="n">
-        <v>0.03320127765286395</v>
+        <v>0.03320127765286391</v>
       </c>
       <c r="U9" t="n">
-        <v>0.03320127765286395</v>
+        <v>0.03320127765286391</v>
       </c>
       <c r="V9" t="n">
-        <v>0.03306665614835866</v>
+        <v>0.03960464446846768</v>
       </c>
       <c r="W9" t="n">
-        <v>0.03320127765286395</v>
+        <v>0.03320127765286391</v>
       </c>
       <c r="X9" t="n">
-        <v>0.03320127765286395</v>
+        <v>0.03320127765286391</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.03320127765286395</v>
+        <v>0.03320127765286391</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.03320127765286395</v>
+        <v>0.02978542221469</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.03320127765286395</v>
+        <v>0.03320127765286391</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.03320127765286395</v>
+        <v>0.03320127765286391</v>
       </c>
     </row>
     <row r="10">
@@ -5434,85 +5434,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01389103990060915</v>
+        <v>0.01389103990060913</v>
       </c>
       <c r="C10" t="n">
-        <v>0.01761026495802121</v>
+        <v>0.01761026495802119</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01394474317405427</v>
+        <v>0.01394474317405426</v>
       </c>
       <c r="E10" t="n">
-        <v>0.02993691541262688</v>
+        <v>0.02993691541262689</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01470702475565244</v>
+        <v>0.01470702475565243</v>
       </c>
       <c r="G10" t="n">
-        <v>0.00934816776600364</v>
+        <v>0.009348167766003617</v>
       </c>
       <c r="H10" t="n">
-        <v>0.01706749997157391</v>
+        <v>0.0170674999715739</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01321749078521832</v>
+        <v>0.0132174907852183</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01258954299025448</v>
+        <v>0.01258954299025447</v>
       </c>
       <c r="K10" t="n">
-        <v>0.01050378541520351</v>
+        <v>0.01050378541520349</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01108223035067625</v>
+        <v>0.01108223035067622</v>
       </c>
       <c r="M10" t="n">
-        <v>0.01244273127766037</v>
+        <v>0.01244273127766036</v>
       </c>
       <c r="N10" t="n">
         <v>0.01614486739295998</v>
       </c>
       <c r="O10" t="n">
-        <v>0.01451038866799242</v>
+        <v>0.01451038866799239</v>
       </c>
       <c r="P10" t="n">
-        <v>0.009123667113368941</v>
+        <v>0.009123667113368905</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.01559189553509536</v>
+        <v>0.01559189553509534</v>
       </c>
       <c r="R10" t="n">
-        <v>0.01604469224646205</v>
+        <v>0.01604469224646203</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01248371244811573</v>
+        <v>0.01248371244811571</v>
       </c>
       <c r="T10" t="n">
-        <v>0.01390894801753874</v>
+        <v>0.0139089480175387</v>
       </c>
       <c r="U10" t="n">
-        <v>0.008630891997975686</v>
+        <v>0.008630891997975669</v>
       </c>
       <c r="V10" t="n">
-        <v>0.01329805571534682</v>
+        <v>0.01329805571534683</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0143786156579024</v>
+        <v>0.01437861565790239</v>
       </c>
       <c r="X10" t="n">
-        <v>0.009341997550789023</v>
+        <v>0.009341997550788976</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.0005178816797104136</v>
+        <v>0.0005178816797103876</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.0154011006135463</v>
+        <v>0.01540110061354629</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.01159336529885162</v>
+        <v>0.01159336529885159</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.005070586183869353</v>
+        <v>0.005070586183869344</v>
       </c>
     </row>
     <row r="11">
@@ -5522,13 +5522,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.01711394487793533</v>
+        <v>0.01711394487793532</v>
       </c>
       <c r="C11" t="n">
-        <v>0.01802191657221095</v>
+        <v>0.01802191657221094</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01691991907565921</v>
+        <v>0.0169199190756592</v>
       </c>
       <c r="E11" t="n">
         <v>0.0306285727606532</v>
@@ -5537,49 +5537,49 @@
         <v>0.01717891432071508</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0151383845633365</v>
+        <v>0.01513838456333648</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0185592443330019</v>
+        <v>0.01855924433300189</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01680747788395882</v>
+        <v>0.01680747788395881</v>
       </c>
       <c r="J11" t="n">
-        <v>0.01651080466843205</v>
+        <v>0.01651080466843204</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01558753520263298</v>
+        <v>0.01558753520263297</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01583592758157094</v>
+        <v>0.01583592758157093</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0164969726011</v>
+        <v>0.01649697260109999</v>
       </c>
       <c r="N11" t="n">
         <v>0.01754356066665917</v>
       </c>
       <c r="O11" t="n">
-        <v>0.01739575054084214</v>
+        <v>0.01739575054084213</v>
       </c>
       <c r="P11" t="n">
-        <v>0.01494477506702541</v>
+        <v>0.0149447750670254</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.01788783961193184</v>
+        <v>0.01788783961193183</v>
       </c>
       <c r="R11" t="n">
-        <v>0.01800934583148038</v>
+        <v>0.01800934583148037</v>
       </c>
       <c r="S11" t="n">
         <v>0.01647360640216436</v>
       </c>
       <c r="T11" t="n">
-        <v>0.01712209312820807</v>
+        <v>0.01712209312820806</v>
       </c>
       <c r="U11" t="n">
-        <v>0.01472056081914038</v>
+        <v>0.01472056081914037</v>
       </c>
       <c r="V11" t="n">
         <v>0.01640194184080008</v>
@@ -5588,13 +5588,13 @@
         <v>0.0173357934013155</v>
       </c>
       <c r="X11" t="n">
-        <v>0.01492303263280957</v>
+        <v>0.01492303263280955</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.01102911526969984</v>
+        <v>0.01102911526969983</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.01733018114574871</v>
+        <v>0.0173301811457487</v>
       </c>
       <c r="AA11" t="n">
         <v>0.01606849561188115</v>
@@ -5772,16 +5772,16 @@
         <v>0.01758156605198403</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01789911111288703</v>
+        <v>0.01789911111288702</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03055633690627298</v>
+        <v>0.03055633690627297</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01767604219788878</v>
+        <v>0.01767604219788879</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01760887383893219</v>
+        <v>0.01760887383893218</v>
       </c>
       <c r="H2" t="n">
         <v>0.0178815314773432</v>
@@ -5793,7 +5793,7 @@
         <v>0.01786326440609989</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01789774414997661</v>
+        <v>0.0178977441499766</v>
       </c>
       <c r="L2" t="n">
         <v>0.0178815314773432</v>
@@ -5814,7 +5814,7 @@
         <v>0.0178815314773432</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01788457003614977</v>
+        <v>0.01788457003614976</v>
       </c>
       <c r="S2" t="n">
         <v>0.0178815314773432</v>
@@ -5826,13 +5826,13 @@
         <v>0.0178815314773432</v>
       </c>
       <c r="V2" t="n">
-        <v>0.01770859885476271</v>
+        <v>0.01770859885476267</v>
       </c>
       <c r="W2" t="n">
         <v>0.0178815314773432</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01783746171216808</v>
+        <v>0.01783746171216807</v>
       </c>
       <c r="Y2" t="n">
         <v>0.0178815314773432</v>
@@ -5854,82 +5854,82 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01781967177944966</v>
+        <v>0.01781967177944965</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0179110536955478</v>
+        <v>0.01791105369554779</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01781967177944966</v>
+        <v>0.01781967177944965</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03088813951290242</v>
+        <v>0.03088813951290241</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01785267934571189</v>
+        <v>0.01785267934571188</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01746679651126282</v>
+        <v>0.01746679651126281</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01781967177944966</v>
+        <v>0.01781967177944965</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01781967177944966</v>
+        <v>0.01781967177944965</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01780140263808395</v>
+        <v>0.01780140263808396</v>
       </c>
       <c r="K3" t="n">
         <v>0.017837413154143</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01781967177944966</v>
+        <v>0.01781967177944965</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01781967177944966</v>
+        <v>0.01781967177944965</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01781967177944966</v>
+        <v>0.01781967177944965</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01781967177944966</v>
+        <v>0.01781967177944965</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01781967177944966</v>
+        <v>0.01781967177944965</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01781967177944966</v>
+        <v>0.01781967177944965</v>
       </c>
       <c r="R3" t="n">
         <v>0.0178229967374256</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01781967177944966</v>
+        <v>0.01781967177944965</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01781967177944966</v>
+        <v>0.01781967177944965</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01781967177944966</v>
+        <v>0.01781967177944965</v>
       </c>
       <c r="V3" t="n">
-        <v>0.01791219827492947</v>
+        <v>0.01791219827492944</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01781967177944966</v>
+        <v>0.01781967177944965</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01777144612676041</v>
+        <v>0.0177714461267604</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01781967177944966</v>
+        <v>0.01781967177944965</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0178237500540287</v>
+        <v>0.01782375005402869</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.01781967177944966</v>
+        <v>0.01781967177944965</v>
       </c>
       <c r="AB3" t="n">
         <v>0.01711789165303279</v>
@@ -5942,85 +5942,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.06833764939569868</v>
+        <v>0.06833764939569867</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03186815400239482</v>
+        <v>0.03186815400239479</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1441468589429393</v>
+        <v>0.1441468589429394</v>
       </c>
       <c r="E4" t="n">
-        <v>0.08114572222497242</v>
+        <v>0.08114572222497253</v>
       </c>
       <c r="F4" t="n">
-        <v>0.07317869609323882</v>
+        <v>0.0731786960932389</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1301675426352364</v>
+        <v>0.1301675426352367</v>
       </c>
       <c r="H4" t="n">
         <v>0.1354907779620904</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1237679902365226</v>
+        <v>0.1237679902365225</v>
       </c>
       <c r="J4" t="n">
         <v>0.1252043279859851</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1948901665816882</v>
+        <v>0.1948901665816879</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2018845917419209</v>
+        <v>0.2018845917419212</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1865832566765329</v>
+        <v>0.186583256676533</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1986374909424837</v>
+        <v>0.1986374909424836</v>
       </c>
       <c r="O4" t="n">
-        <v>0.07837026385613585</v>
+        <v>0.0783702638561357</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1621363299783803</v>
+        <v>0.1621363299783802</v>
       </c>
       <c r="Q4" t="n">
         <v>0.1139776337889243</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1414983163385955</v>
+        <v>0.1414983163385953</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1133189122575743</v>
+        <v>0.1133189122575742</v>
       </c>
       <c r="T4" t="n">
         <v>0.09165723118877973</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1986374909424837</v>
+        <v>0.1986374909424836</v>
       </c>
       <c r="V4" t="n">
-        <v>0.05936138659067866</v>
+        <v>0.05936138659067853</v>
       </c>
       <c r="W4" t="n">
-        <v>0.187814410301155</v>
+        <v>0.1878144103011552</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1636331991811875</v>
+        <v>0.1636331991811876</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.07386093317275945</v>
+        <v>0.07386093317275901</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.1049280265472022</v>
+        <v>0.1049280265472021</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.1671491782748867</v>
+        <v>0.1671491782748868</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.2017882920729634</v>
+        <v>0.2017882920729636</v>
       </c>
     </row>
     <row r="5">
@@ -6030,7 +6030,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.008235899876473864</v>
+        <v>0.008235899876473865</v>
       </c>
       <c r="C5" t="n">
         <v>0.008235899876473865</v>
@@ -6042,7 +6042,7 @@
         <v>0.008235899876473865</v>
       </c>
       <c r="F5" t="n">
-        <v>0.008235899876473864</v>
+        <v>0.008235899876473865</v>
       </c>
       <c r="G5" t="n">
         <v>0.008235899876473865</v>
@@ -6054,7 +6054,7 @@
         <v>0.008235899876473865</v>
       </c>
       <c r="J5" t="n">
-        <v>0.008215104072480751</v>
+        <v>0.00821510407248075</v>
       </c>
       <c r="K5" t="n">
         <v>0.008235899876473865</v>
@@ -6066,16 +6066,16 @@
         <v>0.008235899876473865</v>
       </c>
       <c r="N5" t="n">
-        <v>0.008235899876473864</v>
+        <v>0.008235899876473865</v>
       </c>
       <c r="O5" t="n">
-        <v>0.008235899876473864</v>
+        <v>0.008235899876473865</v>
       </c>
       <c r="P5" t="n">
-        <v>0.008235899876473864</v>
+        <v>0.008235899876473865</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.008235899876473864</v>
+        <v>0.008235899876473865</v>
       </c>
       <c r="R5" t="n">
         <v>0.008235899876473865</v>
@@ -6087,19 +6087,19 @@
         <v>0.008235899876473865</v>
       </c>
       <c r="U5" t="n">
-        <v>0.008116192761970079</v>
+        <v>0.008116192761970085</v>
       </c>
       <c r="V5" t="n">
-        <v>0.008102537651797147</v>
+        <v>0.008102537651797165</v>
       </c>
       <c r="W5" t="n">
-        <v>0.008235899876473864</v>
+        <v>0.008235899876473865</v>
       </c>
       <c r="X5" t="n">
-        <v>0.008235899876473864</v>
+        <v>0.008235899876473865</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.008116192761970079</v>
+        <v>0.008116192761970085</v>
       </c>
       <c r="Z5" t="n">
         <v>0.008235899876473865</v>
@@ -6108,7 +6108,7 @@
         <v>0.008235899876473865</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.008235899876473864</v>
+        <v>0.008235899876473865</v>
       </c>
     </row>
     <row r="6">
@@ -6118,85 +6118,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01205088595904733</v>
+        <v>0.01205088595904729</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01883427287164197</v>
+        <v>0.01883427287164198</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01883427287164197</v>
+        <v>0.01205088595904729</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01883427287164197</v>
+        <v>0.01205088595904729</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01883427287164197</v>
+        <v>0.01883427287164198</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01205088595904733</v>
+        <v>0.01883427287164198</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01205088595904733</v>
+        <v>0.01205088595904729</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01883427287164197</v>
+        <v>0.01205088595904729</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01203009015505426</v>
+        <v>0.01203009015505417</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01883427287164197</v>
+        <v>0.01205088595904729</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01883427287164197</v>
+        <v>0.01205088595904729</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01205088595904733</v>
+        <v>0.01883427287164198</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01205814198926089</v>
+        <v>0.01205814198926087</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01881527298849161</v>
+        <v>0.01881527298849165</v>
       </c>
       <c r="P6" t="n">
-        <v>0.01881525754135551</v>
+        <v>0.01166757610758576</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01883427287164197</v>
+        <v>0.01883427287164198</v>
       </c>
       <c r="R6" t="n">
-        <v>0.01883427287164197</v>
+        <v>0.01205088595904729</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01883427287164197</v>
+        <v>0.01205088595904729</v>
       </c>
       <c r="T6" t="n">
-        <v>0.01205088595904733</v>
+        <v>0.01883427287164198</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01883427287164197</v>
+        <v>0.01205088595904729</v>
       </c>
       <c r="V6" t="n">
-        <v>0.01191752373437068</v>
+        <v>0.01870091064696526</v>
       </c>
       <c r="W6" t="n">
-        <v>0.01242815212467958</v>
+        <v>0.01242815212467937</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01205088595904733</v>
+        <v>0.01205088595904729</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01234233507606041</v>
+        <v>0.01234233507606053</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.01205088595904733</v>
+        <v>0.01883427287164198</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.01205088595904733</v>
+        <v>0.01883427287164198</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.01208608082312701</v>
+        <v>0.01208608082312702</v>
       </c>
     </row>
     <row r="7">
@@ -6245,10 +6245,10 @@
         <v>0.01250352925769575</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01250281488899297</v>
+        <v>0.01250281488899298</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01250281488899297</v>
+        <v>0.01250281488899298</v>
       </c>
       <c r="Q7" t="n">
         <v>0.01250352925769575</v>
@@ -6266,7 +6266,7 @@
         <v>0.01249653312940489</v>
       </c>
       <c r="V7" t="n">
-        <v>0.01237016703301904</v>
+        <v>0.01237016703301905</v>
       </c>
       <c r="W7" t="n">
         <v>0.01250352925769575</v>
@@ -6294,70 +6294,70 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.018939483643826</v>
+        <v>0.01893948364382599</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02765671810331819</v>
+        <v>0.02765671810331817</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02765671810331819</v>
+        <v>0.02765671810331817</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02765671810331819</v>
+        <v>0.023015047896172</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02029752689200567</v>
+        <v>0.02029752689200565</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02765671810331819</v>
+        <v>0.02946429345591849</v>
       </c>
       <c r="H8" t="n">
-        <v>0.02765671810331819</v>
+        <v>0.02765671810331817</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02765671810331819</v>
+        <v>0.02765671810331817</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02763592229932503</v>
+        <v>0.02763592229932504</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02765671810331819</v>
+        <v>0.02765671810331817</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02765671810331819</v>
+        <v>0.02765671810331817</v>
       </c>
       <c r="M8" t="n">
-        <v>0.02765671810331819</v>
+        <v>0.02765671810331723</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0208994030353707</v>
+        <v>0.02089940303537068</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02275637188828995</v>
+        <v>0.02275637188828993</v>
       </c>
       <c r="P8" t="n">
-        <v>0.02230118395183781</v>
+        <v>0.0223011839518378</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01722634811163678</v>
+        <v>0.01722634811163675</v>
       </c>
       <c r="R8" t="n">
-        <v>0.02765671810331819</v>
+        <v>0.02765671810331817</v>
       </c>
       <c r="S8" t="n">
-        <v>0.02765671810331819</v>
+        <v>0.02765671810331817</v>
       </c>
       <c r="T8" t="n">
-        <v>0.02765671810331819</v>
+        <v>0.02765671810331817</v>
       </c>
       <c r="U8" t="n">
-        <v>0.02228801472740737</v>
+        <v>0.02339708410115365</v>
       </c>
       <c r="V8" t="n">
-        <v>0.02752335587864146</v>
+        <v>0.02513543476767452</v>
       </c>
       <c r="W8" t="n">
-        <v>0.02765843128860095</v>
+        <v>0.02765843128860091</v>
       </c>
       <c r="X8" t="n">
         <v>0.01802529997061189</v>
@@ -6366,13 +6366,13 @@
         <v>0.03631573781900763</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.02765671810331819</v>
+        <v>0.01877755653838011</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.02765671810331819</v>
+        <v>0.02765671810331817</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.03676259841858289</v>
+        <v>0.03676259841858288</v>
       </c>
     </row>
     <row r="9">
@@ -6382,85 +6382,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02451064683610589</v>
+        <v>0.02451064683610591</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02984558489201555</v>
+        <v>0.02984558489201558</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02984558489201555</v>
+        <v>0.02984558489201558</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02984558489201555</v>
+        <v>0.0286143050388093</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02984558489201555</v>
+        <v>0.0175470930850739</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02984558489201555</v>
+        <v>0.02984558760817626</v>
       </c>
       <c r="H9" t="n">
-        <v>0.02984558489201555</v>
+        <v>0.02984558489201558</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02984558489201555</v>
+        <v>0.02984558489201558</v>
       </c>
       <c r="J9" t="n">
         <v>0.02982478908802251</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02984558489201555</v>
+        <v>0.02984558489201558</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02984558489201555</v>
+        <v>0.02984558489201558</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02984558489201555</v>
+        <v>0.02984558489201558</v>
       </c>
       <c r="N9" t="n">
-        <v>0.02984558489201555</v>
+        <v>0.02984558489201558</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0316135799945324</v>
+        <v>0.03161357999453241</v>
       </c>
       <c r="P9" t="n">
-        <v>0.03199808800492328</v>
+        <v>0.03199808800492326</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.02984558760817625</v>
+        <v>0.02984558760817626</v>
       </c>
       <c r="R9" t="n">
-        <v>0.02984558489201555</v>
+        <v>0.02984558489201558</v>
       </c>
       <c r="S9" t="n">
-        <v>0.02984558489201555</v>
+        <v>0.02984558489201558</v>
       </c>
       <c r="T9" t="n">
-        <v>0.02984558489201555</v>
+        <v>0.02984558489201558</v>
       </c>
       <c r="U9" t="n">
-        <v>0.02984558489201555</v>
+        <v>0.02984558489201558</v>
       </c>
       <c r="V9" t="n">
-        <v>0.02971222266733891</v>
+        <v>0.03586862679819239</v>
       </c>
       <c r="W9" t="n">
-        <v>0.02984558489201555</v>
+        <v>0.02984558489201558</v>
       </c>
       <c r="X9" t="n">
-        <v>0.02984558489201555</v>
+        <v>0.02984558489201558</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.02984558489201555</v>
+        <v>0.02984558489201558</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.02984558489201555</v>
+        <v>0.02662909272406112</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.02984558489201555</v>
+        <v>0.02984558489201558</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.02984558489201555</v>
+        <v>0.02984558489201558</v>
       </c>
     </row>
     <row r="10">
@@ -6470,7 +6470,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01641956475532753</v>
+        <v>0.01641956475532752</v>
       </c>
       <c r="C10" t="n">
         <v>0.017449536612295</v>
@@ -6479,31 +6479,31 @@
         <v>0.01500952035817392</v>
       </c>
       <c r="E10" t="n">
-        <v>0.02925685666469406</v>
+        <v>0.02925685666469409</v>
       </c>
       <c r="F10" t="n">
         <v>0.01653235436082835</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01442252642697437</v>
+        <v>0.01442252642697435</v>
       </c>
       <c r="H10" t="n">
         <v>0.01532885911900401</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01547376087895272</v>
+        <v>0.01547376087895273</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01506821538439258</v>
+        <v>0.01506821538439259</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0135869495122582</v>
+        <v>0.01358694951225819</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01306632504267141</v>
+        <v>0.0130663250426714</v>
       </c>
       <c r="M10" t="n">
-        <v>0.01384085979012846</v>
+        <v>0.01384085979012845</v>
       </c>
       <c r="N10" t="n">
         <v>0.01430661956135399</v>
@@ -6515,22 +6515,22 @@
         <v>0.01422991395572412</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0155045520346197</v>
+        <v>0.01550455203461969</v>
       </c>
       <c r="R10" t="n">
-        <v>0.01518095499237963</v>
+        <v>0.01518095499237964</v>
       </c>
       <c r="S10" t="n">
         <v>0.01510154985014503</v>
       </c>
       <c r="T10" t="n">
-        <v>0.01605808187515535</v>
+        <v>0.01605808187515534</v>
       </c>
       <c r="U10" t="n">
-        <v>0.01347029675920742</v>
+        <v>0.01347029675920741</v>
       </c>
       <c r="V10" t="n">
-        <v>0.01672691920514131</v>
+        <v>0.01672691920514129</v>
       </c>
       <c r="W10" t="n">
         <v>0.01395019216580292</v>
@@ -6539,7 +6539,7 @@
         <v>0.01450629316686035</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.0164158961282143</v>
+        <v>0.01641589612821431</v>
       </c>
       <c r="Z10" t="n">
         <v>0.01548734604341629</v>
@@ -6548,7 +6548,7 @@
         <v>0.01439361705115539</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.01319818811580067</v>
+        <v>0.01319818811580066</v>
       </c>
     </row>
     <row r="11">
@@ -6558,10 +6558,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.01724447831949128</v>
+        <v>0.01724447831949127</v>
       </c>
       <c r="C11" t="n">
-        <v>0.01737157430833633</v>
+        <v>0.01737157430833634</v>
       </c>
       <c r="D11" t="n">
         <v>0.01662048326078535</v>
@@ -6576,16 +6576,16 @@
         <v>0.01622372124906779</v>
       </c>
       <c r="H11" t="n">
-        <v>0.01674820377909146</v>
+        <v>0.01674820377909147</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01681413454164266</v>
+        <v>0.01681413454164264</v>
       </c>
       <c r="J11" t="n">
-        <v>0.01661965549551934</v>
+        <v>0.01661965549551935</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01596376964749511</v>
+        <v>0.01596376964749512</v>
       </c>
       <c r="L11" t="n">
         <v>0.01571874356409184</v>
@@ -6594,7 +6594,7 @@
         <v>0.01629084553151859</v>
       </c>
       <c r="N11" t="n">
-        <v>0.01641812873348717</v>
+        <v>0.01641812873348716</v>
       </c>
       <c r="O11" t="n">
         <v>0.01711566743754914</v>
@@ -6609,19 +6609,19 @@
         <v>0.01668243262246636</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01664477733736894</v>
+        <v>0.01664477733736896</v>
       </c>
       <c r="T11" t="n">
-        <v>0.01708000245703534</v>
+        <v>0.01708000245703535</v>
       </c>
       <c r="U11" t="n">
         <v>0.0159025519824972</v>
       </c>
       <c r="V11" t="n">
-        <v>0.01716929310074883</v>
+        <v>0.01716929310074879</v>
       </c>
       <c r="W11" t="n">
-        <v>0.01612090592183408</v>
+        <v>0.01612090592183407</v>
       </c>
       <c r="X11" t="n">
         <v>0.01635180670998848</v>
@@ -6630,10 +6630,10 @@
         <v>0.01724280908246354</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.01675316168309953</v>
+        <v>0.01675316168309954</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.01632266565778071</v>
+        <v>0.01632266565778072</v>
       </c>
       <c r="AB11" t="n">
         <v>0.01545674947638398</v>
@@ -6805,19 +6805,19 @@
         <v>0.01761711369738071</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01758924129802023</v>
+        <v>0.01758924129802022</v>
       </c>
       <c r="D2" t="n">
         <v>0.01749747811453359</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03055835071006808</v>
+        <v>0.03055835071006807</v>
       </c>
       <c r="F2" t="n">
         <v>0.01769607817106254</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01719628348592607</v>
+        <v>0.01719628348592608</v>
       </c>
       <c r="H2" t="n">
         <v>0.01761711369738071</v>
@@ -6826,7 +6826,7 @@
         <v>0.01761711369738071</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01760996624887319</v>
+        <v>0.0176099662488732</v>
       </c>
       <c r="K2" t="n">
         <v>0.01764011018687637</v>
@@ -6835,10 +6835,10 @@
         <v>0.01761711369738071</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01746191898459258</v>
+        <v>0.01746191898459257</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0176525277049782</v>
+        <v>0.01765252770497819</v>
       </c>
       <c r="O2" t="n">
         <v>0.01761711369738071</v>
@@ -6862,7 +6862,7 @@
         <v>0.01761711369738071</v>
       </c>
       <c r="V2" t="n">
-        <v>0.01768915632353345</v>
+        <v>0.01768915632353344</v>
       </c>
       <c r="W2" t="n">
         <v>0.01761711369738071</v>
@@ -6899,7 +6899,7 @@
         <v>0.01772531058085606</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03084297748401467</v>
+        <v>0.03084297748401468</v>
       </c>
       <c r="F3" t="n">
         <v>0.01777189495553481</v>
@@ -6914,7 +6914,7 @@
         <v>0.01772531058085606</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0177181623368031</v>
+        <v>0.01771816233680312</v>
       </c>
       <c r="K3" t="n">
         <v>0.0177504755212056</v>
@@ -6956,7 +6956,7 @@
         <v>0.01772531058085606</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01714967292288436</v>
+        <v>0.01714967292288437</v>
       </c>
       <c r="Y3" t="n">
         <v>0.01772531058085606</v>
@@ -6978,85 +6978,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04930291117255787</v>
+        <v>0.04930291117255779</v>
       </c>
       <c r="C4" t="n">
-        <v>0.052975136149922</v>
+        <v>0.05297513614992207</v>
       </c>
       <c r="D4" t="n">
-        <v>0.05211833408437157</v>
+        <v>0.05211833408437151</v>
       </c>
       <c r="E4" t="n">
-        <v>0.08691260930688813</v>
+        <v>0.08691260930688822</v>
       </c>
       <c r="F4" t="n">
-        <v>0.09197019037223478</v>
+        <v>0.09197019037223496</v>
       </c>
       <c r="G4" t="n">
-        <v>0.06409203747796668</v>
+        <v>0.06409203747796664</v>
       </c>
       <c r="H4" t="n">
-        <v>0.08515987680985233</v>
+        <v>0.08515987680985235</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07860426133185019</v>
+        <v>0.07860426133185022</v>
       </c>
       <c r="J4" t="n">
-        <v>0.07625885663426263</v>
+        <v>0.07625885663426268</v>
       </c>
       <c r="K4" t="n">
-        <v>0.05731278529797847</v>
+        <v>0.05731278529797849</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07687543024383778</v>
+        <v>0.07687543024383793</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04255597156206751</v>
+        <v>0.04255597156206757</v>
       </c>
       <c r="N4" t="n">
-        <v>0.03382351810642265</v>
+        <v>0.03382351810642271</v>
       </c>
       <c r="O4" t="n">
-        <v>0.08447677745140701</v>
+        <v>0.08447677745140694</v>
       </c>
       <c r="P4" t="n">
-        <v>0.07622944293396293</v>
+        <v>0.07622944293396289</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.03980084951813077</v>
+        <v>0.03980084951813078</v>
       </c>
       <c r="R4" t="n">
-        <v>0.16527443429153</v>
+        <v>0.1652744342915299</v>
       </c>
       <c r="S4" t="n">
-        <v>0.07767880219655565</v>
+        <v>0.07767880219655569</v>
       </c>
       <c r="T4" t="n">
-        <v>0.05304175900649755</v>
+        <v>0.05304175900649746</v>
       </c>
       <c r="U4" t="n">
-        <v>0.03382351810642263</v>
+        <v>0.0338235181064227</v>
       </c>
       <c r="V4" t="n">
-        <v>0.07401430179349593</v>
+        <v>0.07401430179349605</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1456052185781141</v>
+        <v>0.1456052185781142</v>
       </c>
       <c r="X4" t="n">
         <v>0.2336390504127926</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.07969298073297419</v>
+        <v>0.07969298073297401</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.09296541337889141</v>
+        <v>0.09296541337889157</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.1206593542383707</v>
+        <v>0.1206593542383704</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.02479150087891224</v>
+        <v>0.02479150087891221</v>
       </c>
     </row>
     <row r="5">
@@ -7066,85 +7066,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.00754918329938637</v>
+        <v>0.007549183299386405</v>
       </c>
       <c r="C5" t="n">
-        <v>0.007549183299386407</v>
+        <v>0.007549183299386403</v>
       </c>
       <c r="D5" t="n">
-        <v>0.007549183299386407</v>
+        <v>0.007549183299386403</v>
       </c>
       <c r="E5" t="n">
-        <v>0.007549183299386407</v>
+        <v>0.007549183299386403</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00754918329938637</v>
+        <v>0.007549183299386405</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007549183299386407</v>
+        <v>0.007549183299386403</v>
       </c>
       <c r="H5" t="n">
-        <v>0.007549183299386407</v>
+        <v>0.007549183299386403</v>
       </c>
       <c r="I5" t="n">
-        <v>0.007549183299386407</v>
+        <v>0.007549183299386403</v>
       </c>
       <c r="J5" t="n">
-        <v>0.007531532258499374</v>
+        <v>0.007531532258499368</v>
       </c>
       <c r="K5" t="n">
-        <v>0.007549183299386407</v>
+        <v>0.007549183299386403</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007549183299386407</v>
+        <v>0.007549183299386403</v>
       </c>
       <c r="M5" t="n">
-        <v>0.007549183299386407</v>
+        <v>0.007549183299386403</v>
       </c>
       <c r="N5" t="n">
-        <v>0.00754918329938637</v>
+        <v>0.007549183299386405</v>
       </c>
       <c r="O5" t="n">
-        <v>0.00754918329938637</v>
+        <v>0.007549183299386405</v>
       </c>
       <c r="P5" t="n">
-        <v>0.00754918329938637</v>
+        <v>0.007549183299386405</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.00754918329938637</v>
+        <v>0.007549183299386405</v>
       </c>
       <c r="R5" t="n">
-        <v>0.007549183299386407</v>
+        <v>0.007549183299386403</v>
       </c>
       <c r="S5" t="n">
-        <v>0.007549183299386407</v>
+        <v>0.007549183299386403</v>
       </c>
       <c r="T5" t="n">
-        <v>0.007549183299386407</v>
+        <v>0.007549183299386403</v>
       </c>
       <c r="U5" t="n">
-        <v>0.007488504759384425</v>
+        <v>0.007488504759384431</v>
       </c>
       <c r="V5" t="n">
-        <v>0.007436035953174815</v>
+        <v>0.007436035953174834</v>
       </c>
       <c r="W5" t="n">
-        <v>0.00754918329938637</v>
+        <v>0.007549183299386405</v>
       </c>
       <c r="X5" t="n">
-        <v>0.00754918329938637</v>
+        <v>0.007549183299386405</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.007488504759384425</v>
+        <v>0.007488504759384429</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.007549183299386407</v>
+        <v>0.007549183299386403</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.007549183299386407</v>
+        <v>0.007549183299386403</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.00754918329938637</v>
+        <v>0.007549183299386405</v>
       </c>
     </row>
     <row r="6">
@@ -7154,85 +7154,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01122545148257364</v>
+        <v>0.01122545148257361</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01729967614751697</v>
+        <v>0.01122545148257361</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01122545148257364</v>
+        <v>0.01122545148257361</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01729967614751697</v>
+        <v>0.01729967614751696</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01729967614751697</v>
+        <v>0.01729967614751696</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01729967614751697</v>
+        <v>0.01122545148257361</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01729967614751697</v>
+        <v>0.01122545148257361</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01122545148257364</v>
+        <v>0.01122545148257361</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01728202510662995</v>
+        <v>0.01120780044168659</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01122545148257364</v>
+        <v>0.01122545148257361</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01729967614751697</v>
+        <v>0.01729967614751696</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01122545148257364</v>
+        <v>0.01729967614751696</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01121872494099972</v>
+        <v>0.01121872494099965</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01121872494099972</v>
+        <v>0.0112187249409997</v>
       </c>
       <c r="P6" t="n">
-        <v>0.01726027034717939</v>
+        <v>0.0108518818167085</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01729967614751697</v>
+        <v>0.01122545148257361</v>
       </c>
       <c r="R6" t="n">
-        <v>0.01729967614751697</v>
+        <v>0.01729967614751696</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01729967614751697</v>
+        <v>0.01122545148257361</v>
       </c>
       <c r="T6" t="n">
-        <v>0.01729967614751697</v>
+        <v>0.01729967614751696</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01122545148257364</v>
+        <v>0.01122545148257361</v>
       </c>
       <c r="V6" t="n">
-        <v>0.01111230413636203</v>
+        <v>0.01718652880130539</v>
       </c>
       <c r="W6" t="n">
-        <v>0.01156872634702915</v>
+        <v>0.01156872634702904</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01122545148257364</v>
+        <v>0.01122545148257361</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01149566355943647</v>
+        <v>0.01149566355943645</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.01729967614751697</v>
+        <v>0.01729967614751696</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.01122545148257364</v>
+        <v>0.01729967614751696</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.01120357161277541</v>
+        <v>0.01120357161277542</v>
       </c>
     </row>
     <row r="7">
@@ -7242,85 +7242,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0112614320453678</v>
+        <v>0.01126143204536777</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0112614320453678</v>
+        <v>0.01126143204536777</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0112614320453678</v>
+        <v>0.01126143204536777</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0112614320453678</v>
+        <v>0.01126143204536777</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0112614320453678</v>
+        <v>0.01126143204536777</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0112614320453678</v>
+        <v>0.01126143204536777</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0112614320453678</v>
+        <v>0.01126143204536777</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0112614320453678</v>
+        <v>0.01126143204536777</v>
       </c>
       <c r="J7" t="n">
         <v>0.01124378100448073</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0112614320453678</v>
+        <v>0.01126143204536777</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0112614320453678</v>
+        <v>0.01126143204536777</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0112614320453678</v>
+        <v>0.01126143204536777</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0112614320453678</v>
+        <v>0.01126143204536777</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01126076506033627</v>
+        <v>0.01126076506033626</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01126076506033627</v>
+        <v>0.01126076506033626</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0112614320453678</v>
+        <v>0.01126143204536777</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0112614320453678</v>
+        <v>0.01126143204536777</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0112614320453678</v>
+        <v>0.01126143204536777</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0112614320453678</v>
+        <v>0.01126143204536777</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01125513552328035</v>
+        <v>0.01125513552328032</v>
       </c>
       <c r="V7" t="n">
         <v>0.01114828469915619</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0112614320453678</v>
+        <v>0.01126143204536777</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0112614320453678</v>
+        <v>0.01126143204536777</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0112614320453678</v>
+        <v>0.01126143204536777</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0112614320453678</v>
+        <v>0.01126143204536777</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0112614320453678</v>
+        <v>0.01126143204536777</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0112614320453678</v>
+        <v>0.01126143204536777</v>
       </c>
     </row>
     <row r="8">
@@ -7330,85 +7330,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01707104820226005</v>
+        <v>0.01707104820226004</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02486352858935663</v>
+        <v>0.0248635285893566</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02486352858935663</v>
+        <v>0.0248635285893566</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02486352858935663</v>
+        <v>0.02071426264719007</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01828502557381204</v>
+        <v>0.01828502557381202</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02486352858935663</v>
+        <v>0.02647935016084688</v>
       </c>
       <c r="H8" t="n">
-        <v>0.02486352858935663</v>
+        <v>0.0248635285893566</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02486352858935663</v>
+        <v>0.0248635285893566</v>
       </c>
       <c r="J8" t="n">
         <v>0.02484587754846958</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02486352858935663</v>
+        <v>0.0248635285893566</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02486352858935663</v>
+        <v>0.0248635285893566</v>
       </c>
       <c r="M8" t="n">
-        <v>0.02486352858935663</v>
+        <v>0.02486352858935521</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01882305263554817</v>
+        <v>0.01882305263554815</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02048302787578024</v>
+        <v>0.02048302787578023</v>
       </c>
       <c r="P8" t="n">
-        <v>0.02007612783382145</v>
+        <v>0.02007612783382144</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01553964795173553</v>
+        <v>0.01553964795173551</v>
       </c>
       <c r="R8" t="n">
-        <v>0.02486352858935663</v>
+        <v>0.0248635285893566</v>
       </c>
       <c r="S8" t="n">
-        <v>0.02486352858935663</v>
+        <v>0.0248635285893566</v>
       </c>
       <c r="T8" t="n">
-        <v>0.02486352858935663</v>
+        <v>0.0248635285893566</v>
       </c>
       <c r="U8" t="n">
-        <v>0.02006434533583961</v>
+        <v>0.02105576016392943</v>
       </c>
       <c r="V8" t="n">
-        <v>0.02475038124314503</v>
+        <v>0.02261576686754238</v>
       </c>
       <c r="W8" t="n">
-        <v>0.02486506003414085</v>
+        <v>0.02486506003414084</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0162538442625658</v>
+        <v>0.01625384426256582</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.03260395106859956</v>
+        <v>0.03260395106859957</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.02486352858935663</v>
+        <v>0.01692629887846603</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.02486352858935663</v>
+        <v>0.0248635285893566</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.03300342594948374</v>
+        <v>0.03300342594948368</v>
       </c>
     </row>
     <row r="9">
@@ -7418,85 +7418,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02093453185780298</v>
+        <v>0.02093453185780296</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02539469894971169</v>
+        <v>0.02539469894971163</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02539469894971169</v>
+        <v>0.02539469894971163</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02539469894971169</v>
+        <v>0.02436531345076968</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02539469894971169</v>
+        <v>0.01511279163223127</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02539469894971169</v>
+        <v>0.02539470268497592</v>
       </c>
       <c r="H9" t="n">
-        <v>0.02539469894971169</v>
+        <v>0.02539469894971163</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02539469894971169</v>
+        <v>0.02539469894971163</v>
       </c>
       <c r="J9" t="n">
-        <v>0.02537704790882464</v>
+        <v>0.02537704790882459</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02539469894971169</v>
+        <v>0.02539469894971163</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02539469894971169</v>
+        <v>0.02539469894971163</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02539469894971169</v>
+        <v>0.02539469894971163</v>
       </c>
       <c r="N9" t="n">
-        <v>0.02539469894971169</v>
+        <v>0.02539469894971163</v>
       </c>
       <c r="O9" t="n">
-        <v>0.02687279745700663</v>
+        <v>0.0268727974570066</v>
       </c>
       <c r="P9" t="n">
-        <v>0.02719425771008714</v>
+        <v>0.02719425771008711</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.02539470268497595</v>
+        <v>0.02539470268497592</v>
       </c>
       <c r="R9" t="n">
-        <v>0.02539469894971169</v>
+        <v>0.02539469894971163</v>
       </c>
       <c r="S9" t="n">
-        <v>0.02539469894971169</v>
+        <v>0.02539469894971163</v>
       </c>
       <c r="T9" t="n">
-        <v>0.02539469894971169</v>
+        <v>0.02539469894971163</v>
       </c>
       <c r="U9" t="n">
-        <v>0.02539469894971169</v>
+        <v>0.02539469894971163</v>
       </c>
       <c r="V9" t="n">
-        <v>0.02528155160350008</v>
+        <v>0.03042849244666928</v>
       </c>
       <c r="W9" t="n">
-        <v>0.02539469894971169</v>
+        <v>0.02539469894971163</v>
       </c>
       <c r="X9" t="n">
-        <v>0.02539469894971169</v>
+        <v>0.02539469894971163</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.02539469894971169</v>
+        <v>0.02539469894971163</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.02539469894971169</v>
+        <v>0.02270561629005538</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.02539469894971169</v>
+        <v>0.02539469894971163</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.02539469894971169</v>
+        <v>0.02539469894971163</v>
       </c>
     </row>
     <row r="10">
@@ -7506,16 +7506,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01670291753171162</v>
+        <v>0.01670291753171161</v>
       </c>
       <c r="C10" t="n">
-        <v>0.01679097861558546</v>
+        <v>0.01679097861558547</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01672001076726722</v>
+        <v>0.01672001076726721</v>
       </c>
       <c r="E10" t="n">
-        <v>0.02893356893110581</v>
+        <v>0.02893356893110582</v>
       </c>
       <c r="F10" t="n">
         <v>0.01586204648518106</v>
@@ -7524,13 +7524,13 @@
         <v>0.01579737089806034</v>
       </c>
       <c r="H10" t="n">
-        <v>0.01608793043884842</v>
+        <v>0.01608793043884843</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01615076253981957</v>
+        <v>0.0161507625398196</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01599564201437049</v>
+        <v>0.0159956420143705</v>
       </c>
       <c r="K10" t="n">
         <v>0.0165693476438017</v>
@@ -7539,22 +7539,22 @@
         <v>0.01579606370162077</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0169313517127508</v>
+        <v>0.01693135171275081</v>
       </c>
       <c r="N10" t="n">
-        <v>0.01580367697033169</v>
+        <v>0.01580367697033168</v>
       </c>
       <c r="O10" t="n">
         <v>0.01571801711289684</v>
       </c>
       <c r="P10" t="n">
-        <v>0.01599788879817638</v>
+        <v>0.01599788879817639</v>
       </c>
       <c r="Q10" t="n">
         <v>0.01695142203195454</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0141615435647362</v>
+        <v>0.01416154356473619</v>
       </c>
       <c r="S10" t="n">
         <v>0.0158199939822483</v>
@@ -7566,19 +7566,19 @@
         <v>0.01710068013374262</v>
       </c>
       <c r="V10" t="n">
-        <v>0.01607579985345951</v>
+        <v>0.01607579985345949</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0143461200678434</v>
+        <v>0.01434612006784341</v>
       </c>
       <c r="X10" t="n">
         <v>0.01170918512088904</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.01607609130093974</v>
+        <v>0.01607609130093975</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.01548773106913471</v>
+        <v>0.01548773106913472</v>
       </c>
       <c r="AA10" t="n">
         <v>0.01511357567625209</v>
@@ -7600,13 +7600,13 @@
         <v>0.01712045061771676</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01704006349565022</v>
+        <v>0.01704006349565024</v>
       </c>
       <c r="E11" t="n">
         <v>0.02968956373357054</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01682709103072564</v>
+        <v>0.01682709103072563</v>
       </c>
       <c r="G11" t="n">
         <v>0.01650989530837436</v>
@@ -7618,22 +7618,22 @@
         <v>0.01690068932092224</v>
       </c>
       <c r="J11" t="n">
-        <v>0.01682621401281977</v>
+        <v>0.01682621401281975</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01710269323862639</v>
+        <v>0.01710269323862637</v>
       </c>
       <c r="L11" t="n">
         <v>0.01673930021918364</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0171006651694079</v>
+        <v>0.01710066516940789</v>
       </c>
       <c r="N11" t="n">
         <v>0.01677817828830664</v>
       </c>
       <c r="O11" t="n">
-        <v>0.01670378877259452</v>
+        <v>0.01670378877259453</v>
       </c>
       <c r="P11" t="n">
         <v>0.01683113128129484</v>
@@ -7642,7 +7642,7 @@
         <v>0.01726499194139405</v>
       </c>
       <c r="R11" t="n">
-        <v>0.01595174423885857</v>
+        <v>0.01595174423885858</v>
       </c>
       <c r="S11" t="n">
         <v>0.01675018857313045</v>
@@ -7651,28 +7651,28 @@
         <v>0.01714995724129808</v>
       </c>
       <c r="U11" t="n">
-        <v>0.01733290485336495</v>
+        <v>0.01733290485336496</v>
       </c>
       <c r="V11" t="n">
-        <v>0.01690445587205478</v>
+        <v>0.01690445587205477</v>
       </c>
       <c r="W11" t="n">
         <v>0.01607957124511874</v>
       </c>
       <c r="X11" t="n">
-        <v>0.01461564220367279</v>
+        <v>0.0146156422036728</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.01686671366926876</v>
+        <v>0.01686671366926877</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.01668856288722684</v>
+        <v>0.01668856288722683</v>
       </c>
       <c r="AA11" t="n">
         <v>0.01642876599268058</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.01682267529217971</v>
+        <v>0.0168226752921797</v>
       </c>
     </row>
   </sheetData>
@@ -7838,16 +7838,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01763157903370371</v>
+        <v>0.0176315790337037</v>
       </c>
       <c r="C2" t="n">
         <v>0.01766266841649037</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01758117687426555</v>
+        <v>0.01758117687426554</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03119870893381102</v>
+        <v>0.03119870893381097</v>
       </c>
       <c r="F2" t="n">
         <v>0.01772147271449214</v>
@@ -7856,67 +7856,67 @@
         <v>0.0168908551520481</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01763157903370371</v>
+        <v>0.0176315790337037</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01763157903370371</v>
+        <v>0.0176315790337037</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0176284632080263</v>
+        <v>0.01762846320802628</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01766105955080122</v>
+        <v>0.01766105955080121</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01763157903370371</v>
+        <v>0.0176315790337037</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01749701352517235</v>
+        <v>0.01749701352517234</v>
       </c>
       <c r="N2" t="n">
-        <v>0.01760633577189742</v>
+        <v>0.01760633577189741</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01763157903370371</v>
+        <v>0.0176315790337037</v>
       </c>
       <c r="P2" t="n">
-        <v>0.01763157903370371</v>
+        <v>0.0176315790337037</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.01763157903370371</v>
+        <v>0.0176315790337037</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01746324699203305</v>
+        <v>0.01746324699203304</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01763157903370371</v>
+        <v>0.0176315790337037</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01763157903370371</v>
+        <v>0.0176315790337037</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01763157903370371</v>
+        <v>0.0176315790337037</v>
       </c>
       <c r="V2" t="n">
-        <v>0.01725353971133784</v>
+        <v>0.01725353971133782</v>
       </c>
       <c r="W2" t="n">
-        <v>0.01763157903370371</v>
+        <v>0.0176315790337037</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01739041977467637</v>
+        <v>0.01739041977467636</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.01763157903370371</v>
+        <v>0.0176315790337037</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.01769548198502944</v>
+        <v>0.01769548198502942</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.01763157903370371</v>
+        <v>0.0176315790337037</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.01699027463353914</v>
+        <v>0.01699027463353913</v>
       </c>
     </row>
     <row r="3">
@@ -7926,85 +7926,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01776264397156777</v>
+        <v>0.01776264397156778</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01785823880704926</v>
+        <v>0.01785823880704927</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01776264397156777</v>
+        <v>0.01776264397156778</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03138720702676147</v>
+        <v>0.03138720702676144</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01782447023727982</v>
+        <v>0.01782447023727983</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01704308986310624</v>
+        <v>0.01704308986310625</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01776264397156777</v>
+        <v>0.01776264397156778</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01776264397156777</v>
+        <v>0.01776264397156778</v>
       </c>
       <c r="J3" t="n">
         <v>0.01775952781134177</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01779490442034312</v>
+        <v>0.01779490442034313</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01776264397156777</v>
+        <v>0.01776264397156778</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01776264397156777</v>
+        <v>0.01776264397156778</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01776264397156777</v>
+        <v>0.01776264397156778</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01776264397156777</v>
+        <v>0.01776264397156778</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01776264397156777</v>
+        <v>0.01776264397156778</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01776264397156777</v>
+        <v>0.01776264397156778</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01757843797697398</v>
+        <v>0.01757843797697399</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01776264397156777</v>
+        <v>0.01776264397156778</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01776264397156777</v>
+        <v>0.01776264397156778</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01776264397156777</v>
+        <v>0.01776264397156778</v>
       </c>
       <c r="V3" t="n">
-        <v>0.01731750350180655</v>
+        <v>0.01731750350180654</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01776264397156777</v>
+        <v>0.01776264397156778</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01749874300672141</v>
+        <v>0.01749874300672142</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01776264397156777</v>
+        <v>0.01776264397156778</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01776939133762664</v>
+        <v>0.01776939133762665</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.01776264397156777</v>
+        <v>0.01776264397156778</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0170608638451509</v>
+        <v>0.01706086384515091</v>
       </c>
     </row>
     <row r="4">
@@ -8014,10 +8014,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.07413724669773494</v>
+        <v>0.07413724669773503</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0611078840732011</v>
+        <v>0.06110788407320112</v>
       </c>
       <c r="D4" t="n">
         <v>0.06305949258538308</v>
@@ -8026,46 +8026,46 @@
         <v>0.1058838451117504</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0861222311226548</v>
+        <v>0.08612223112265492</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0501922719587421</v>
+        <v>0.05019227195874186</v>
       </c>
       <c r="H4" t="n">
-        <v>0.06161997028418821</v>
+        <v>0.0616199702841882</v>
       </c>
       <c r="I4" t="n">
         <v>0.05447563940068156</v>
       </c>
       <c r="J4" t="n">
-        <v>0.07151074218046809</v>
+        <v>0.07151074218046803</v>
       </c>
       <c r="K4" t="n">
-        <v>0.04614552500001957</v>
+        <v>0.04614552500001947</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09196036821582462</v>
+        <v>0.09196036821582466</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04230079502375788</v>
+        <v>0.04230079502375785</v>
       </c>
       <c r="N4" t="n">
-        <v>0.03869521221539229</v>
+        <v>0.03869521221539226</v>
       </c>
       <c r="O4" t="n">
-        <v>0.09958351895972122</v>
+        <v>0.09958351895972131</v>
       </c>
       <c r="P4" t="n">
-        <v>0.09103509997640358</v>
+        <v>0.09103509997640351</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.03883332282933022</v>
+        <v>0.03883332282933021</v>
       </c>
       <c r="R4" t="n">
         <v>0.1768418899450988</v>
       </c>
       <c r="S4" t="n">
-        <v>0.07778675699748841</v>
+        <v>0.0777867569974884</v>
       </c>
       <c r="T4" t="n">
         <v>0.04877940106612735</v>
@@ -8074,22 +8074,22 @@
         <v>0.03869521221539226</v>
       </c>
       <c r="V4" t="n">
-        <v>0.08313571822589585</v>
+        <v>0.08313571822589601</v>
       </c>
       <c r="W4" t="n">
         <v>0.1334838279738635</v>
       </c>
       <c r="X4" t="n">
-        <v>0.2799333159534979</v>
+        <v>0.2799333159534971</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.07831524531071395</v>
+        <v>0.07831524531071414</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.07923868615325669</v>
+        <v>0.07923868615325676</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.1308358244570748</v>
+        <v>0.1308358244570746</v>
       </c>
       <c r="AB4" t="n">
         <v>0.03778782997055292</v>
@@ -8102,85 +8102,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.008214719645630173</v>
+        <v>0.00821471964563021</v>
       </c>
       <c r="C5" t="n">
-        <v>0.008214719645630173</v>
+        <v>0.008214719645630211</v>
       </c>
       <c r="D5" t="n">
-        <v>0.008214719645630173</v>
+        <v>0.008214719645630211</v>
       </c>
       <c r="E5" t="n">
-        <v>0.008214719645630173</v>
+        <v>0.008214719645630211</v>
       </c>
       <c r="F5" t="n">
-        <v>0.008214719645630175</v>
+        <v>0.00821471964563021</v>
       </c>
       <c r="G5" t="n">
-        <v>0.008214719645630173</v>
+        <v>0.008214719645630211</v>
       </c>
       <c r="H5" t="n">
-        <v>0.008214719645630173</v>
+        <v>0.008214719645630211</v>
       </c>
       <c r="I5" t="n">
-        <v>0.008214719645630173</v>
+        <v>0.008214719645630211</v>
       </c>
       <c r="J5" t="n">
-        <v>0.00819723407999982</v>
+        <v>0.008197234079999827</v>
       </c>
       <c r="K5" t="n">
-        <v>0.008214719645630173</v>
+        <v>0.008214719645630211</v>
       </c>
       <c r="L5" t="n">
-        <v>0.008214719645630173</v>
+        <v>0.008214719645630211</v>
       </c>
       <c r="M5" t="n">
-        <v>0.008214719645630173</v>
+        <v>0.008214719645630211</v>
       </c>
       <c r="N5" t="n">
-        <v>0.008214719645630175</v>
+        <v>0.00821471964563021</v>
       </c>
       <c r="O5" t="n">
-        <v>0.008214719645630175</v>
+        <v>0.00821471964563021</v>
       </c>
       <c r="P5" t="n">
-        <v>0.008214719645630175</v>
+        <v>0.00821471964563021</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.008214719645630175</v>
+        <v>0.00821471964563021</v>
       </c>
       <c r="R5" t="n">
-        <v>0.008214719645630173</v>
+        <v>0.008214719645630211</v>
       </c>
       <c r="S5" t="n">
-        <v>0.008214719645630173</v>
+        <v>0.008214719645630211</v>
       </c>
       <c r="T5" t="n">
-        <v>0.008214719645630173</v>
+        <v>0.008214719645630211</v>
       </c>
       <c r="U5" t="n">
-        <v>0.008208781457858203</v>
+        <v>0.008208781457858215</v>
       </c>
       <c r="V5" t="n">
-        <v>0.008102497544417366</v>
+        <v>0.008102497544417385</v>
       </c>
       <c r="W5" t="n">
-        <v>0.008214719645630175</v>
+        <v>0.00821471964563021</v>
       </c>
       <c r="X5" t="n">
-        <v>0.008214719645630175</v>
+        <v>0.00821471964563021</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.008208781457858203</v>
+        <v>0.008208781457858215</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.008214719645630173</v>
+        <v>0.008214719645630211</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.008214719645630173</v>
+        <v>0.008214719645630211</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.008214719645630175</v>
+        <v>0.00821471964563021</v>
       </c>
     </row>
     <row r="6">
@@ -8190,85 +8190,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01957727390775909</v>
+        <v>0.01957727390775907</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01957727390775909</v>
+        <v>0.01957727390775907</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01957727390775909</v>
+        <v>0.01957727390775907</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01957727390775909</v>
+        <v>0.01957727390775907</v>
       </c>
       <c r="F6" t="n">
-        <v>0.013010055609359</v>
+        <v>0.01957727390775907</v>
       </c>
       <c r="G6" t="n">
-        <v>0.013010055609359</v>
+        <v>0.01957727390775907</v>
       </c>
       <c r="H6" t="n">
-        <v>0.013010055609359</v>
+        <v>0.01301005560935899</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01957727390775909</v>
+        <v>0.01301005560935899</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01955978834212875</v>
+        <v>0.01299257004372864</v>
       </c>
       <c r="K6" t="n">
-        <v>0.013010055609359</v>
+        <v>0.01957727390775907</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01957727390775909</v>
+        <v>0.01957727390775907</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01957727390775909</v>
+        <v>0.01957727390775907</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01299644965795931</v>
+        <v>0.01299644965795926</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0129964496579592</v>
+        <v>0.01948745585944375</v>
       </c>
       <c r="P6" t="n">
         <v>0.01948740151776925</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01957727390775909</v>
+        <v>0.01957727390775907</v>
       </c>
       <c r="R6" t="n">
-        <v>0.01957727390775909</v>
+        <v>0.01301005560935899</v>
       </c>
       <c r="S6" t="n">
-        <v>0.013010055609359</v>
+        <v>0.01301005560935899</v>
       </c>
       <c r="T6" t="n">
-        <v>0.01957727390775909</v>
+        <v>0.01957727390775907</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01957727390775909</v>
+        <v>0.01957727390775907</v>
       </c>
       <c r="V6" t="n">
         <v>0.01289783350814618</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0194875002020398</v>
+        <v>0.01948750020203979</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01957727390775909</v>
+        <v>0.01301005560935899</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01334808849088139</v>
+        <v>0.01334808849088136</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.01957727390775909</v>
+        <v>0.01301005560935899</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.01957727390775909</v>
+        <v>0.01301005560935899</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.01298377251702279</v>
+        <v>0.01298377251702278</v>
       </c>
     </row>
     <row r="7">
@@ -8278,85 +8278,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01151495666081854</v>
+        <v>0.01151495666081853</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01151495666081854</v>
+        <v>0.01151495666081853</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01151495666081854</v>
+        <v>0.01151495666081853</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01151495666081854</v>
+        <v>0.01151495666081853</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01151495666081854</v>
+        <v>0.01151495666081853</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01151495666081854</v>
+        <v>0.01151495666081853</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01151495666081854</v>
+        <v>0.01151495666081853</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01151495666081854</v>
+        <v>0.01151495666081853</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01149747109518817</v>
+        <v>0.01149747109518816</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01151495666081854</v>
+        <v>0.01151495666081853</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01151495666081854</v>
+        <v>0.01151495666081853</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01151495666081854</v>
+        <v>0.01151495666081853</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01151495666081854</v>
+        <v>0.01151495666081853</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01151427867330905</v>
+        <v>0.01151427867330904</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01151427867330905</v>
+        <v>0.01151427867330904</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.01151495666081854</v>
+        <v>0.01151495666081853</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01151495666081854</v>
+        <v>0.01151495666081853</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01151495666081854</v>
+        <v>0.01151495666081853</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01151495666081854</v>
+        <v>0.01151495666081853</v>
       </c>
       <c r="U7" t="n">
         <v>0.01150866737755336</v>
       </c>
       <c r="V7" t="n">
-        <v>0.01140273455960573</v>
+        <v>0.01140273455960572</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01151495666081854</v>
+        <v>0.01151495666081853</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01151495666081854</v>
+        <v>0.01151495666081853</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01151495666081854</v>
+        <v>0.01151495666081853</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.01151495666081854</v>
+        <v>0.01151495666081853</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01151495666081854</v>
+        <v>0.01151495666081853</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01151495666081854</v>
+        <v>0.01151495666081853</v>
       </c>
     </row>
     <row r="8">
@@ -8366,85 +8366,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01779519981029914</v>
+        <v>0.01779519981029912</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02595823634683826</v>
+        <v>0.0259582363468382</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02595823634683826</v>
+        <v>0.0259582363468382</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02595823634683826</v>
+        <v>0.02161166018579446</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01906690549915344</v>
+        <v>0.01906690549915346</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02595823634683826</v>
+        <v>0.02765089514987265</v>
       </c>
       <c r="H8" t="n">
-        <v>0.02595823634683826</v>
+        <v>0.0259582363468382</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02595823634683826</v>
+        <v>0.0259582363468382</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0259407507812079</v>
+        <v>0.02594075078120782</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02595823634683826</v>
+        <v>0.0259582363468382</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02595823634683826</v>
+        <v>0.0259582363468382</v>
       </c>
       <c r="M8" t="n">
-        <v>0.02595823634683826</v>
+        <v>0.02595823634683661</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01963051738453072</v>
+        <v>0.0196305173845307</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02136942949762978</v>
+        <v>0.02136942949762979</v>
       </c>
       <c r="P8" t="n">
-        <v>0.02094318012074424</v>
+        <v>0.02094318012074416</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01619097681884402</v>
+        <v>0.01619097681884399</v>
       </c>
       <c r="R8" t="n">
-        <v>0.02595823634683826</v>
+        <v>0.0259582363468382</v>
       </c>
       <c r="S8" t="n">
-        <v>0.02595823634683826</v>
+        <v>0.0259582363468382</v>
       </c>
       <c r="T8" t="n">
-        <v>0.02595823634683826</v>
+        <v>0.0259582363468382</v>
       </c>
       <c r="U8" t="n">
-        <v>0.02093104540710463</v>
+        <v>0.02196961854722809</v>
       </c>
       <c r="V8" t="n">
-        <v>0.02584601424562542</v>
+        <v>0.02361013687932551</v>
       </c>
       <c r="W8" t="n">
-        <v>0.02595984061659785</v>
+        <v>0.02595984061659778</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01693913533712715</v>
+        <v>0.01693913533712712</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.03406711855464589</v>
+        <v>0.03406711855464575</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.02595823634683826</v>
+        <v>0.01764356721576789</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.02595823634683826</v>
+        <v>0.0259582363468382</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.03448521059054856</v>
+        <v>0.03448521059054853</v>
       </c>
     </row>
     <row r="9">
@@ -8454,85 +8454,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02048034072311511</v>
+        <v>0.0204803407231151</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02477591710257009</v>
+        <v>0.0247759171025701</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02477591710257009</v>
+        <v>0.0247759171025701</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02477591710257009</v>
+        <v>0.0237845184126068</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02477591710257009</v>
+        <v>0.01487343639356361</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02477591710257009</v>
+        <v>0.0247759207648988</v>
       </c>
       <c r="H9" t="n">
-        <v>0.02477591710257009</v>
+        <v>0.0247759171025701</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02477591710257009</v>
+        <v>0.0247759171025701</v>
       </c>
       <c r="J9" t="n">
-        <v>0.02475843153693974</v>
+        <v>0.02475843153693973</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02477591710257009</v>
+        <v>0.0247759171025701</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02477591710257009</v>
+        <v>0.0247759171025701</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02477591710257009</v>
+        <v>0.0247759171025701</v>
       </c>
       <c r="N9" t="n">
-        <v>0.02477591710257009</v>
+        <v>0.0247759171025701</v>
       </c>
       <c r="O9" t="n">
-        <v>0.02619947036616475</v>
+        <v>0.02619947036616477</v>
       </c>
       <c r="P9" t="n">
         <v>0.02650906798044145</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.02477592076489881</v>
+        <v>0.0247759207648988</v>
       </c>
       <c r="R9" t="n">
-        <v>0.02477591710257009</v>
+        <v>0.0247759171025701</v>
       </c>
       <c r="S9" t="n">
-        <v>0.02477591710257009</v>
+        <v>0.0247759171025701</v>
       </c>
       <c r="T9" t="n">
-        <v>0.02477591710257009</v>
+        <v>0.0247759171025701</v>
       </c>
       <c r="U9" t="n">
-        <v>0.02477591710257009</v>
+        <v>0.0247759171025701</v>
       </c>
       <c r="V9" t="n">
-        <v>0.02466369500135728</v>
+        <v>0.02962070155683096</v>
       </c>
       <c r="W9" t="n">
-        <v>0.02477591710257009</v>
+        <v>0.0247759171025701</v>
       </c>
       <c r="X9" t="n">
-        <v>0.02477591710257009</v>
+        <v>0.0247759171025701</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.02477591710257009</v>
+        <v>0.0247759171025701</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.02477591710257009</v>
+        <v>0.02218606797758427</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.02477591710257009</v>
+        <v>0.0247759171025701</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.02477591710257009</v>
+        <v>0.0247759171025701</v>
       </c>
     </row>
     <row r="10">
@@ -8542,46 +8542,46 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01609928069334999</v>
+        <v>0.01609928069335</v>
       </c>
       <c r="C10" t="n">
         <v>0.01664663924889348</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01651809900977636</v>
+        <v>0.01651809900977635</v>
       </c>
       <c r="E10" t="n">
-        <v>0.02889507752457083</v>
+        <v>0.02889507752457078</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0160975850240339</v>
+        <v>0.01609758502403391</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01597454098172406</v>
+        <v>0.01597454098172405</v>
       </c>
       <c r="H10" t="n">
-        <v>0.01663162724030481</v>
+        <v>0.0166316272403048</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01675189348701901</v>
+        <v>0.016751893487019</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01620658444205457</v>
+        <v>0.01620658444205456</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0169265943561279</v>
+        <v>0.01692659435612791</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01553062365807974</v>
+        <v>0.01553062365807975</v>
       </c>
       <c r="M10" t="n">
-        <v>0.01701396867760671</v>
+        <v>0.01701396867760672</v>
       </c>
       <c r="N10" t="n">
         <v>0.01636481020839359</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0153662373573396</v>
+        <v>0.01536623735733959</v>
       </c>
       <c r="P10" t="n">
         <v>0.01560678830454107</v>
@@ -8590,34 +8590,34 @@
         <v>0.01704981666319625</v>
       </c>
       <c r="R10" t="n">
-        <v>0.01390108315348667</v>
+        <v>0.01390108315348668</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01596599897778155</v>
+        <v>0.01596599897778154</v>
       </c>
       <c r="T10" t="n">
-        <v>0.01686392237625841</v>
+        <v>0.0168639223762584</v>
       </c>
       <c r="U10" t="n">
         <v>0.0170180541255371</v>
       </c>
       <c r="V10" t="n">
-        <v>0.01539258481069313</v>
+        <v>0.01539258481069311</v>
       </c>
       <c r="W10" t="n">
         <v>0.01474557566996719</v>
       </c>
       <c r="X10" t="n">
-        <v>0.01083472028987215</v>
+        <v>0.01083472028987217</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.01616697159752313</v>
+        <v>0.01616697159752314</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.01586404190853554</v>
+        <v>0.01586404190853555</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.0149281927843736</v>
+        <v>0.01492819278437361</v>
       </c>
       <c r="AB10" t="n">
         <v>0.01644581786609485</v>
@@ -8630,7 +8630,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.01687474344129035</v>
+        <v>0.01687474344129033</v>
       </c>
       <c r="C11" t="n">
         <v>0.01711138675639078</v>
@@ -8639,13 +8639,13 @@
         <v>0.017014904950521</v>
       </c>
       <c r="E11" t="n">
-        <v>0.03006478206836876</v>
+        <v>0.03006478206836873</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0169357344392086</v>
+        <v>0.01693573443920859</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01640466200575598</v>
+        <v>0.01640466200575597</v>
       </c>
       <c r="H11" t="n">
         <v>0.01711696281664258</v>
@@ -8654,13 +8654,13 @@
         <v>0.01717168434216334</v>
       </c>
       <c r="J11" t="n">
-        <v>0.01692186902606373</v>
+        <v>0.01692186902606374</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01726597570444328</v>
+        <v>0.01726597570444326</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01661600267803994</v>
+        <v>0.01661600267803995</v>
       </c>
       <c r="M11" t="n">
         <v>0.01715636388053349</v>
@@ -8669,46 +8669,46 @@
         <v>0.01697031695502128</v>
       </c>
       <c r="O11" t="n">
-        <v>0.01654120638733511</v>
+        <v>0.01654120638733509</v>
       </c>
       <c r="P11" t="n">
-        <v>0.01665065783490218</v>
+        <v>0.01665065783490217</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.01730724033674879</v>
+        <v>0.01730724033674878</v>
       </c>
       <c r="R11" t="n">
-        <v>0.01579003882831185</v>
+        <v>0.01579003882831184</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01681409983596309</v>
+        <v>0.01681409983596307</v>
       </c>
       <c r="T11" t="n">
-        <v>0.01722265784378215</v>
+        <v>0.01722265784378214</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0172927882808927</v>
+        <v>0.01729278828089268</v>
       </c>
       <c r="V11" t="n">
-        <v>0.01637769557252935</v>
+        <v>0.01637769557252934</v>
       </c>
       <c r="W11" t="n">
-        <v>0.01625880334164923</v>
+        <v>0.01625880334164922</v>
       </c>
       <c r="X11" t="n">
-        <v>0.01435826820152963</v>
+        <v>0.01435826820152961</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.01690554301840726</v>
+        <v>0.01690554301840725</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.01682854192280462</v>
+        <v>0.01682854192280461</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.01634189471067037</v>
+        <v>0.01634189471067036</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.01671042675303337</v>
+        <v>0.01671042675303336</v>
       </c>
     </row>
   </sheetData>
@@ -8874,7 +8874,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01920499746563093</v>
+        <v>0.01920499746563092</v>
       </c>
       <c r="C2" t="n">
         <v>0.01833043091148915</v>
@@ -8886,70 +8886,70 @@
         <v>0.03103491127325134</v>
       </c>
       <c r="F2" t="n">
-        <v>0.018538612263024</v>
+        <v>0.01853861226302398</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01943897398285629</v>
+        <v>0.01943897398285628</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01920499746563093</v>
+        <v>0.01920499746563092</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01920499746563093</v>
+        <v>0.01920499746563092</v>
       </c>
       <c r="J2" t="n">
         <v>0.01915889754340052</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01922121013826434</v>
+        <v>0.01922121013826433</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01920499746563093</v>
+        <v>0.01920499746563092</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0199332899082563</v>
+        <v>0.01993328990825629</v>
       </c>
       <c r="N2" t="n">
         <v>0.019219970390484</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01920499746563093</v>
+        <v>0.01920499746563092</v>
       </c>
       <c r="P2" t="n">
-        <v>0.01920499746563093</v>
+        <v>0.01920499746563092</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.01920499746563093</v>
+        <v>0.01920499746563092</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0192080360244375</v>
+        <v>0.01920803602443749</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01920499746563093</v>
+        <v>0.01920499746563092</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01920499746563093</v>
+        <v>0.01920499746563092</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01920499746563093</v>
+        <v>0.01920499746563092</v>
       </c>
       <c r="V2" t="n">
         <v>0.01842681486587385</v>
       </c>
       <c r="W2" t="n">
-        <v>0.01920499746563093</v>
+        <v>0.01920499746563092</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01916092770045581</v>
+        <v>0.0191609277004558</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.01920499746563093</v>
+        <v>0.01920499746563092</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.01869517822521739</v>
+        <v>0.01869517822521738</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.01920499746563093</v>
+        <v>0.01920499746563092</v>
       </c>
       <c r="AB2" t="n">
         <v>0.01856369306546635</v>
@@ -8965,19 +8965,19 @@
         <v>0.01849550295737172</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01858688487346987</v>
+        <v>0.01858688487346986</v>
       </c>
       <c r="D3" t="n">
         <v>0.01849550295737172</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03127878197899846</v>
+        <v>0.03127878197899847</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01852851052363396</v>
+        <v>0.01852851052363395</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01814262768918489</v>
+        <v>0.01814262768918488</v>
       </c>
       <c r="H3" t="n">
         <v>0.01849550295737172</v>
@@ -9022,13 +9022,13 @@
         <v>0.01849550295737172</v>
       </c>
       <c r="V3" t="n">
-        <v>0.01849400472213223</v>
+        <v>0.01849400472213222</v>
       </c>
       <c r="W3" t="n">
         <v>0.01849550295737172</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01844727730468248</v>
+        <v>0.01844727730468247</v>
       </c>
       <c r="Y3" t="n">
         <v>0.01849550295737172</v>
@@ -9050,85 +9050,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1955295543246834</v>
+        <v>0.1955295543246831</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0553681198127573</v>
+        <v>0.05536811981275699</v>
       </c>
       <c r="D4" t="n">
-        <v>0.219888514675894</v>
+        <v>0.2198885146758938</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1069657163780598</v>
+        <v>0.1069657163780596</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1295381586355755</v>
+        <v>0.1295381586355751</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4216348980605836</v>
+        <v>0.4216348980605834</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1315405756487973</v>
+        <v>0.1315405756487969</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2225380146623716</v>
+        <v>0.2225380146623713</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2953746784025399</v>
+        <v>0.2953746784025401</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2876906328274511</v>
+        <v>0.2876906328274505</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4303970996531425</v>
+        <v>0.4303970996531421</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4961122236506604</v>
+        <v>0.4961122236506605</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3762439313441632</v>
+        <v>0.3762439313441646</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1702107720350092</v>
+        <v>0.1702107720350091</v>
       </c>
       <c r="P4" t="n">
-        <v>0.370119827272067</v>
+        <v>0.3701198272720658</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1516169636924246</v>
+        <v>0.1516169636924244</v>
       </c>
       <c r="R4" t="n">
         <v>0.1744830343614283</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2135288766586651</v>
+        <v>0.2135288766586645</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2136923242560253</v>
+        <v>0.213692324256025</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3762439313441632</v>
+        <v>0.3762439313441642</v>
       </c>
       <c r="V4" t="n">
-        <v>0.09606033383840056</v>
+        <v>0.09606033383840047</v>
       </c>
       <c r="W4" t="n">
-        <v>0.189125232945914</v>
+        <v>0.1891252329459135</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3753512336131289</v>
+        <v>0.3753512336131291</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.2795751621464594</v>
+        <v>0.2795751621464586</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.1627211858326273</v>
+        <v>0.162721185832627</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.2683939280691293</v>
+        <v>0.2683939280691287</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.6743625247862911</v>
+        <v>0.6743625247862901</v>
       </c>
     </row>
     <row r="5">
@@ -9138,85 +9138,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01025971082671174</v>
+        <v>0.01025971082671155</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01025971082671174</v>
+        <v>0.01025971082671155</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01025971082671174</v>
+        <v>0.01025971082671155</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01025971082671174</v>
+        <v>0.01025971082671155</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01025971082671174</v>
+        <v>0.01025971082671155</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01025971082671174</v>
+        <v>0.01025971082671155</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01025971082671174</v>
+        <v>0.01025971082671155</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01025971082671174</v>
+        <v>0.01025971082671155</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01023307692714116</v>
+        <v>0.01023307692714106</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01025971082671174</v>
+        <v>0.01025971082671155</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01025971082671174</v>
+        <v>0.01025971082671155</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01025971082671174</v>
+        <v>0.01025971082671155</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01025971082671174</v>
+        <v>0.01025971082671155</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01025971082671174</v>
+        <v>0.01025971082671155</v>
       </c>
       <c r="P5" t="n">
-        <v>0.01025971082671174</v>
+        <v>0.01025971082671155</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01025971082671174</v>
+        <v>0.01025971082671155</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01025971082671174</v>
+        <v>0.01025971082671155</v>
       </c>
       <c r="S5" t="n">
-        <v>0.01025971082671174</v>
+        <v>0.01025971082671155</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01025971082671174</v>
+        <v>0.01025971082671155</v>
       </c>
       <c r="U5" t="n">
-        <v>0.009993635198813385</v>
+        <v>0.009993635198813048</v>
       </c>
       <c r="V5" t="n">
         <v>0.01008907502383808</v>
       </c>
       <c r="W5" t="n">
-        <v>0.01025971082671174</v>
+        <v>0.01025971082671155</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01025971082671174</v>
+        <v>0.01025971082671155</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.009993635198813385</v>
+        <v>0.009993635198813048</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.01025971082671174</v>
+        <v>0.01025971082671155</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.01025971082671174</v>
+        <v>0.01025971082671155</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.01025971082671174</v>
+        <v>0.01025971082671155</v>
       </c>
     </row>
     <row r="6">
@@ -9226,85 +9226,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02227539796697084</v>
+        <v>0.02227539796697047</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01422302910021072</v>
+        <v>0.0142230291002105</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02227539796697084</v>
+        <v>0.02227539796697047</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02227539796697084</v>
+        <v>0.02227539796697047</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02227539796697084</v>
+        <v>0.02227539796697047</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01422302910021072</v>
+        <v>0.0142230291002105</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02227539796697084</v>
+        <v>0.02227539796697047</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01422302910021072</v>
+        <v>0.0142230291002105</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02224876406740002</v>
+        <v>0.01419639520064001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01422302910021072</v>
+        <v>0.0142230291002105</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01422302910021072</v>
+        <v>0.02227539796697047</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02227539796697084</v>
+        <v>0.02227539796697047</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01424997588616821</v>
+        <v>0.0142499758861679</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01424997588616818</v>
+        <v>0.0142499758861679</v>
       </c>
       <c r="P6" t="n">
-        <v>0.02227102327539121</v>
+        <v>0.02227102327539088</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01422302910021072</v>
+        <v>0.02227539796697047</v>
       </c>
       <c r="R6" t="n">
-        <v>0.02227539796697084</v>
+        <v>0.02227539796697047</v>
       </c>
       <c r="S6" t="n">
-        <v>0.02227539796697084</v>
+        <v>0.02227539796697047</v>
       </c>
       <c r="T6" t="n">
-        <v>0.02227539796697084</v>
+        <v>0.0142230291002105</v>
       </c>
       <c r="U6" t="n">
-        <v>0.02227539796697084</v>
+        <v>0.02227539796697047</v>
       </c>
       <c r="V6" t="n">
-        <v>0.01405239329733702</v>
+        <v>0.02210476216409698</v>
       </c>
       <c r="W6" t="n">
-        <v>0.01461448485765406</v>
+        <v>0.01461448485765375</v>
       </c>
       <c r="X6" t="n">
-        <v>0.02227539796697084</v>
+        <v>0.0142230291002105</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01452675126135089</v>
+        <v>0.01452675126135111</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.01422302910021072</v>
+        <v>0.0142230291002105</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.02227539796697084</v>
+        <v>0.02227539796697047</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.01438913767121211</v>
+        <v>0.01438913767121192</v>
       </c>
     </row>
     <row r="7">
@@ -9314,85 +9314,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01523236991453828</v>
+        <v>0.01523236991453799</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01523236991453828</v>
+        <v>0.01523236991453799</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01523236991453828</v>
+        <v>0.01523236991453799</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01523236991453828</v>
+        <v>0.01523236991453799</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01523236991453828</v>
+        <v>0.01523236991453799</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01523236991453828</v>
+        <v>0.01523236991453799</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01523236991453828</v>
+        <v>0.01523236991453799</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01523236991453828</v>
+        <v>0.01523236991453799</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01520573601496771</v>
+        <v>0.01520573601496751</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01523236991453828</v>
+        <v>0.01523236991453799</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01523236991453828</v>
+        <v>0.01523236991453799</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01523236991453828</v>
+        <v>0.01523236991453799</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01523236991453828</v>
+        <v>0.01523236991453799</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01523164829777733</v>
+        <v>0.01523164829777706</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01523164829777733</v>
+        <v>0.01523164829777706</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.01523236991453828</v>
+        <v>0.01523236991453799</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01523236991453828</v>
+        <v>0.01523236991453799</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01523236991453828</v>
+        <v>0.01523236991453799</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01523236991453828</v>
+        <v>0.01523236991453799</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01522329594328584</v>
+        <v>0.01522329594328536</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0150617341116645</v>
+        <v>0.01506173411166452</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01523236991453828</v>
+        <v>0.01523236991453799</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01523236991453828</v>
+        <v>0.01523236991453799</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01523236991453828</v>
+        <v>0.01523236991453799</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.01523236991453828</v>
+        <v>0.01523236991453799</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01523236991453828</v>
+        <v>0.01523236991453799</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01523236991453828</v>
+        <v>0.01523236991453799</v>
       </c>
     </row>
     <row r="8">
@@ -9402,85 +9402,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02230574513168129</v>
+        <v>0.02230574513168099</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03206649945136073</v>
+        <v>0.03206649945136034</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03206649945136073</v>
+        <v>0.03206649945136034</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03206649945136073</v>
+        <v>0.02686918570064498</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02382635657816953</v>
+        <v>0.02382635657816922</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03206649945136073</v>
+        <v>0.03409045544484722</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03206649945136073</v>
+        <v>0.03206649945136034</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03206649945136073</v>
+        <v>0.03206649945136034</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03203986555178993</v>
+        <v>0.03203986555178984</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03206649945136073</v>
+        <v>0.03206649945136034</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03206649945136073</v>
+        <v>0.03206649945136034</v>
       </c>
       <c r="M8" t="n">
-        <v>0.03206649945136073</v>
+        <v>0.03206649945135952</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02450028191461877</v>
+        <v>0.02450028191461839</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02657954418937472</v>
+        <v>0.02657954418937434</v>
       </c>
       <c r="P8" t="n">
-        <v>0.02606986676388649</v>
+        <v>0.02606986676388607</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.02038753412988337</v>
+        <v>0.02038753412988286</v>
       </c>
       <c r="R8" t="n">
-        <v>0.03206649945136073</v>
+        <v>0.03206649945136034</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03206649945136073</v>
+        <v>0.03206649945136034</v>
       </c>
       <c r="T8" t="n">
-        <v>0.03206649945136073</v>
+        <v>0.03206649945136034</v>
       </c>
       <c r="U8" t="n">
-        <v>0.02605416153470932</v>
+        <v>0.0272959326727275</v>
       </c>
       <c r="V8" t="n">
-        <v>0.03189586364848686</v>
+        <v>0.02922096293190351</v>
       </c>
       <c r="W8" t="n">
-        <v>0.03206841771786921</v>
+        <v>0.0320684177178688</v>
       </c>
       <c r="X8" t="n">
-        <v>0.02128212665734605</v>
+        <v>0.02128212665734576</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0417603221051203</v>
+        <v>0.04176032210512007</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.03206649945136073</v>
+        <v>0.02212443410912196</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.03206649945136073</v>
+        <v>0.03206649945136034</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.04226242351798815</v>
+        <v>0.04226242351798783</v>
       </c>
     </row>
     <row r="9">
@@ -9490,85 +9490,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0312953754325202</v>
+        <v>0.03129537543252017</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03802990499418232</v>
+        <v>0.03802990499418202</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03802990499418232</v>
+        <v>0.03802990499418202</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03802990499418232</v>
+        <v>0.03647560409871575</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03802990499418232</v>
+        <v>0.0225049745321906</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03802990499418232</v>
+        <v>0.03802990636926523</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03802990499418232</v>
+        <v>0.03802990499418202</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03802990499418232</v>
+        <v>0.03802990499418202</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03800327109461164</v>
+        <v>0.03800327109461152</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03802990499418232</v>
+        <v>0.03802990499418202</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03802990499418232</v>
+        <v>0.03802990499418202</v>
       </c>
       <c r="M9" t="n">
-        <v>0.03802990499418232</v>
+        <v>0.03802990499418202</v>
       </c>
       <c r="N9" t="n">
-        <v>0.03802990499418232</v>
+        <v>0.03802990499418202</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04026172110358796</v>
+        <v>0.04026172110358773</v>
       </c>
       <c r="P9" t="n">
-        <v>0.04074710251681023</v>
+        <v>0.04074710251681007</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03802990636926553</v>
+        <v>0.03802990636926523</v>
       </c>
       <c r="R9" t="n">
-        <v>0.03802990499418232</v>
+        <v>0.03802990499418202</v>
       </c>
       <c r="S9" t="n">
-        <v>0.03802990499418232</v>
+        <v>0.03802990499418202</v>
       </c>
       <c r="T9" t="n">
-        <v>0.03802990499418232</v>
+        <v>0.03802990499418202</v>
       </c>
       <c r="U9" t="n">
-        <v>0.03802990499418232</v>
+        <v>0.03802990499418202</v>
       </c>
       <c r="V9" t="n">
-        <v>0.03785926919130849</v>
+        <v>0.0456307655792737</v>
       </c>
       <c r="W9" t="n">
-        <v>0.03802990499418232</v>
+        <v>0.03802990499418202</v>
       </c>
       <c r="X9" t="n">
-        <v>0.03802990499418232</v>
+        <v>0.03802990499418202</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.03802990499418232</v>
+        <v>0.03802990499418202</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.03802990499418232</v>
+        <v>0.03396958307226469</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.03802990499418232</v>
+        <v>0.03802990499418202</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.03802990499418232</v>
+        <v>0.03802990499418202</v>
       </c>
     </row>
     <row r="10">
@@ -9584,79 +9584,79 @@
         <v>0.01766530872844068</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01420778992669994</v>
+        <v>0.01420778992669992</v>
       </c>
       <c r="E10" t="n">
-        <v>0.02912122434936729</v>
+        <v>0.0291212243493673</v>
       </c>
       <c r="F10" t="n">
         <v>0.016088122351968</v>
       </c>
       <c r="G10" t="n">
-        <v>0.00820301595618874</v>
+        <v>0.008203015956188733</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0161287196685879</v>
+        <v>0.01612871966858789</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01415931117344679</v>
+        <v>0.0141593111734468</v>
       </c>
       <c r="J10" t="n">
         <v>0.01185028902985529</v>
       </c>
       <c r="K10" t="n">
-        <v>0.01214388378098252</v>
+        <v>0.01214388378098253</v>
       </c>
       <c r="L10" t="n">
-        <v>0.008976417360339432</v>
+        <v>0.008976417360339434</v>
       </c>
       <c r="M10" t="n">
-        <v>0.007738067779990453</v>
+        <v>0.007738067779990461</v>
       </c>
       <c r="N10" t="n">
         <v>0.01184731017590263</v>
       </c>
       <c r="O10" t="n">
-        <v>0.01460706382645044</v>
+        <v>0.01460706382645045</v>
       </c>
       <c r="P10" t="n">
-        <v>0.01013812010113034</v>
+        <v>0.01013812010113035</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.01545836539639982</v>
+        <v>0.01545836539639981</v>
       </c>
       <c r="R10" t="n">
-        <v>0.01523560405400732</v>
+        <v>0.01523560405400731</v>
       </c>
       <c r="S10" t="n">
         <v>0.01352719993153447</v>
       </c>
       <c r="T10" t="n">
-        <v>0.01432753220198958</v>
+        <v>0.01432753220198957</v>
       </c>
       <c r="U10" t="n">
-        <v>0.01026903008509349</v>
+        <v>0.01026903008509347</v>
       </c>
       <c r="V10" t="n">
-        <v>0.01646720086567281</v>
+        <v>0.01646720086567282</v>
       </c>
       <c r="W10" t="n">
         <v>0.01464074039869773</v>
       </c>
       <c r="X10" t="n">
-        <v>0.01080491068062055</v>
+        <v>0.01080491068062052</v>
       </c>
       <c r="Y10" t="n">
         <v>0.01260622344150946</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.01492395989553985</v>
+        <v>0.01492395989553984</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.01291034783718609</v>
+        <v>0.01291034783718608</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.004738393495515716</v>
+        <v>0.004738393495515703</v>
       </c>
     </row>
     <row r="11">
@@ -9669,13 +9669,13 @@
         <v>0.01720490657944647</v>
       </c>
       <c r="C11" t="n">
-        <v>0.01791111082861195</v>
+        <v>0.01791111082861194</v>
       </c>
       <c r="D11" t="n">
         <v>0.01687085235309718</v>
       </c>
       <c r="E11" t="n">
-        <v>0.03005321567604094</v>
+        <v>0.03005321567604095</v>
       </c>
       <c r="F11" t="n">
         <v>0.01742822786786031</v>
@@ -9687,43 +9687,43 @@
         <v>0.01812810352674347</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0172320163853218</v>
+        <v>0.01723201638532179</v>
       </c>
       <c r="J11" t="n">
         <v>0.01615628203541388</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01632313078957409</v>
+        <v>0.01632313078957408</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01487378318345538</v>
+        <v>0.01487378318345539</v>
       </c>
       <c r="M11" t="n">
-        <v>0.01503862262063599</v>
+        <v>0.01503862262063598</v>
       </c>
       <c r="N11" t="n">
         <v>0.01619502148838224</v>
       </c>
       <c r="O11" t="n">
-        <v>0.01743574526934149</v>
+        <v>0.01743574526934148</v>
       </c>
       <c r="P11" t="n">
-        <v>0.0154023616326422</v>
+        <v>0.01540236163264221</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.0178230901966056</v>
+        <v>0.01782309019660559</v>
       </c>
       <c r="R11" t="n">
-        <v>0.01772325876825023</v>
+        <v>0.01772325876825022</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01694440375583268</v>
+        <v>0.01694440375583267</v>
       </c>
       <c r="T11" t="n">
-        <v>0.01730855748939737</v>
+        <v>0.01730855748939736</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0154619260925308</v>
+        <v>0.01546192609253079</v>
       </c>
       <c r="V11" t="n">
         <v>0.01750461265214419</v>
@@ -9732,10 +9732,10 @@
         <v>0.01745106821703487</v>
       </c>
       <c r="X11" t="n">
-        <v>0.01568362653173026</v>
+        <v>0.01568362653173025</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.01652535651789338</v>
+        <v>0.01652535651789337</v>
       </c>
       <c r="Z11" t="n">
         <v>0.0170682591223213</v>
@@ -9910,85 +9910,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01828704681804449</v>
+        <v>0.01828704681804451</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01789229921463118</v>
+        <v>0.01789229921463121</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01784972473676036</v>
+        <v>0.01784972473676034</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03062164356890778</v>
+        <v>0.0306216435689078</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01792881236265876</v>
+        <v>0.01792881236265879</v>
       </c>
       <c r="G2" t="n">
         <v>0.01864739882763469</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01828704681804449</v>
+        <v>0.01828704681804451</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01828704681804449</v>
+        <v>0.01828704681804451</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01824934499846663</v>
+        <v>0.01824934499846662</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01831004330754015</v>
+        <v>0.01831004330754018</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01828704681804449</v>
+        <v>0.01828704681804451</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01790087131162425</v>
+        <v>0.01790087131162428</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0179759554224638</v>
+        <v>0.01797595542246379</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01828704681804449</v>
+        <v>0.01828704681804451</v>
       </c>
       <c r="P2" t="n">
-        <v>0.01828704681804449</v>
+        <v>0.01828704681804451</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.01828704681804449</v>
+        <v>0.01828704681804451</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01819972333935349</v>
+        <v>0.01819972333935351</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01828704681804449</v>
+        <v>0.01828704681804451</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01828704681804449</v>
+        <v>0.01828704681804451</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01828704681804449</v>
+        <v>0.01828704681804451</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0177864720760253</v>
+        <v>0.01778647207602531</v>
       </c>
       <c r="W2" t="n">
-        <v>0.01828704681804449</v>
+        <v>0.01828704681804451</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01776101461205037</v>
+        <v>0.01776101461205039</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.01828704681804449</v>
+        <v>0.01828704681804451</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.01787166953232855</v>
+        <v>0.01787166953232858</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.01828704681804449</v>
+        <v>0.01828704681804451</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.01764574241787991</v>
+        <v>0.01764574241787993</v>
       </c>
     </row>
     <row r="3">
@@ -9998,85 +9998,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01802302438978641</v>
+        <v>0.01802302438978642</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01811899439578156</v>
+        <v>0.01811899439578157</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01802302438978641</v>
+        <v>0.01802302438978642</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03099886814630337</v>
+        <v>0.03099886814630333</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01806960876446516</v>
+        <v>0.01806960876446517</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01760361958641114</v>
+        <v>0.01760361958641115</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01802302438978641</v>
+        <v>0.01802302438978642</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01802302438978641</v>
+        <v>0.01802302438978642</v>
       </c>
       <c r="J3" t="n">
         <v>0.01798531827337071</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01804818933013595</v>
+        <v>0.01804818933013596</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01802302438978641</v>
+        <v>0.01802302438978642</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01802302438978641</v>
+        <v>0.01802302438978642</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01802302438978641</v>
+        <v>0.01802302438978642</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01802302438978641</v>
+        <v>0.01802302438978642</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01802302438978641</v>
+        <v>0.01802302438978642</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01802302438978641</v>
+        <v>0.01802302438978642</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01792746600510829</v>
+        <v>0.0179274660051083</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01802302438978641</v>
+        <v>0.01802302438978642</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01802302438978641</v>
+        <v>0.01802302438978642</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01802302438978641</v>
+        <v>0.01802302438978642</v>
       </c>
       <c r="V3" t="n">
         <v>0.01795395006015538</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01802302438978641</v>
+        <v>0.01802302438978642</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01744738673181472</v>
+        <v>0.01744738673181473</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01802302438978641</v>
+        <v>0.01802302438978642</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01802988185214936</v>
+        <v>0.01802988185214937</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.01802302438978641</v>
+        <v>0.01802302438978642</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01732124426336955</v>
+        <v>0.01732124426336956</v>
       </c>
     </row>
     <row r="4">
@@ -10086,85 +10086,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.033171374646726</v>
+        <v>0.03317137464672591</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0560198528335778</v>
+        <v>0.05601985283357771</v>
       </c>
       <c r="D4" t="n">
-        <v>0.06880736215891319</v>
+        <v>0.06880736215891312</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06500596216436216</v>
+        <v>0.06500596216436212</v>
       </c>
       <c r="F4" t="n">
-        <v>0.07805574906496826</v>
+        <v>0.07805574906496822</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3183343899137717</v>
+        <v>0.3183343899137694</v>
       </c>
       <c r="H4" t="n">
-        <v>0.07322448651639417</v>
+        <v>0.07322448651639381</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07390414640395171</v>
+        <v>0.07390414640395156</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1618376648796957</v>
+        <v>0.1618376648796953</v>
       </c>
       <c r="K4" t="n">
-        <v>0.09748030241344377</v>
+        <v>0.09748030241344376</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2200186617432983</v>
+        <v>0.2200186617432981</v>
       </c>
       <c r="M4" t="n">
-        <v>0.07905454434363991</v>
+        <v>0.07905454434363977</v>
       </c>
       <c r="N4" t="n">
-        <v>0.07687626569007135</v>
+        <v>0.07687626569007111</v>
       </c>
       <c r="O4" t="n">
-        <v>0.07176029001212655</v>
+        <v>0.07176029001212669</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2033672788813989</v>
+        <v>0.203367278881399</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.08126374581556089</v>
+        <v>0.08126374581556076</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1677291014501258</v>
+        <v>0.1677291014501256</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1075727973065991</v>
+        <v>0.1075727973065992</v>
       </c>
       <c r="T4" t="n">
-        <v>0.08067673013387545</v>
+        <v>0.08067673013387536</v>
       </c>
       <c r="U4" t="n">
-        <v>0.07687626569007136</v>
+        <v>0.07687626569007114</v>
       </c>
       <c r="V4" t="n">
         <v>0.06366510115256616</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1635293880889651</v>
+        <v>0.1635293880889648</v>
       </c>
       <c r="X4" t="n">
-        <v>0.2540371065671914</v>
+        <v>0.2540371065671909</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.329055209231597</v>
+        <v>0.3290552092315965</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.06491083999168887</v>
+        <v>0.06491083999168877</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.1016458145031216</v>
+        <v>0.1016458145031218</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.392574614701006</v>
+        <v>0.3925746147010051</v>
       </c>
     </row>
     <row r="5">
@@ -10174,85 +10174,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.00868689288836717</v>
+        <v>0.008686892888367079</v>
       </c>
       <c r="C5" t="n">
-        <v>0.008686892888367135</v>
+        <v>0.008686892888367079</v>
       </c>
       <c r="D5" t="n">
-        <v>0.008686892888367135</v>
+        <v>0.008686892888367079</v>
       </c>
       <c r="E5" t="n">
-        <v>0.008686892888367135</v>
+        <v>0.008686892888367079</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00868689288836717</v>
+        <v>0.008686892888367079</v>
       </c>
       <c r="G5" t="n">
-        <v>0.008686892888367135</v>
+        <v>0.008686892888367079</v>
       </c>
       <c r="H5" t="n">
-        <v>0.008686892888367135</v>
+        <v>0.008686892888367079</v>
       </c>
       <c r="I5" t="n">
-        <v>0.008686892888367135</v>
+        <v>0.008686892888367079</v>
       </c>
       <c r="J5" t="n">
-        <v>0.008662943320600382</v>
+        <v>0.00866294332060036</v>
       </c>
       <c r="K5" t="n">
-        <v>0.008686892888367135</v>
+        <v>0.008686892888367079</v>
       </c>
       <c r="L5" t="n">
-        <v>0.008686892888367135</v>
+        <v>0.008686892888367079</v>
       </c>
       <c r="M5" t="n">
-        <v>0.008686892888367135</v>
+        <v>0.008686892888367079</v>
       </c>
       <c r="N5" t="n">
-        <v>0.008686892888367171</v>
+        <v>0.008686892888367081</v>
       </c>
       <c r="O5" t="n">
-        <v>0.00868689288836717</v>
+        <v>0.008686892888367079</v>
       </c>
       <c r="P5" t="n">
-        <v>0.00868689288836717</v>
+        <v>0.008686892888367079</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.00868689288836717</v>
+        <v>0.008686892888367079</v>
       </c>
       <c r="R5" t="n">
-        <v>0.008686892888367135</v>
+        <v>0.008686892888367079</v>
       </c>
       <c r="S5" t="n">
-        <v>0.008686892888367135</v>
+        <v>0.008686892888367079</v>
       </c>
       <c r="T5" t="n">
-        <v>0.008686892888367135</v>
+        <v>0.008686892888367079</v>
       </c>
       <c r="U5" t="n">
-        <v>0.008461731384989705</v>
+        <v>0.008461731384989664</v>
       </c>
       <c r="V5" t="n">
-        <v>0.008533486666048484</v>
+        <v>0.008533486666048458</v>
       </c>
       <c r="W5" t="n">
-        <v>0.00868689288836717</v>
+        <v>0.008686892888367079</v>
       </c>
       <c r="X5" t="n">
-        <v>0.00868689288836717</v>
+        <v>0.008686892888367079</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.008461731384989705</v>
+        <v>0.008461731384989664</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.008686892888367135</v>
+        <v>0.008686892888367079</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.008686892888367135</v>
+        <v>0.008686892888367079</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.00868689288836717</v>
+        <v>0.008686892888367079</v>
       </c>
     </row>
     <row r="6">
@@ -10262,85 +10262,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01923412191978625</v>
+        <v>0.0122244276011787</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01923412191978625</v>
+        <v>0.01923412191978626</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01222442760117867</v>
+        <v>0.0122244276011787</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01222442760117867</v>
+        <v>0.01923412191978626</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01222442760117867</v>
+        <v>0.01923412191978626</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01923412191978625</v>
+        <v>0.0122244276011787</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01222442760117867</v>
+        <v>0.01923412191978626</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01222442760117867</v>
+        <v>0.01923412191978626</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01921017235201952</v>
+        <v>0.01220047803341197</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01222442760117867</v>
+        <v>0.01923412191978626</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01923412191978625</v>
+        <v>0.0122244276011787</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01222442760117867</v>
+        <v>0.01923412191978626</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01223121993820663</v>
+        <v>0.01223121993820645</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01922400663586975</v>
+        <v>0.01223121993820633</v>
       </c>
       <c r="P6" t="n">
-        <v>0.01186010290756567</v>
+        <v>0.01186010290756529</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01222442760117867</v>
+        <v>0.01923412191978626</v>
       </c>
       <c r="R6" t="n">
-        <v>0.01923412191978625</v>
+        <v>0.01923412191978626</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01222442760117867</v>
+        <v>0.0122244276011787</v>
       </c>
       <c r="T6" t="n">
-        <v>0.01222442760117867</v>
+        <v>0.0122244276011787</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01923412191978625</v>
+        <v>0.0122244276011787</v>
       </c>
       <c r="V6" t="n">
-        <v>0.01908071569746765</v>
+        <v>0.01908071569746764</v>
       </c>
       <c r="W6" t="n">
-        <v>0.01258201148841865</v>
+        <v>0.01258201148841858</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01923412191978625</v>
+        <v>0.0122244276011787</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01248388944182069</v>
+        <v>0.01248388944182103</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.01222442760117867</v>
+        <v>0.0122244276011787</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.01923412191978625</v>
+        <v>0.01923412191978626</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.01232280353482656</v>
+        <v>0.01232280353482649</v>
       </c>
     </row>
     <row r="7">
@@ -10350,85 +10350,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01277705610029654</v>
+        <v>0.01277705610029644</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01277705610029654</v>
+        <v>0.01277705610029644</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01277705610029654</v>
+        <v>0.01277705610029644</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01277705610029654</v>
+        <v>0.01277705610029644</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01277705610029654</v>
+        <v>0.01277705610029644</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01277705610029654</v>
+        <v>0.01277705610029644</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01277705610029654</v>
+        <v>0.01277705610029644</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01277705610029654</v>
+        <v>0.01277705610029644</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01275310653252967</v>
+        <v>0.01275310653252971</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01277705610029654</v>
+        <v>0.01277705610029644</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01277705610029654</v>
+        <v>0.01277705610029644</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01277705610029654</v>
+        <v>0.01277705610029644</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01277705610029654</v>
+        <v>0.01277705610029644</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01277638799335708</v>
+        <v>0.01277638799335706</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01277638799335708</v>
+        <v>0.01277638799335706</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.01277705610029654</v>
+        <v>0.01277705610029644</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01277705610029654</v>
+        <v>0.01277705610029644</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01277705610029654</v>
+        <v>0.01277705610029644</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01277705610029654</v>
+        <v>0.01277705610029644</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0127673650408735</v>
+        <v>0.01276736504087348</v>
       </c>
       <c r="V7" t="n">
-        <v>0.01262364987797779</v>
+        <v>0.01262364987797783</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01277705610029654</v>
+        <v>0.01277705610029644</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01277705610029654</v>
+        <v>0.01277705610029644</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01277705610029654</v>
+        <v>0.01277705610029644</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.01277705610029654</v>
+        <v>0.01277705610029644</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01277705610029654</v>
+        <v>0.01277705610029644</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01277705610029654</v>
+        <v>0.01277705610029644</v>
       </c>
     </row>
     <row r="8">
@@ -10438,85 +10438,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0189733013832428</v>
+        <v>0.01897330138324279</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02738262015890744</v>
+        <v>0.02738262015890742</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02738262015890744</v>
+        <v>0.02738262015890742</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02738262015890744</v>
+        <v>0.0229049059704882</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02028337496655985</v>
+        <v>0.02028337496655987</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02738262015890744</v>
+        <v>0.02912634718857215</v>
       </c>
       <c r="H8" t="n">
-        <v>0.02738262015890744</v>
+        <v>0.02738262015890742</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02738262015890744</v>
+        <v>0.02738262015890742</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0273586705911407</v>
+        <v>0.02735867059114069</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02738262015890744</v>
+        <v>0.02738262015890742</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02738262015890744</v>
+        <v>0.02738262015890742</v>
       </c>
       <c r="M8" t="n">
-        <v>0.02738262015890744</v>
+        <v>0.02738262015890655</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02086399125906949</v>
+        <v>0.02086399125906957</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02265536708044353</v>
+        <v>0.02265536708044351</v>
       </c>
       <c r="P8" t="n">
-        <v>0.02221625758098001</v>
+        <v>0.02221625758098006</v>
       </c>
       <c r="Q8" t="n">
         <v>0.01732067831080504</v>
       </c>
       <c r="R8" t="n">
-        <v>0.02738262015890744</v>
+        <v>0.02738262015890742</v>
       </c>
       <c r="S8" t="n">
-        <v>0.02738262015890744</v>
+        <v>0.02738262015890742</v>
       </c>
       <c r="T8" t="n">
-        <v>0.02738262015890744</v>
+        <v>0.02738262015890742</v>
       </c>
       <c r="U8" t="n">
-        <v>0.02220139732163502</v>
+        <v>0.02327115133503495</v>
       </c>
       <c r="V8" t="n">
-        <v>0.02722921393658884</v>
+        <v>0.02492310772091875</v>
       </c>
       <c r="W8" t="n">
-        <v>0.02738427282980421</v>
+        <v>0.02738427282980419</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01809140908543442</v>
+        <v>0.01809140908543443</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.03573185216163299</v>
+        <v>0.035731852161633</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.02738262015890744</v>
+        <v>0.01881709396972834</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.02738262015890744</v>
+        <v>0.02738262015890742</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.03616685679478601</v>
+        <v>0.03616685679478603</v>
       </c>
     </row>
     <row r="9">
@@ -10526,85 +10526,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02504677259476617</v>
+        <v>0.02504677259476618</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03038660335368815</v>
+        <v>0.03038660335368809</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03038660335368815</v>
+        <v>0.03038660335368809</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03038660335368815</v>
+        <v>0.02915419561764657</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03038660335368815</v>
+        <v>0.01807683026886503</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03038660335368815</v>
+        <v>0.0303866078028908</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03038660335368815</v>
+        <v>0.03038660335368809</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03038660335368815</v>
+        <v>0.03038660335368809</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0303626537859214</v>
+        <v>0.03036265378592135</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03038660335368815</v>
+        <v>0.03038660335368809</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03038660335368815</v>
+        <v>0.03038660335368809</v>
       </c>
       <c r="M9" t="n">
-        <v>0.03038660335368815</v>
+        <v>0.03038660335368809</v>
       </c>
       <c r="N9" t="n">
-        <v>0.03038660335368815</v>
+        <v>0.03038660335368809</v>
       </c>
       <c r="O9" t="n">
-        <v>0.03215622219894656</v>
+        <v>0.03215622219894654</v>
       </c>
       <c r="P9" t="n">
-        <v>0.03254108296861821</v>
+        <v>0.03254108296861816</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03038660780289078</v>
+        <v>0.0303866078028908</v>
       </c>
       <c r="R9" t="n">
-        <v>0.03038660335368815</v>
+        <v>0.03038660335368809</v>
       </c>
       <c r="S9" t="n">
-        <v>0.03038660335368815</v>
+        <v>0.03038660335368809</v>
       </c>
       <c r="T9" t="n">
-        <v>0.03038660335368815</v>
+        <v>0.03038660335368809</v>
       </c>
       <c r="U9" t="n">
-        <v>0.03038660335368815</v>
+        <v>0.03038660335368809</v>
       </c>
       <c r="V9" t="n">
-        <v>0.03023319713136947</v>
+        <v>0.03639525094333672</v>
       </c>
       <c r="W9" t="n">
-        <v>0.03038660335368815</v>
+        <v>0.03038660335368809</v>
       </c>
       <c r="X9" t="n">
-        <v>0.03038660335368815</v>
+        <v>0.03038660335368809</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.03038660335368815</v>
+        <v>0.03038660335368809</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.03038660335368815</v>
+        <v>0.02716716200906519</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.03038660335368815</v>
+        <v>0.03038660335368809</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.03038660335368815</v>
+        <v>0.03038660335368809</v>
       </c>
     </row>
     <row r="10">
@@ -10623,34 +10623,34 @@
         <v>0.0166883326546973</v>
       </c>
       <c r="E10" t="n">
-        <v>0.02963931717252558</v>
+        <v>0.02963931717252551</v>
       </c>
       <c r="F10" t="n">
         <v>0.01652860865097585</v>
       </c>
       <c r="G10" t="n">
-        <v>0.009226995736769774</v>
+        <v>0.009226995736769866</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0166916537426942</v>
+        <v>0.01669165374269417</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0166169680894529</v>
+        <v>0.01661696808945294</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01404293941470157</v>
+        <v>0.01404293941470156</v>
       </c>
       <c r="K10" t="n">
-        <v>0.01586257212738357</v>
+        <v>0.01586257212738355</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01257939011155747</v>
+        <v>0.01257939011155749</v>
       </c>
       <c r="M10" t="n">
         <v>0.01639497046455463</v>
       </c>
       <c r="N10" t="n">
-        <v>0.01594012616160762</v>
+        <v>0.01594012616160763</v>
       </c>
       <c r="O10" t="n">
         <v>0.01639816120892229</v>
@@ -10659,40 +10659,40 @@
         <v>0.01305548472701954</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.01625358851561299</v>
+        <v>0.01625358851561301</v>
       </c>
       <c r="R10" t="n">
-        <v>0.01451835608419313</v>
+        <v>0.01451835608419314</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0154352218347928</v>
+        <v>0.01543522183479279</v>
       </c>
       <c r="T10" t="n">
-        <v>0.01644254230438171</v>
+        <v>0.01644254230438169</v>
       </c>
       <c r="U10" t="n">
-        <v>0.01633460097472327</v>
+        <v>0.01633460097472329</v>
       </c>
       <c r="V10" t="n">
         <v>0.01655793678913524</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0144449940157586</v>
+        <v>0.01444499401575859</v>
       </c>
       <c r="X10" t="n">
         <v>0.01175566483188926</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.0105087770632358</v>
+        <v>0.01050877706323579</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.01658253232287544</v>
+        <v>0.01658253232287545</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.01588755282802139</v>
+        <v>0.01588755282802143</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.009035695042513042</v>
+        <v>0.009035695042513033</v>
       </c>
     </row>
     <row r="11">
@@ -10702,85 +10702,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.01802187286541697</v>
+        <v>0.01802187286541698</v>
       </c>
       <c r="C11" t="n">
         <v>0.01740470978962471</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01724243574388464</v>
+        <v>0.01724243574388463</v>
       </c>
       <c r="E11" t="n">
         <v>0.03000304354320706</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01722765240014517</v>
+        <v>0.01722765240014514</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01483600828133162</v>
+        <v>0.01483600828133163</v>
       </c>
       <c r="H11" t="n">
-        <v>0.01768126893079102</v>
+        <v>0.01768126893079104</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01764728672055727</v>
+        <v>0.01764728672055723</v>
       </c>
       <c r="J11" t="n">
-        <v>0.01645555005415623</v>
+        <v>0.0164555500541562</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01731558051513913</v>
+        <v>0.01731558051513907</v>
       </c>
       <c r="L11" t="n">
         <v>0.01581017587361724</v>
       </c>
       <c r="M11" t="n">
-        <v>0.01716010158734385</v>
+        <v>0.01716010158734383</v>
       </c>
       <c r="N11" t="n">
-        <v>0.01702823009083968</v>
+        <v>0.01702823009083967</v>
       </c>
       <c r="O11" t="n">
-        <v>0.01754772889261963</v>
+        <v>0.01754772889261962</v>
       </c>
       <c r="P11" t="n">
-        <v>0.01602680044087599</v>
+        <v>0.01602680044087598</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.01748194785643802</v>
+        <v>0.01748194785643805</v>
       </c>
       <c r="R11" t="n">
         <v>0.01664856746114841</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01710958840868499</v>
+        <v>0.017109588408685</v>
       </c>
       <c r="T11" t="n">
-        <v>0.01756792243248783</v>
+        <v>0.01756792243248782</v>
       </c>
       <c r="U11" t="n">
-        <v>0.01751880878350461</v>
+        <v>0.01751880878350464</v>
       </c>
       <c r="V11" t="n">
-        <v>0.01715128158888082</v>
+        <v>0.01715128158888083</v>
       </c>
       <c r="W11" t="n">
         <v>0.01665903159535562</v>
       </c>
       <c r="X11" t="n">
-        <v>0.01517126300914283</v>
+        <v>0.01517126300914284</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.01486804033797859</v>
+        <v>0.0148680403379786</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.01721312088407966</v>
+        <v>0.01721312088407968</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.01731540045209734</v>
+        <v>0.01731540045209738</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.01387579111791152</v>
+        <v>0.01387579111791153</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Hydrogen/hydrogen eutrophication terrestrial results.xlsx
+++ b/Results/Phase 2/Hydrogen/hydrogen eutrophication terrestrial results.xlsx
@@ -886,7 +886,7 @@
         <v>0.007738556275496514</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3892300692142192</v>
+        <v>0.007738556275496528</v>
       </c>
       <c r="O5" t="n">
         <v>0.007738556275496528</v>
@@ -974,7 +974,7 @@
         <v>0.02037047208349062</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3892300692142192</v>
+        <v>0.01216151944370902</v>
       </c>
       <c r="O6" t="n">
         <v>0.01216150393273123</v>
@@ -1062,7 +1062,7 @@
         <v>0.01323506933257146</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3892300692142192</v>
+        <v>0.01323506933257146</v>
       </c>
       <c r="O7" t="n">
         <v>0.01323429123443886</v>
@@ -1150,7 +1150,7 @@
         <v>0.03163853068047922</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3892300692142192</v>
+        <v>0.02338284211932033</v>
       </c>
       <c r="O8" t="n">
         <v>0.0256515770182097</v>
@@ -1238,7 +1238,7 @@
         <v>0.03807914589549045</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3892300692142192</v>
+        <v>0.03807914589549045</v>
       </c>
       <c r="O9" t="n">
         <v>0.04050957592697839</v>
@@ -1922,7 +1922,7 @@
         <v>0.006278975565530445</v>
       </c>
       <c r="N5" t="n">
-        <v>0.07486350105476881</v>
+        <v>0.006278975565530439</v>
       </c>
       <c r="O5" t="n">
         <v>0.006278975565530439</v>
@@ -2010,7 +2010,7 @@
         <v>0.009859094838372589</v>
       </c>
       <c r="N6" t="n">
-        <v>0.07486350105476881</v>
+        <v>0.009908946493945161</v>
       </c>
       <c r="O6" t="n">
         <v>0.01602246205768336</v>
@@ -2098,7 +2098,7 @@
         <v>0.01001817530289031</v>
       </c>
       <c r="N7" t="n">
-        <v>0.07486350105476881</v>
+        <v>0.01001817530289031</v>
       </c>
       <c r="O7" t="n">
         <v>0.01001751489508947</v>
@@ -2186,7 +2186,7 @@
         <v>0.02356364611223218</v>
       </c>
       <c r="N8" t="n">
-        <v>0.07486350105476881</v>
+        <v>0.01755290875391476</v>
       </c>
       <c r="O8" t="n">
         <v>0.01920471156993938</v>
@@ -2274,7 +2274,7 @@
         <v>0.02264387314092671</v>
       </c>
       <c r="N9" t="n">
-        <v>0.07486350105476881</v>
+        <v>0.02264387314092671</v>
       </c>
       <c r="O9" t="n">
         <v>0.02401071117984667</v>
@@ -2958,7 +2958,7 @@
         <v>0.006942856248202741</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2579550597110485</v>
+        <v>0.006942856248202731</v>
       </c>
       <c r="O5" t="n">
         <v>0.006942856248202731</v>
@@ -3046,7 +3046,7 @@
         <v>0.01797611009234184</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2579550597110485</v>
+        <v>0.01074115773161201</v>
       </c>
       <c r="O6" t="n">
         <v>0.01072496567792875</v>
@@ -3134,7 +3134,7 @@
         <v>0.01176341016517467</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2579550597110485</v>
+        <v>0.01176341016517467</v>
       </c>
       <c r="O7" t="n">
         <v>0.01176269958729963</v>
@@ -3222,7 +3222,7 @@
         <v>0.02819838809474075</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2579550597110485</v>
+        <v>0.02085092508361365</v>
       </c>
       <c r="O8" t="n">
         <v>0.02287007171541515</v>
@@ -3310,7 +3310,7 @@
         <v>0.03129031456049004</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2579550597110485</v>
+        <v>0.03129031456049004</v>
       </c>
       <c r="O9" t="n">
         <v>0.03326381951690533</v>
@@ -3694,7 +3694,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01843966047627447</v>
+        <v>0.01843966047627445</v>
       </c>
       <c r="C2" t="n">
         <v>0.01806408486760887</v>
@@ -3703,76 +3703,76 @@
         <v>0.01871590207914622</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03083567900973541</v>
+        <v>0.0308356790097354</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01822866081073087</v>
+        <v>0.01822866081073086</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01824310405546205</v>
+        <v>0.01824310405546204</v>
       </c>
       <c r="H2" t="n">
         <v>0.01804108708753787</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01868695935603017</v>
+        <v>0.01868695935603016</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01865682137381931</v>
+        <v>0.0186568213738193</v>
       </c>
       <c r="K2" t="n">
         <v>0.01887570486802135</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01852643637664726</v>
+        <v>0.01852643637664725</v>
       </c>
       <c r="M2" t="n">
-        <v>0.02034024728917725</v>
+        <v>0.02034024728917723</v>
       </c>
       <c r="N2" t="n">
         <v>0.01836791889196171</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01835132295312825</v>
+        <v>0.01835132295312823</v>
       </c>
       <c r="P2" t="n">
-        <v>0.01867533456207076</v>
+        <v>0.01867533456207075</v>
       </c>
       <c r="Q2" t="n">
         <v>0.01818477743857088</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01795338370189449</v>
+        <v>0.01795338370189448</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01858590062578324</v>
+        <v>0.01858590062578322</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01848440331495848</v>
+        <v>0.01848440331495845</v>
       </c>
       <c r="U2" t="n">
         <v>0.01863942360260042</v>
       </c>
       <c r="V2" t="n">
-        <v>0.01820210560694322</v>
+        <v>0.01820210560694323</v>
       </c>
       <c r="W2" t="n">
-        <v>0.01859957617349577</v>
+        <v>0.01859957617349576</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01814778621419415</v>
+        <v>0.01814778621419417</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.01886753080939607</v>
+        <v>0.01886753080939608</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.01825226922055413</v>
+        <v>0.01825226922055412</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.01879086679906091</v>
+        <v>0.01879086679906092</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0185962763275576</v>
+        <v>0.01859627632755761</v>
       </c>
     </row>
     <row r="3">
@@ -3782,85 +3782,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01817786422568066</v>
+        <v>0.01817786422568064</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01827383423167581</v>
+        <v>0.01827383423167579</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01817786422568066</v>
+        <v>0.01817786422568064</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03107021345110365</v>
+        <v>0.03107021345110369</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01822444860035941</v>
+        <v>0.01822444860035939</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01775845942230539</v>
+        <v>0.01775845942230538</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01817786422568066</v>
+        <v>0.01817786422568064</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01817786422568066</v>
+        <v>0.01817786422568064</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01815700831786115</v>
+        <v>0.01815700831786114</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0182030291660302</v>
+        <v>0.01820302916603019</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01817786422568066</v>
+        <v>0.01817786422568064</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01817786422568066</v>
+        <v>0.01817786422568064</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01817786422568066</v>
+        <v>0.01817786422568064</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01817786422568066</v>
+        <v>0.01817786422568064</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01817786422568066</v>
+        <v>0.01817786422568064</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01817786422568066</v>
+        <v>0.01817786422568064</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01808230584100254</v>
+        <v>0.01808230584100252</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01817786422568066</v>
+        <v>0.01817786422568064</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01817786422568066</v>
+        <v>0.01817786422568064</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01817786422568066</v>
+        <v>0.01817786422568064</v>
       </c>
       <c r="V3" t="n">
         <v>0.01817898390749697</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01817786422568066</v>
+        <v>0.01817786422568064</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01760222656770896</v>
+        <v>0.01760222656770895</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01817786422568066</v>
+        <v>0.01817786422568064</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01818472168804361</v>
+        <v>0.0181847216880436</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.01817786422568066</v>
+        <v>0.01817786422568064</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01747608409926379</v>
+        <v>0.01747608409926378</v>
       </c>
     </row>
     <row r="4">
@@ -3870,85 +3870,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1665995135667725</v>
+        <v>0.1665995135667729</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05985029388940107</v>
+        <v>0.05985029388940096</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2560893254856331</v>
+        <v>0.2560893254856332</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1001641120108674</v>
+        <v>0.100164112010867</v>
       </c>
       <c r="F4" t="n">
         <v>0.1165361274228701</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2094389035011884</v>
+        <v>0.2094389035011887</v>
       </c>
       <c r="H4" t="n">
-        <v>0.08265158721142839</v>
+        <v>0.08265158721142832</v>
       </c>
       <c r="I4" t="n">
-        <v>0.252462991892225</v>
+        <v>0.2524629918922245</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2340868225655787</v>
+        <v>0.2340868225655786</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2613966842130224</v>
+        <v>0.2613966842130225</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1969518570297039</v>
+        <v>0.1969518570297002</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6932655167888997</v>
+        <v>0.6932655167888981</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1620204503010221</v>
+        <v>0.1620204503010219</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1389657296779609</v>
+        <v>0.1389657296779612</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2209640598734967</v>
+        <v>0.2209640598734966</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1126838872719958</v>
+        <v>0.1126838872719956</v>
       </c>
       <c r="R4" t="n">
-        <v>0.08108431887963138</v>
+        <v>0.08108431887963133</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2014420710340212</v>
+        <v>0.2014420710340205</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1971907070980643</v>
+        <v>0.1971907070980645</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2192021206777227</v>
+        <v>0.219202120677725</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1058626312179047</v>
+        <v>0.1058626312179051</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2179752118430451</v>
+        <v>0.2179752118430448</v>
       </c>
       <c r="X4" t="n">
-        <v>0.2417863876390815</v>
+        <v>0.2417863876390825</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.2834129962022781</v>
+        <v>0.2834129962022783</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.1153100669357403</v>
+        <v>0.11531006693574</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.2666318150242095</v>
+        <v>0.2666318150242092</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.4174738706390657</v>
+        <v>0.4174738706390654</v>
       </c>
     </row>
     <row r="5">
@@ -3958,85 +3958,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.006734954302457764</v>
+        <v>0.006734954302457743</v>
       </c>
       <c r="C5" t="n">
-        <v>0.006734954302457775</v>
+        <v>0.006734954302457725</v>
       </c>
       <c r="D5" t="n">
-        <v>0.006734954302457775</v>
+        <v>0.006734954302457725</v>
       </c>
       <c r="E5" t="n">
-        <v>0.006734954302457775</v>
+        <v>0.006734954302457725</v>
       </c>
       <c r="F5" t="n">
-        <v>0.006734954302457766</v>
+        <v>0.006734954302457737</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006734954302457775</v>
+        <v>0.006734954302457725</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006734954302457775</v>
+        <v>0.006734954302457725</v>
       </c>
       <c r="I5" t="n">
-        <v>0.006734954302457775</v>
+        <v>0.006734954302457725</v>
       </c>
       <c r="J5" t="n">
-        <v>0.006714389458779873</v>
+        <v>0.006714389458779843</v>
       </c>
       <c r="K5" t="n">
-        <v>0.006734954302457775</v>
+        <v>0.006734954302457725</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006734954302457775</v>
+        <v>0.006734954302457731</v>
       </c>
       <c r="M5" t="n">
-        <v>0.006734954302457775</v>
+        <v>0.006734954302457725</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1620204503010221</v>
+        <v>0.006734954302457737</v>
       </c>
       <c r="O5" t="n">
-        <v>0.006734954302457766</v>
+        <v>0.006734954302457737</v>
       </c>
       <c r="P5" t="n">
-        <v>0.006734954302457766</v>
+        <v>0.006734954302457737</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.006734954302457766</v>
+        <v>0.006734954302457737</v>
       </c>
       <c r="R5" t="n">
-        <v>0.006734954302457775</v>
+        <v>0.006734954302457725</v>
       </c>
       <c r="S5" t="n">
-        <v>0.006734954302457775</v>
+        <v>0.006734954302457725</v>
       </c>
       <c r="T5" t="n">
-        <v>0.006734954302457775</v>
+        <v>0.006734954302457725</v>
       </c>
       <c r="U5" t="n">
-        <v>0.00636952102920595</v>
+        <v>0.006369521029205914</v>
       </c>
       <c r="V5" t="n">
-        <v>0.006603195736642915</v>
+        <v>0.006603195736642906</v>
       </c>
       <c r="W5" t="n">
-        <v>0.006734954302457766</v>
+        <v>0.006734954302457737</v>
       </c>
       <c r="X5" t="n">
-        <v>0.006734954302457764</v>
+        <v>0.006734954302457743</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.00636952102920595</v>
+        <v>0.006369521029205914</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.006734954302457775</v>
+        <v>0.006734954302457725</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.006734954302457775</v>
+        <v>0.006734954302457725</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.006734954302457766</v>
+        <v>0.006734954302457737</v>
       </c>
     </row>
     <row r="6">
@@ -4046,85 +4046,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01723658556972025</v>
+        <v>0.01723658556972018</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01050510023534867</v>
+        <v>0.0105051002353486</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01723658556972025</v>
+        <v>0.01723658556972018</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01723658556972025</v>
+        <v>0.01723658556972018</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01050510023534867</v>
+        <v>0.0105051002353486</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01050510023534867</v>
+        <v>0.0105051002353486</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01050510023534867</v>
+        <v>0.0105051002353486</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01050510023534867</v>
+        <v>0.0105051002353486</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01721602072604232</v>
+        <v>0.01721602072604229</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01723658556972025</v>
+        <v>0.01723658556972018</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01723658556972025</v>
+        <v>0.01723658556972018</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01050510023534867</v>
+        <v>0.0105051002353486</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1620204503010221</v>
+        <v>0.01054953203152929</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01722946961036453</v>
+        <v>0.01722946961036447</v>
       </c>
       <c r="P6" t="n">
-        <v>0.01723807741588351</v>
+        <v>0.01723807741588344</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01723658556972025</v>
+        <v>0.01723658556972018</v>
       </c>
       <c r="R6" t="n">
-        <v>0.01050510023534867</v>
+        <v>0.0105051002353486</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01723658556972025</v>
+        <v>0.01723658556972018</v>
       </c>
       <c r="T6" t="n">
-        <v>0.01050510023534867</v>
+        <v>0.0105051002353486</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01050510023534867</v>
+        <v>0.0105051002353486</v>
       </c>
       <c r="V6" t="n">
-        <v>0.01710482700390539</v>
+        <v>0.01710482700390537</v>
       </c>
       <c r="W6" t="n">
-        <v>0.01722823612290983</v>
+        <v>0.01722823612290976</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01050510023534867</v>
+        <v>0.0105051002353486</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01081023306227066</v>
+        <v>0.01081023306227079</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.01723658556972025</v>
+        <v>0.01723658556972018</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.01723658556972025</v>
+        <v>0.01723658556972018</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.01055402455758045</v>
+        <v>0.01055402455758042</v>
       </c>
     </row>
     <row r="7">
@@ -4134,85 +4134,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01110859874681177</v>
+        <v>0.01110859874681176</v>
       </c>
       <c r="C7" t="n">
+        <v>0.01110859874681175</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.01110859874681175</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.01110859874681175</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.01110859874681175</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.01110859874681175</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.01110859874681175</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.01110859874681175</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.01108803390313387</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.01110859874681175</v>
+      </c>
+      <c r="L7" t="n">
         <v>0.01110859874681176</v>
       </c>
-      <c r="D7" t="n">
+      <c r="M7" t="n">
+        <v>0.01110859874681175</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.01110859874681175</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.01110793324877873</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.01110793324877873</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.01110859874681175</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.01110859874681175</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.01110859874681175</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.01110859874681175</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.01110067081738605</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.01097684018099695</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.01110859874681175</v>
+      </c>
+      <c r="X7" t="n">
         <v>0.01110859874681176</v>
       </c>
-      <c r="E7" t="n">
-        <v>0.01110859874681176</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.01110859874681176</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.01110859874681176</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.01110859874681176</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.01110859874681176</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.01108803390313392</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.01110859874681176</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.01110859874681177</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.01110859874681176</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.1620204503010221</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.01110793324877876</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0.01110793324877876</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.01110859874681176</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.01110859874681176</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.01110859874681176</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.01110859874681176</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0.01110067081738608</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0.01097684018099694</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0.01110859874681176</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0.01110859874681177</v>
-      </c>
       <c r="Y7" t="n">
-        <v>0.01110859874681176</v>
+        <v>0.01110859874681175</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.01110859874681176</v>
+        <v>0.01110859874681175</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01110859874681176</v>
+        <v>0.01110859874681175</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01110859874681176</v>
+        <v>0.01110859874681175</v>
       </c>
     </row>
     <row r="8">
@@ -4225,82 +4225,82 @@
         <v>0.01748450504839125</v>
       </c>
       <c r="C8" t="n">
+        <v>0.02614309181803775</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.02614309181803775</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.0215326497757568</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.01883341167192005</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.02793850619009531</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.02614309181803775</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.02614309181803775</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.02612252697435984</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.02614309181803775</v>
+      </c>
+      <c r="L8" t="n">
         <v>0.02614309181803776</v>
       </c>
-      <c r="D8" t="n">
-        <v>0.02614309181803776</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.02153264977575682</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.01883341167192008</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.02793850619009535</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.02614309181803776</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.02614309181803776</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.02612252697435986</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.02614309181803776</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.02614309181803777</v>
-      </c>
       <c r="M8" t="n">
-        <v>0.02614309181804119</v>
+        <v>0.02614309181804117</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1620204503010221</v>
+        <v>0.01943123852125363</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02127571408468237</v>
+        <v>0.02127571408468233</v>
       </c>
       <c r="P8" t="n">
-        <v>0.02082358855536987</v>
+        <v>0.02082358855536982</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01578289512585195</v>
+        <v>0.01578289512585191</v>
       </c>
       <c r="R8" t="n">
-        <v>0.02614309181803776</v>
+        <v>0.02614309181803775</v>
       </c>
       <c r="S8" t="n">
-        <v>0.02614309181803776</v>
+        <v>0.02614309181803775</v>
       </c>
       <c r="T8" t="n">
-        <v>0.02614309181803776</v>
+        <v>0.02614309181803775</v>
       </c>
       <c r="U8" t="n">
-        <v>0.02191132297391313</v>
+        <v>0.02191132297391314</v>
       </c>
       <c r="V8" t="n">
         <v>0.02363860318517256</v>
       </c>
       <c r="W8" t="n">
-        <v>0.02614479347730412</v>
+        <v>0.02614479347730407</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01657647180747469</v>
+        <v>0.01657647180747471</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.03474249933757517</v>
+        <v>0.03474249933757519</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.01732366735390653</v>
+        <v>0.01732366735390652</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.02614309181803776</v>
+        <v>0.02614309181803775</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.03518770971715153</v>
+        <v>0.03518770971715154</v>
       </c>
     </row>
     <row r="9">
@@ -4310,85 +4310,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02248893689020759</v>
+        <v>0.02248893689020752</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02764162162254149</v>
+        <v>0.0276416216225414</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02764162162254149</v>
+        <v>0.0276416216225414</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02645240068996089</v>
+        <v>0.02645240068996085</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01576328093970223</v>
+        <v>0.01576328093970219</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02764161861452828</v>
+        <v>0.02764161861452822</v>
       </c>
       <c r="H9" t="n">
-        <v>0.02764162162254149</v>
+        <v>0.0276416216225414</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02764162162254149</v>
+        <v>0.0276416216225414</v>
       </c>
       <c r="J9" t="n">
-        <v>0.02762105677886358</v>
+        <v>0.02762105677886354</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02764162162254149</v>
+        <v>0.0276416216225414</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02764162162254148</v>
+        <v>0.02764162162254141</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02764162162254149</v>
+        <v>0.0276416216225414</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1620204503010221</v>
+        <v>0.0276416216225414</v>
       </c>
       <c r="O9" t="n">
-        <v>0.02934921059110819</v>
+        <v>0.02934921059110814</v>
       </c>
       <c r="P9" t="n">
-        <v>0.02972058254866928</v>
+        <v>0.02972058254866924</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.02764161861452828</v>
+        <v>0.02764161861452822</v>
       </c>
       <c r="R9" t="n">
-        <v>0.02764162162254149</v>
+        <v>0.0276416216225414</v>
       </c>
       <c r="S9" t="n">
-        <v>0.02764162162254149</v>
+        <v>0.0276416216225414</v>
       </c>
       <c r="T9" t="n">
-        <v>0.02764162162254149</v>
+        <v>0.0276416216225414</v>
       </c>
       <c r="U9" t="n">
-        <v>0.02764162162254149</v>
+        <v>0.0276416216225414</v>
       </c>
       <c r="V9" t="n">
-        <v>0.03345593787159764</v>
+        <v>0.03345593787159765</v>
       </c>
       <c r="W9" t="n">
-        <v>0.02764162162254149</v>
+        <v>0.0276416216225414</v>
       </c>
       <c r="X9" t="n">
-        <v>0.02764162162254148</v>
+        <v>0.02764162162254141</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.02764162162254149</v>
+        <v>0.0276416216225414</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.02453500972909939</v>
+        <v>0.02453500972909932</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.02764162162254149</v>
+        <v>0.0276416216225414</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.02764162162254149</v>
+        <v>0.0276416216225414</v>
       </c>
     </row>
     <row r="10">
@@ -4398,85 +4398,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0142036440797179</v>
+        <v>0.01420364407971787</v>
       </c>
       <c r="C10" t="n">
-        <v>0.01707320253494407</v>
+        <v>0.01707320253494408</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01264688673737688</v>
+        <v>0.01264688673737687</v>
       </c>
       <c r="E10" t="n">
-        <v>0.02884491732156675</v>
+        <v>0.02884491732156677</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01580874171335402</v>
+        <v>0.01580874171335401</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01267632338678722</v>
+        <v>0.01267632338678719</v>
       </c>
       <c r="H10" t="n">
-        <v>0.01661033375302408</v>
+        <v>0.01661033375302409</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01282647004655907</v>
+        <v>0.01282647004655906</v>
       </c>
       <c r="J10" t="n">
         <v>0.01281552343529359</v>
       </c>
       <c r="K10" t="n">
-        <v>0.01186171652957095</v>
+        <v>0.01186171652957094</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01371562691719326</v>
+        <v>0.01371562691719327</v>
       </c>
       <c r="M10" t="n">
-        <v>0.003189359422817675</v>
+        <v>0.003189359422817663</v>
       </c>
       <c r="N10" t="n">
         <v>0.01467040111716646</v>
       </c>
       <c r="O10" t="n">
-        <v>0.01472541535473372</v>
+        <v>0.0147254153547337</v>
       </c>
       <c r="P10" t="n">
-        <v>0.01279092754565154</v>
+        <v>0.01279092754565153</v>
       </c>
       <c r="Q10" t="n">
         <v>0.01575175859140508</v>
       </c>
       <c r="R10" t="n">
-        <v>0.01651254384704997</v>
+        <v>0.01651254384704996</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01334861582895751</v>
+        <v>0.01334861582895749</v>
       </c>
       <c r="T10" t="n">
-        <v>0.01400555383535715</v>
+        <v>0.01400555383535711</v>
       </c>
       <c r="U10" t="n">
-        <v>0.01304253555091788</v>
+        <v>0.01304253555091787</v>
       </c>
       <c r="V10" t="n">
-        <v>0.01561914093429197</v>
+        <v>0.01561914093429198</v>
       </c>
       <c r="W10" t="n">
-        <v>0.01329141519538995</v>
+        <v>0.01329141519538996</v>
       </c>
       <c r="X10" t="n">
-        <v>0.01231266294606379</v>
+        <v>0.0123126629460638</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.01172041049666567</v>
+        <v>0.01172041049666565</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.01536574047817552</v>
+        <v>0.01536574047817553</v>
       </c>
       <c r="AA10" t="n">
         <v>0.01216731876331816</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.008891317849324218</v>
+        <v>0.008891317849324207</v>
       </c>
     </row>
     <row r="11">
@@ -4486,19 +4486,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.01663137764477328</v>
+        <v>0.01663137764477327</v>
       </c>
       <c r="C11" t="n">
         <v>0.01751779361940973</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01619928969578862</v>
+        <v>0.01619928969578861</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02982316217919809</v>
+        <v>0.02982316217919807</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01712950647874233</v>
+        <v>0.01712950647874234</v>
       </c>
       <c r="G11" t="n">
         <v>0.0159307159634947</v>
@@ -4507,64 +4507,64 @@
         <v>0.01732785572705592</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01625205795064851</v>
+        <v>0.0162520579506485</v>
       </c>
       <c r="J11" t="n">
-        <v>0.01622642872994878</v>
+        <v>0.01622642872994877</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0159903874098681</v>
+        <v>0.01599038740986809</v>
       </c>
       <c r="L11" t="n">
         <v>0.01649610418097896</v>
       </c>
       <c r="M11" t="n">
-        <v>0.01352042983834392</v>
+        <v>0.01352042983834389</v>
       </c>
       <c r="N11" t="n">
         <v>0.01677201199996606</v>
       </c>
       <c r="O11" t="n">
-        <v>0.01678044771454566</v>
+        <v>0.01678044771454567</v>
       </c>
       <c r="P11" t="n">
-        <v>0.01622426120550894</v>
+        <v>0.01622426120550891</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.01708089164343558</v>
+        <v>0.01708089164343557</v>
       </c>
       <c r="R11" t="n">
-        <v>0.01723913699211143</v>
+        <v>0.01723913699211142</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01638857721537272</v>
+        <v>0.01638857721537271</v>
       </c>
       <c r="T11" t="n">
-        <v>0.01658598879099698</v>
+        <v>0.01658598879099697</v>
       </c>
       <c r="U11" t="n">
         <v>0.0163028326902619</v>
       </c>
       <c r="V11" t="n">
-        <v>0.01703736889639941</v>
+        <v>0.01703736889639942</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0163762262925244</v>
+        <v>0.01637622629252439</v>
       </c>
       <c r="X11" t="n">
         <v>0.01574101790950655</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.01592936878401023</v>
+        <v>0.01592936878401022</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.01696962378650407</v>
+        <v>0.01696962378650409</v>
       </c>
       <c r="AA11" t="n">
         <v>0.01605604945921412</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.01469018032580836</v>
+        <v>0.01469018032580835</v>
       </c>
     </row>
   </sheetData>
@@ -4730,43 +4730,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01762239989738098</v>
+        <v>0.017622399897381</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01731753261255506</v>
+        <v>0.01731753261255507</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01768200885641893</v>
+        <v>0.01768200885641896</v>
       </c>
       <c r="E2" t="n">
         <v>0.03062852580250826</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01757907873318697</v>
+        <v>0.01757907873318698</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01716590563294717</v>
+        <v>0.01716590563294721</v>
       </c>
       <c r="H2" t="n">
         <v>0.01731153201609974</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01790327828556246</v>
+        <v>0.01790327828556248</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01788361607381407</v>
+        <v>0.01788361607381408</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01834369721162101</v>
+        <v>0.01834369721162104</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01771815504140869</v>
+        <v>0.0177181550414087</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01918450875844273</v>
+        <v>0.01918450875844275</v>
       </c>
       <c r="N2" t="n">
-        <v>0.01744490669521729</v>
+        <v>0.01744490669521731</v>
       </c>
       <c r="O2" t="n">
         <v>0.01759880744155701</v>
@@ -4775,40 +4775,40 @@
         <v>0.01785273788939891</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.01743998133968592</v>
+        <v>0.01743998133968593</v>
       </c>
       <c r="R2" t="n">
         <v>0.01728810671140729</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01781121978136952</v>
+        <v>0.01781121978136956</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01781679569728533</v>
+        <v>0.01781679569728534</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01790696014044505</v>
+        <v>0.01790696014044508</v>
       </c>
       <c r="V2" t="n">
-        <v>0.01723241078188191</v>
+        <v>0.01723241078188193</v>
       </c>
       <c r="W2" t="n">
-        <v>0.01757980958257282</v>
+        <v>0.01757980958257283</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0177877118319243</v>
+        <v>0.01778771183192432</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.01866857513324999</v>
+        <v>0.01866857513325</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.01746516512445054</v>
+        <v>0.01746516512445055</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.01814801837438519</v>
+        <v>0.01814801837438521</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.01775452853334218</v>
+        <v>0.01775452853334221</v>
       </c>
     </row>
     <row r="3">
@@ -4818,85 +4818,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01744373108442671</v>
+        <v>0.01744373108442673</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0175393259199082</v>
+        <v>0.01753932591990823</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01744373108442671</v>
+        <v>0.01744373108442673</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03098066099373961</v>
+        <v>0.03098066099373967</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01750555735013876</v>
+        <v>0.01750555735013878</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01672417697596518</v>
+        <v>0.0167241769759652</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01744373108442671</v>
+        <v>0.01744373108442673</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01744373108442671</v>
+        <v>0.01744373108442673</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01743400221880709</v>
+        <v>0.0174340022188071</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01747599153320207</v>
+        <v>0.01747599153320209</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01744373108442671</v>
+        <v>0.01744373108442673</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01744373108442671</v>
+        <v>0.01744373108442673</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01744373108442671</v>
+        <v>0.01744373108442673</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01744373108442671</v>
+        <v>0.01744373108442673</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01744373108442671</v>
+        <v>0.01744373108442673</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01744373108442671</v>
+        <v>0.01744373108442673</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01725952508983292</v>
+        <v>0.01725952508983294</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01744373108442671</v>
+        <v>0.01744373108442673</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01744373108442671</v>
+        <v>0.01744373108442673</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01744373108442671</v>
+        <v>0.01744373108442673</v>
       </c>
       <c r="V3" t="n">
-        <v>0.01701364122718831</v>
+        <v>0.01701364122718824</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01744373108442671</v>
+        <v>0.01744373108442673</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01717983011958036</v>
+        <v>0.01717983011958038</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01744373108442671</v>
+        <v>0.01744373108442673</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01745047845048559</v>
+        <v>0.01745047845048561</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.01744373108442671</v>
+        <v>0.01744373108442673</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01674195095800985</v>
+        <v>0.01674195095800987</v>
       </c>
     </row>
     <row r="4">
@@ -4906,85 +4906,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1399372496974125</v>
+        <v>0.1399372496974131</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05370805588126101</v>
+        <v>0.05370805588126099</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1678341069407991</v>
+        <v>0.1678341069407994</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06712877328715511</v>
+        <v>0.06712877328715526</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1307744397865629</v>
+        <v>0.1307744397865625</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1845792613242023</v>
+        <v>0.1845792613242021</v>
       </c>
       <c r="H4" t="n">
-        <v>0.08080361365968562</v>
+        <v>0.08080361365968565</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2319993009225904</v>
+        <v>0.2319993009225903</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2131784730620099</v>
+        <v>0.2131784730620093</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3043742299011616</v>
+        <v>0.3043742299011623</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1692753038458072</v>
+        <v>0.1692753038458074</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5529520382147534</v>
+        <v>0.5529520382147532</v>
       </c>
       <c r="N4" t="n">
         <v>0.1104477977541437</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1323941148608755</v>
+        <v>0.1323941148608754</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1909495656709616</v>
+        <v>0.1909495656709609</v>
       </c>
       <c r="Q4" t="n">
         <v>0.1046526511497114</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1185393392254004</v>
+        <v>0.1185393392254005</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1865582555024014</v>
+        <v>0.1865582555024015</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2119377539279918</v>
+        <v>0.2119377539279922</v>
       </c>
       <c r="U4" t="n">
-        <v>0.209483231970671</v>
+        <v>0.2094832319706712</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1439854235502203</v>
+        <v>0.1439854235502196</v>
       </c>
       <c r="W4" t="n">
-        <v>0.14270584123838</v>
+        <v>0.1427058412383798</v>
       </c>
       <c r="X4" t="n">
-        <v>0.2539158144512678</v>
+        <v>0.2539158144512672</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4231474580196702</v>
+        <v>0.4231474580196703</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.09622990687941266</v>
+        <v>0.09622990687941291</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.2883983330478464</v>
+        <v>0.2883983330478462</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3785741787206806</v>
+        <v>0.3785741787206801</v>
       </c>
     </row>
     <row r="5">
@@ -4994,85 +4994,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.006845399105523116</v>
+        <v>0.006845399105523189</v>
       </c>
       <c r="C5" t="n">
-        <v>0.006845399105523104</v>
+        <v>0.006845399105523203</v>
       </c>
       <c r="D5" t="n">
-        <v>0.006845399105523104</v>
+        <v>0.006845399105523203</v>
       </c>
       <c r="E5" t="n">
-        <v>0.006845399105523104</v>
+        <v>0.006845399105523203</v>
       </c>
       <c r="F5" t="n">
-        <v>0.006845399105523102</v>
+        <v>0.006845399105523147</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006845399105523104</v>
+        <v>0.006845399105523203</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006845399105523104</v>
+        <v>0.006845399105523203</v>
       </c>
       <c r="I5" t="n">
-        <v>0.006845399105523104</v>
+        <v>0.006845399105523203</v>
       </c>
       <c r="J5" t="n">
-        <v>0.006826487868110796</v>
+        <v>0.006826487868110827</v>
       </c>
       <c r="K5" t="n">
-        <v>0.006845399105523104</v>
+        <v>0.006845399105523203</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006845399105523113</v>
+        <v>0.006845399105523209</v>
       </c>
       <c r="M5" t="n">
-        <v>0.006845399105523104</v>
+        <v>0.006845399105523203</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1104477977541437</v>
+        <v>0.006845399105523147</v>
       </c>
       <c r="O5" t="n">
-        <v>0.006845399105523102</v>
+        <v>0.006845399105523147</v>
       </c>
       <c r="P5" t="n">
-        <v>0.006845399105523102</v>
+        <v>0.006845399105523147</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.006845399105523102</v>
+        <v>0.006845399105523147</v>
       </c>
       <c r="R5" t="n">
-        <v>0.006845399105523104</v>
+        <v>0.006845399105523203</v>
       </c>
       <c r="S5" t="n">
-        <v>0.006845399105523104</v>
+        <v>0.006845399105523203</v>
       </c>
       <c r="T5" t="n">
-        <v>0.006845399105523104</v>
+        <v>0.006845399105523203</v>
       </c>
       <c r="U5" t="n">
-        <v>0.006577077188610428</v>
+        <v>0.0065770771886105</v>
       </c>
       <c r="V5" t="n">
-        <v>0.006724043408628817</v>
+        <v>0.006724043408628733</v>
       </c>
       <c r="W5" t="n">
-        <v>0.006845399105523102</v>
+        <v>0.006845399105523147</v>
       </c>
       <c r="X5" t="n">
-        <v>0.006845399105523117</v>
+        <v>0.006845399105523148</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.006577077188610428</v>
+        <v>0.0065770771886105</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.006845399105523104</v>
+        <v>0.006845399105523203</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.006845399105523104</v>
+        <v>0.006845399105523203</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.006845399105523102</v>
+        <v>0.006845399105523147</v>
       </c>
     </row>
     <row r="6">
@@ -5088,10 +5088,10 @@
         <v>0.01072625145824839</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01741454243533127</v>
+        <v>0.01741454243533141</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01741454243533127</v>
+        <v>0.01741454243533141</v>
       </c>
       <c r="F6" t="n">
         <v>0.01072625145824839</v>
@@ -5100,16 +5100,16 @@
         <v>0.01072625145824839</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01741454243533127</v>
+        <v>0.01741454243533141</v>
       </c>
       <c r="I6" t="n">
         <v>0.01072625145824839</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01739563119791894</v>
+        <v>0.01739563119791896</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01741454243533127</v>
+        <v>0.01741454243533141</v>
       </c>
       <c r="L6" t="n">
         <v>0.01072625145824839</v>
@@ -5118,49 +5118,49 @@
         <v>0.01072625145824839</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1104477977541437</v>
+        <v>0.01079916973125701</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01187810419899099</v>
+        <v>0.01187810419899101</v>
       </c>
       <c r="P6" t="n">
-        <v>0.01743224309302847</v>
+        <v>0.01743224309302857</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01741454243533127</v>
+        <v>0.01741454243533141</v>
       </c>
       <c r="R6" t="n">
-        <v>0.01741454243533127</v>
+        <v>0.01741454243533141</v>
       </c>
       <c r="S6" t="n">
         <v>0.01072625145824839</v>
       </c>
       <c r="T6" t="n">
-        <v>0.01741454243533127</v>
+        <v>0.01741454243533141</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01741454243533127</v>
+        <v>0.01741454243533141</v>
       </c>
       <c r="V6" t="n">
-        <v>0.01060489576135412</v>
+        <v>0.01060489576135394</v>
       </c>
       <c r="W6" t="n">
-        <v>0.01112551689531911</v>
+        <v>0.01112551689531914</v>
       </c>
       <c r="X6" t="n">
         <v>0.01072625145824839</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01119442313919222</v>
+        <v>0.01119442313919199</v>
       </c>
       <c r="Z6" t="n">
         <v>0.01072625145824839</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.01741454243533127</v>
+        <v>0.01741454243533141</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.01081667518765563</v>
+        <v>0.01081667518765571</v>
       </c>
     </row>
     <row r="7">
@@ -5170,85 +5170,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01115592519293505</v>
+        <v>0.0111559251929351</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01115592519293503</v>
+        <v>0.0111559251929351</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01115592519293503</v>
+        <v>0.0111559251929351</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01115592519293503</v>
+        <v>0.0111559251929351</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01115592519293503</v>
+        <v>0.0111559251929351</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01115592519293503</v>
+        <v>0.0111559251929351</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01115592519293503</v>
+        <v>0.0111559251929351</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01115592519293503</v>
+        <v>0.0111559251929351</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0111370139555227</v>
+        <v>0.01113701395552272</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01115592519293503</v>
+        <v>0.0111559251929351</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01115592519293505</v>
+        <v>0.0111559251929351</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01115592519293503</v>
+        <v>0.0111559251929351</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1104477977541437</v>
+        <v>0.0111559251929351</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01115525585927213</v>
+        <v>0.01115525585927218</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01115525585927213</v>
+        <v>0.01115525585927218</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.01115592519293503</v>
+        <v>0.0111559251929351</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01115592519293503</v>
+        <v>0.0111559251929351</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01115592519293503</v>
+        <v>0.0111559251929351</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01115592519293503</v>
+        <v>0.0111559251929351</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01114812830339751</v>
+        <v>0.01114812830339752</v>
       </c>
       <c r="V7" t="n">
-        <v>0.01103456949604075</v>
+        <v>0.0110345694960406</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01115592519293503</v>
+        <v>0.0111559251929351</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01115592519293505</v>
+        <v>0.0111559251929351</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01115592519293503</v>
+        <v>0.0111559251929351</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.01115592519293503</v>
+        <v>0.0111559251929351</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01115592519293503</v>
+        <v>0.0111559251929351</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01115592519293503</v>
+        <v>0.0111559251929351</v>
       </c>
     </row>
     <row r="8">
@@ -5267,13 +5267,13 @@
         <v>0.02600025736425678</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02144800941312231</v>
+        <v>0.02144800941312234</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0187828417317875</v>
+        <v>0.01878284173178749</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02777300959097917</v>
+        <v>0.02777300959097916</v>
       </c>
       <c r="H8" t="n">
         <v>0.02600025736425678</v>
@@ -5282,7 +5282,7 @@
         <v>0.02600025736425678</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02598134612684446</v>
+        <v>0.02598134612684445</v>
       </c>
       <c r="K8" t="n">
         <v>0.02600025736425678</v>
@@ -5294,16 +5294,16 @@
         <v>0.02600025736426178</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1104477977541437</v>
+        <v>0.01937312266907392</v>
       </c>
       <c r="O8" t="n">
         <v>0.02119431682520426</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0207478981313753</v>
+        <v>0.02074789813137533</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0157708295278775</v>
+        <v>0.01577082952787755</v>
       </c>
       <c r="R8" t="n">
         <v>0.02600025736425678</v>
@@ -5315,28 +5315,28 @@
         <v>0.02600025736425678</v>
       </c>
       <c r="U8" t="n">
-        <v>0.021821936393194</v>
+        <v>0.02182193639319396</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0235361576936727</v>
+        <v>0.02353615769367269</v>
       </c>
       <c r="W8" t="n">
         <v>0.02600193754480272</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01655438949673206</v>
+        <v>0.0165543894967321</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.03449117840838434</v>
+        <v>0.03449117840838433</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.01729215376403897</v>
+        <v>0.01729215376403902</v>
       </c>
       <c r="AA8" t="n">
         <v>0.02600025736425678</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.03493071195462085</v>
+        <v>0.03493071195462084</v>
       </c>
     </row>
     <row r="9">
@@ -5346,85 +5346,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0215084413009454</v>
+        <v>0.02150844130094542</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02635167183111136</v>
+        <v>0.02635167183111145</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02635167183111136</v>
+        <v>0.02635167183111145</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02523387218583053</v>
+        <v>0.02523387218583058</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01518670666048171</v>
+        <v>0.01518670666048177</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02635166949870575</v>
+        <v>0.02635166949870574</v>
       </c>
       <c r="H9" t="n">
-        <v>0.02635167183111136</v>
+        <v>0.02635167183111145</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02635167183111136</v>
+        <v>0.02635167183111145</v>
       </c>
       <c r="J9" t="n">
-        <v>0.02633276059369904</v>
+        <v>0.02633276059369901</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02635167183111136</v>
+        <v>0.02635167183111145</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02635167183111136</v>
+        <v>0.02635167183111145</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02635167183111136</v>
+        <v>0.02635167183111145</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1104477977541437</v>
+        <v>0.02635167183111145</v>
       </c>
       <c r="O9" t="n">
-        <v>0.02795670898177836</v>
+        <v>0.02795670898177838</v>
       </c>
       <c r="P9" t="n">
-        <v>0.02830577753150608</v>
+        <v>0.02830577753150606</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.02635166949870575</v>
+        <v>0.02635166949870574</v>
       </c>
       <c r="R9" t="n">
-        <v>0.02635167183111136</v>
+        <v>0.02635167183111145</v>
       </c>
       <c r="S9" t="n">
-        <v>0.02635167183111136</v>
+        <v>0.02635167183111145</v>
       </c>
       <c r="T9" t="n">
-        <v>0.02635167183111136</v>
+        <v>0.02635167183111145</v>
       </c>
       <c r="U9" t="n">
-        <v>0.02635167183111136</v>
+        <v>0.02635167183111145</v>
       </c>
       <c r="V9" t="n">
-        <v>0.03181929020453715</v>
+        <v>0.03181929020453694</v>
       </c>
       <c r="W9" t="n">
-        <v>0.02635167183111136</v>
+        <v>0.02635167183111145</v>
       </c>
       <c r="X9" t="n">
-        <v>0.02635167183111136</v>
+        <v>0.02635167183111145</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.02635167183111136</v>
+        <v>0.02635167183111145</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.0234316335721115</v>
+        <v>0.02343163357211154</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.02635167183111136</v>
+        <v>0.02635167183111145</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.02635167183111136</v>
+        <v>0.02635167183111145</v>
       </c>
     </row>
     <row r="10">
@@ -5434,85 +5434,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01403719591451302</v>
+        <v>0.01403719591451305</v>
       </c>
       <c r="C10" t="n">
-        <v>0.01648161442339</v>
+        <v>0.01648161442339002</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01374062571319653</v>
+        <v>0.0137406257131966</v>
       </c>
       <c r="E10" t="n">
-        <v>0.02946359782216079</v>
+        <v>0.02946359782216084</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01474986107110229</v>
+        <v>0.01474986107110234</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01212410931787685</v>
+        <v>0.01212410931787688</v>
       </c>
       <c r="H10" t="n">
-        <v>0.01592109727783577</v>
+        <v>0.01592109727783578</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01245390527906397</v>
+        <v>0.01245390527906398</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01246463149196089</v>
+        <v>0.01246463149196093</v>
       </c>
       <c r="K10" t="n">
-        <v>0.01005919835182622</v>
+        <v>0.01005919835182624</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01349253209208212</v>
+        <v>0.01349253209208216</v>
       </c>
       <c r="M10" t="n">
-        <v>0.004987165816582692</v>
+        <v>0.004987165816582732</v>
       </c>
       <c r="N10" t="n">
-        <v>0.01511963654949191</v>
+        <v>0.01511963654949192</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0141739863426865</v>
+        <v>0.01417398634268652</v>
       </c>
       <c r="P10" t="n">
-        <v>0.01265741063229623</v>
+        <v>0.01265741063229625</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.01515244603184467</v>
+        <v>0.01515244603184469</v>
       </c>
       <c r="R10" t="n">
-        <v>0.01488711877826314</v>
+        <v>0.01488711877826316</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0129278826998336</v>
+        <v>0.01292788269983364</v>
       </c>
       <c r="T10" t="n">
-        <v>0.01295396499736883</v>
+        <v>0.01295396499736886</v>
       </c>
       <c r="U10" t="n">
-        <v>0.01237128041857028</v>
+        <v>0.0123712804185703</v>
       </c>
       <c r="V10" t="n">
-        <v>0.01340628245698621</v>
+        <v>0.01340628245698614</v>
       </c>
       <c r="W10" t="n">
-        <v>0.01431564833785321</v>
+        <v>0.01431564833785324</v>
       </c>
       <c r="X10" t="n">
-        <v>0.01143944250575497</v>
+        <v>0.011439442505755</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.007905221428837995</v>
+        <v>0.007905221428838033</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.01501874764625356</v>
+        <v>0.01501874764625358</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.01096736910761509</v>
+        <v>0.0109673691076151</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.008859398398201228</v>
+        <v>0.008859398398201254</v>
       </c>
     </row>
     <row r="11">
@@ -5522,85 +5522,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.01607241553908678</v>
+        <v>0.0160724155390868</v>
       </c>
       <c r="C11" t="n">
-        <v>0.01683627051091274</v>
+        <v>0.01683627051091275</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01599708411141259</v>
+        <v>0.01599708411141263</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02993825722484646</v>
+        <v>0.02993825722484651</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01632522814434237</v>
+        <v>0.01632522814434242</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01507286018897118</v>
+        <v>0.0150728601889712</v>
       </c>
       <c r="H11" t="n">
-        <v>0.01661872878175482</v>
+        <v>0.01661872878175484</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01563289164249108</v>
+        <v>0.01563289164249109</v>
       </c>
       <c r="J11" t="n">
-        <v>0.01562253655665419</v>
+        <v>0.01562253655665421</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01496903267817754</v>
+        <v>0.01496903267817756</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01592034690816783</v>
+        <v>0.01592034690816784</v>
       </c>
       <c r="M11" t="n">
-        <v>0.01351673186485555</v>
+        <v>0.01351673186485558</v>
       </c>
       <c r="N11" t="n">
-        <v>0.01638743627537212</v>
+        <v>0.01638743627537213</v>
       </c>
       <c r="O11" t="n">
-        <v>0.01611106316400699</v>
+        <v>0.01611106316400701</v>
       </c>
       <c r="P11" t="n">
         <v>0.01567494683058129</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.01639743933886886</v>
+        <v>0.01639743933886888</v>
       </c>
       <c r="R11" t="n">
-        <v>0.01620865427923269</v>
+        <v>0.01620865427923271</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01575649437522476</v>
+        <v>0.0157564943752248</v>
       </c>
       <c r="T11" t="n">
-        <v>0.01577393781963844</v>
+        <v>0.01577393781963846</v>
       </c>
       <c r="U11" t="n">
-        <v>0.01559897892253922</v>
+        <v>0.01559897892253924</v>
       </c>
       <c r="V11" t="n">
-        <v>0.01559105104546966</v>
+        <v>0.01559105104546969</v>
       </c>
       <c r="W11" t="n">
         <v>0.01615652196427361</v>
       </c>
       <c r="X11" t="n">
-        <v>0.01517581717410385</v>
+        <v>0.01517581717410389</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.01432852284253043</v>
+        <v>0.01432852284253045</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.01635871985905868</v>
+        <v>0.0163587198590587</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.01520125303599488</v>
+        <v>0.0152012530359949</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.01416794199842471</v>
+        <v>0.01416794199842476</v>
       </c>
     </row>
   </sheetData>
@@ -6066,7 +6066,7 @@
         <v>0.006481419854209764</v>
       </c>
       <c r="N5" t="n">
-        <v>0.167870398209732</v>
+        <v>0.006481419854209779</v>
       </c>
       <c r="O5" t="n">
         <v>0.006481419854209779</v>
@@ -6154,7 +6154,7 @@
         <v>0.01646375594618598</v>
       </c>
       <c r="N6" t="n">
-        <v>0.167870398209732</v>
+        <v>0.01001275686304289</v>
       </c>
       <c r="O6" t="n">
         <v>0.01654784968043898</v>
@@ -6242,7 +6242,7 @@
         <v>0.0106783259131983</v>
       </c>
       <c r="N7" t="n">
-        <v>0.167870398209732</v>
+        <v>0.0106783259131983</v>
       </c>
       <c r="O7" t="n">
         <v>0.01067762484615034</v>
@@ -6330,7 +6330,7 @@
         <v>0.02569831932618617</v>
       </c>
       <c r="N8" t="n">
-        <v>0.167870398209732</v>
+        <v>0.01902506245193412</v>
       </c>
       <c r="O8" t="n">
         <v>0.02085893138340475</v>
@@ -6418,7 +6418,7 @@
         <v>0.02699052144513758</v>
       </c>
       <c r="N9" t="n">
-        <v>0.167870398209732</v>
+        <v>0.02699052144513758</v>
       </c>
       <c r="O9" t="n">
         <v>0.02867410088425337</v>
@@ -6832,10 +6832,10 @@
         <v>0.0174576631282287</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01756204255072308</v>
+        <v>0.01756204255072307</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01736902984349661</v>
+        <v>0.01736902984349662</v>
       </c>
       <c r="N2" t="n">
         <v>0.01755850718774513</v>
@@ -6984,7 +6984,7 @@
         <v>0.0515933509103664</v>
       </c>
       <c r="D4" t="n">
-        <v>0.04807381454970697</v>
+        <v>0.04807381454970696</v>
       </c>
       <c r="E4" t="n">
         <v>0.08687253882560125</v>
@@ -7011,7 +7011,7 @@
         <v>0.07637558446949679</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04152623913329971</v>
+        <v>0.0415262391332997</v>
       </c>
       <c r="N4" t="n">
         <v>0.08759206097340473</v>
@@ -7102,7 +7102,7 @@
         <v>0.006291773525600995</v>
       </c>
       <c r="N5" t="n">
-        <v>0.08759206097340473</v>
+        <v>0.006291773525600978</v>
       </c>
       <c r="O5" t="n">
         <v>0.00629177352560098</v>
@@ -7190,7 +7190,7 @@
         <v>0.01580903086786592</v>
       </c>
       <c r="N6" t="n">
-        <v>0.08759206097340473</v>
+        <v>0.009873201191313559</v>
       </c>
       <c r="O6" t="n">
         <v>0.01583737438665622</v>
@@ -7278,7 +7278,7 @@
         <v>0.01005805765131192</v>
       </c>
       <c r="N7" t="n">
-        <v>0.08759206097340473</v>
+        <v>0.01005805765131192</v>
       </c>
       <c r="O7" t="n">
         <v>0.01005739876199438</v>
@@ -7366,7 +7366,7 @@
         <v>0.02365060506604457</v>
       </c>
       <c r="N8" t="n">
-        <v>0.08759206097340473</v>
+        <v>0.01761529162595438</v>
       </c>
       <c r="O8" t="n">
         <v>0.01927384816261513</v>
@@ -7454,7 +7454,7 @@
         <v>0.0239932980017823</v>
       </c>
       <c r="N9" t="n">
-        <v>0.08759206097340473</v>
+        <v>0.0239932980017823</v>
       </c>
       <c r="O9" t="n">
         <v>0.02545663427910944</v>
@@ -8050,7 +8050,7 @@
         <v>0.03948155519936168</v>
       </c>
       <c r="N4" t="n">
-        <v>0.06583723582804527</v>
+        <v>0.06583723582804528</v>
       </c>
       <c r="O4" t="n">
         <v>0.1318342585909859</v>
@@ -8138,7 +8138,7 @@
         <v>0.006294551119350495</v>
       </c>
       <c r="N5" t="n">
-        <v>0.06583723582804528</v>
+        <v>0.006294551119350508</v>
       </c>
       <c r="O5" t="n">
         <v>0.006294551119350508</v>
@@ -8226,7 +8226,7 @@
         <v>0.01591583953437128</v>
       </c>
       <c r="N6" t="n">
-        <v>0.06583723582804527</v>
+        <v>0.009965748185199979</v>
       </c>
       <c r="O6" t="n">
         <v>0.01104503461379259</v>
@@ -8314,7 +8314,7 @@
         <v>0.01001070944419089</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06583723582804527</v>
+        <v>0.01001070944419089</v>
       </c>
       <c r="O7" t="n">
         <v>0.01001004872244265</v>
@@ -8402,7 +8402,7 @@
         <v>0.02348275343634232</v>
       </c>
       <c r="N8" t="n">
-        <v>0.06583723582804527</v>
+        <v>0.01750540782179002</v>
       </c>
       <c r="O8" t="n">
         <v>0.0191480342967049</v>
@@ -8490,7 +8490,7 @@
         <v>0.02271893913242542</v>
       </c>
       <c r="N9" t="n">
-        <v>0.06583723582804527</v>
+        <v>0.02271893913242542</v>
       </c>
       <c r="O9" t="n">
         <v>0.0240890148509807</v>
@@ -9174,7 +9174,7 @@
         <v>0.006836145837219878</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3083382367951354</v>
+        <v>0.006836145837219883</v>
       </c>
       <c r="O5" t="n">
         <v>0.006836145837219883</v>
@@ -9262,7 +9262,7 @@
         <v>0.01047875944702208</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3083382367951354</v>
+        <v>0.01051112360469208</v>
       </c>
       <c r="O6" t="n">
         <v>0.01772543264188007</v>
@@ -9350,7 +9350,7 @@
         <v>0.0115023840560219</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3083382367951354</v>
+        <v>0.0115023840560219</v>
       </c>
       <c r="O7" t="n">
         <v>0.01150167667042547</v>
@@ -9438,7 +9438,7 @@
         <v>0.02761540760970462</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3083382367951354</v>
+        <v>0.02042390515262716</v>
       </c>
       <c r="O8" t="n">
         <v>0.02240019246999465</v>
@@ -9526,7 +9526,7 @@
         <v>0.03068575168777248</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3083382367951354</v>
+        <v>0.03068575168777248</v>
       </c>
       <c r="O9" t="n">
         <v>0.032620528551882</v>
@@ -10210,7 +10210,7 @@
         <v>0.006403764449058648</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1008086476581254</v>
+        <v>0.006403764449058649</v>
       </c>
       <c r="O5" t="n">
         <v>0.006403764449058649</v>
@@ -10298,7 +10298,7 @@
         <v>0.009900849064543459</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1008086476581254</v>
+        <v>0.009931956955628971</v>
       </c>
       <c r="O6" t="n">
         <v>0.01635843122204076</v>
@@ -10386,7 +10386,7 @@
         <v>0.01035528986106638</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1008086476581254</v>
+        <v>0.01035528986106638</v>
       </c>
       <c r="O7" t="n">
         <v>0.01035462950218271</v>
@@ -10474,7 +10474,7 @@
         <v>0.02448836143587308</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1008086476581254</v>
+        <v>0.01820369564597645</v>
       </c>
       <c r="O8" t="n">
         <v>0.01993077637336469</v>
@@ -10562,7 +10562,7 @@
         <v>0.02585907535193158</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1008086476581254</v>
+        <v>0.02585907535193158</v>
       </c>
       <c r="O9" t="n">
         <v>0.02745565937476411</v>

--- a/Results/Phase 2/Hydrogen/hydrogen eutrophication terrestrial results.xlsx
+++ b/Results/Phase 2/Hydrogen/hydrogen eutrophication terrestrial results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01938398770442724</v>
+        <v>0.01938398770442723</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01854326532375742</v>
+        <v>0.01854326532375739</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0192634790723868</v>
+        <v>0.01926347907238678</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03104861337264414</v>
+        <v>0.03104861337264419</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01900131159259907</v>
+        <v>0.01900131159259905</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01927428538629349</v>
+        <v>0.01927428538629347</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0191692748594759</v>
+        <v>0.01916927485947594</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0194223570353954</v>
+        <v>0.01942235703539539</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01928905563732521</v>
+        <v>0.0192890556373252</v>
       </c>
       <c r="K2" t="n">
-        <v>0.02006673913396207</v>
+        <v>0.02006673913396204</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01934738131878924</v>
+        <v>0.01934738131878923</v>
       </c>
       <c r="M2" t="n">
-        <v>0.02153937526498527</v>
+        <v>0.02153937526498526</v>
       </c>
       <c r="N2" t="n">
-        <v>0.01959032120316821</v>
+        <v>0.01959032120316818</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01930044331739803</v>
+        <v>0.01930044331739799</v>
       </c>
       <c r="P2" t="n">
-        <v>0.01915034106863879</v>
+        <v>0.01915034106863878</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0189141271297282</v>
+        <v>0.01891412712972816</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01899995779054998</v>
+        <v>0.01899995779054995</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01923687679245957</v>
+        <v>0.01923687679245956</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01945294628362958</v>
+        <v>0.01945294628362954</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01982426815024373</v>
+        <v>0.01982426815024372</v>
       </c>
       <c r="V2" t="n">
-        <v>0.01921953497061761</v>
+        <v>0.0192195349706176</v>
       </c>
       <c r="W2" t="n">
-        <v>0.01912692300674153</v>
+        <v>0.0191269230067415</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01892399239931456</v>
+        <v>0.01892399239931453</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.01904512041991535</v>
+        <v>0.01904512041991533</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.01891967598917394</v>
+        <v>0.01891967598917391</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.01961925055414632</v>
+        <v>0.01961925055414629</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.01996333683601509</v>
+        <v>0.01996333683601507</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0187152664242936</v>
+        <v>0.01871526642429357</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0187152664242936</v>
+        <v>0.01871526642429357</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0187152664242936</v>
+        <v>0.01871526642429357</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03126429948281021</v>
+        <v>0.03126429948281025</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0187152664242936</v>
+        <v>0.01871526642429357</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0187152664242936</v>
+        <v>0.01871526642429357</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0187152664242936</v>
+        <v>0.01871526642429357</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0187152664242936</v>
+        <v>0.01871526642429357</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0186948672029101</v>
+        <v>0.01869486720291007</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0187152664242936</v>
+        <v>0.01871526642429357</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0187152664242936</v>
+        <v>0.01871526642429357</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0187152664242936</v>
+        <v>0.01871526642429357</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0187152664242936</v>
+        <v>0.01871526642429357</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0187152664242936</v>
+        <v>0.01871526642429357</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0187152664242936</v>
+        <v>0.01871526642429357</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0187152664242936</v>
+        <v>0.01871526642429357</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0187152664242936</v>
+        <v>0.01871526642429357</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0187152664242936</v>
+        <v>0.01871526642429357</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0187152664242936</v>
+        <v>0.01871526642429357</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0187152664242936</v>
+        <v>0.01871526642429357</v>
       </c>
       <c r="V3" t="n">
         <v>0.01907140468649561</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0187152664242936</v>
+        <v>0.01871526642429357</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0187152664242936</v>
+        <v>0.01871526642429357</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0187152664242936</v>
+        <v>0.01871526642429357</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0187152664242936</v>
+        <v>0.01871526642429357</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0187152664242936</v>
+        <v>0.01871526642429357</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0187152664242936</v>
+        <v>0.01871526642429357</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.299639666530802</v>
+        <v>0.299639666530801</v>
       </c>
       <c r="C4" t="n">
-        <v>0.08069674166398606</v>
+        <v>0.08069674166398612</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3006810655569711</v>
+        <v>0.3006810655569714</v>
       </c>
       <c r="E4" t="n">
-        <v>0.11980723755697</v>
+        <v>0.1198072375569698</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2254690658094402</v>
+        <v>0.22546906580944</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2777546289848009</v>
+        <v>0.2777546289848006</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2825091147569042</v>
+        <v>0.2825091147569039</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3527411130573628</v>
+        <v>0.3527411130573627</v>
       </c>
       <c r="J4" t="n">
         <v>0.2980907313635899</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5410518310231507</v>
+        <v>0.5410518310231499</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3098815097060624</v>
+        <v>0.3098815097060538</v>
       </c>
       <c r="M4" t="n">
-        <v>1.002377733142813</v>
+        <v>1.002377733142814</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3892300692142192</v>
+        <v>0.3892300692142197</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2710162737496626</v>
+        <v>0.2710162737496625</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2409992768914056</v>
+        <v>0.2409992768914051</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1905908126156785</v>
+        <v>0.1905908126156779</v>
       </c>
       <c r="R4" t="n">
-        <v>0.225476800818957</v>
+        <v>0.2254768008189567</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2677546214112348</v>
+        <v>0.2677546214112346</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3596307398524218</v>
+        <v>0.3596307398524224</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4390356299977362</v>
+        <v>0.4390356299977364</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1628406425996451</v>
+        <v>0.1628406425996445</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2480392684414262</v>
+        <v>0.2480392684414257</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1949341191693684</v>
+        <v>0.1949341191693683</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.2242576027375058</v>
+        <v>0.2242576027375061</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.1793591298299707</v>
+        <v>0.1793591298299715</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.3937840635407269</v>
+        <v>0.3937840635407263</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.5378634849724654</v>
+        <v>0.5378634849724652</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02098832833109028</v>
+        <v>0.02098832833109031</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03163853068047867</v>
+        <v>0.03163853068047857</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03163853068047867</v>
+        <v>0.03163853068047857</v>
       </c>
       <c r="E5" t="n">
-        <v>0.025967612091</v>
+        <v>0.02596761209100009</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02264750538541605</v>
+        <v>0.02264750538541603</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03384691951715094</v>
+        <v>0.03384691951715092</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03163853068047867</v>
+        <v>0.03163853068047857</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03163853068047867</v>
+        <v>0.03163853068047857</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03161987248931664</v>
+        <v>0.03161987248931659</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03163853068047867</v>
+        <v>0.03163853068047857</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03163853068047867</v>
+        <v>0.03163853068047857</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03163853068047924</v>
+        <v>0.03163853068047912</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3892300692142192</v>
+        <v>0.02338284211932026</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02565157701820966</v>
+        <v>0.02565157701820964</v>
       </c>
       <c r="P5" t="n">
-        <v>0.02509545527424002</v>
+        <v>0.02509545527424006</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01889532049076484</v>
+        <v>0.01889532049076477</v>
       </c>
       <c r="R5" t="n">
-        <v>0.03163853068047867</v>
+        <v>0.03163853068047857</v>
       </c>
       <c r="S5" t="n">
-        <v>0.03163853068047867</v>
+        <v>0.03163853068047857</v>
       </c>
       <c r="T5" t="n">
-        <v>0.03163853068047867</v>
+        <v>0.03163853068047857</v>
       </c>
       <c r="U5" t="n">
-        <v>0.02643686813965272</v>
+        <v>0.02643686813965269</v>
       </c>
       <c r="V5" t="n">
-        <v>0.02860521176833497</v>
+        <v>0.02860521176833498</v>
       </c>
       <c r="W5" t="n">
-        <v>0.03164062374910031</v>
+        <v>0.03164062374910027</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01987143269756705</v>
+        <v>0.01987143269756704</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.04222189804891083</v>
+        <v>0.04222189804891077</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.02079049535472456</v>
+        <v>0.02079049535472459</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.03163853068047867</v>
+        <v>0.03163853068047857</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0427635575886618</v>
+        <v>0.04276355758866178</v>
       </c>
     </row>
     <row r="6">
@@ -947,13 +947,13 @@
         <v>0.0380791458954905</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0363865135289131</v>
+        <v>0.03638651352891299</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02117256811493927</v>
+        <v>0.02117256811493921</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0380791408932243</v>
+        <v>0.03807914089322424</v>
       </c>
       <c r="H6" t="n">
         <v>0.0380791458954905</v>
@@ -962,7 +962,7 @@
         <v>0.0380791458954905</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03806048770432845</v>
+        <v>0.03806048770432837</v>
       </c>
       <c r="K6" t="n">
         <v>0.0380791458954905</v>
@@ -974,16 +974,16 @@
         <v>0.0380791458954905</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3892300692142192</v>
+        <v>0.0380791458954905</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04050957592697845</v>
+        <v>0.04050957592697835</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0410381538475767</v>
+        <v>0.04103815384757659</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0380791408932243</v>
+        <v>0.03807914089322424</v>
       </c>
       <c r="R6" t="n">
         <v>0.0380791458954905</v>
@@ -998,7 +998,7 @@
         <v>0.0380791458954905</v>
       </c>
       <c r="V6" t="n">
-        <v>0.04642359881292357</v>
+        <v>0.04642359881292355</v>
       </c>
       <c r="W6" t="n">
         <v>0.0380791458954905</v>
@@ -1010,7 +1010,7 @@
         <v>0.0380791458954905</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.03365746922055556</v>
+        <v>0.03365746922055549</v>
       </c>
       <c r="AA6" t="n">
         <v>0.0380791458954905</v>
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01229689193724938</v>
+        <v>0.01229689193724937</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01731881347814586</v>
+        <v>0.01731881347814585</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01310176472753661</v>
+        <v>0.01310176472753659</v>
       </c>
       <c r="E7" t="n">
         <v>0.02893580621280459</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01465735673588952</v>
+        <v>0.01465735673588949</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01295274009299133</v>
+        <v>0.0129527400929913</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0136877581429313</v>
+        <v>0.01368775814293124</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01218339671904889</v>
+        <v>0.01218339671904885</v>
       </c>
       <c r="J7" t="n">
-        <v>0.012763992743412</v>
+        <v>0.01276399274341198</v>
       </c>
       <c r="K7" t="n">
-        <v>0.008382003825322717</v>
+        <v>0.008382003825322693</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01255363063285876</v>
+        <v>0.01255363063285884</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0001574457840219524</v>
+        <v>-0.0001574457840219862</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01115539548532488</v>
+        <v>0.01115539548532485</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01278745530113307</v>
+        <v>0.01278745530113306</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01367693359859472</v>
+        <v>0.01367693359859468</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.01513896321894398</v>
+        <v>0.01513896321894397</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01466141653819152</v>
+        <v>0.0146614165381915</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0131892186090765</v>
+        <v>0.01318921860907649</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01199622847994325</v>
+        <v>0.01199622847994323</v>
       </c>
       <c r="U7" t="n">
-        <v>0.009725378869693617</v>
+        <v>0.009725378869693588</v>
       </c>
       <c r="V7" t="n">
-        <v>0.01571582003243165</v>
+        <v>0.01571582003243166</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01386506341736284</v>
+        <v>0.01386506341736282</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01508682258559602</v>
+        <v>0.01508682258559604</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01435492549238447</v>
+        <v>0.01435492549238443</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0150632218953968</v>
+        <v>0.01506322189539681</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01096566923485902</v>
+        <v>0.01096566923485901</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.009004543544282696</v>
+        <v>0.009004543544282671</v>
       </c>
     </row>
     <row r="8">
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01646360685867626</v>
+        <v>0.01646360685867625</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0179078747830287</v>
+        <v>0.01790787478302867</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0167093179111939</v>
+        <v>0.01670931791119384</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02998914151432385</v>
+        <v>0.0299891415143238</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01715494975258433</v>
+        <v>0.01715494975258429</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01665231754146916</v>
+        <v>0.01665231754146914</v>
       </c>
       <c r="H8" t="n">
         <v>0.01688174256973778</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0164503355036754</v>
+        <v>0.01645033550367542</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01659048885767812</v>
+        <v>0.01659048885767806</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01536507172127629</v>
+        <v>0.01536507172127627</v>
       </c>
       <c r="L8" t="n">
         <v>0.01654381739771821</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01295223106643647</v>
+        <v>0.01295223106643644</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01615055583405823</v>
+        <v>0.01615055583405819</v>
       </c>
       <c r="O8" t="n">
-        <v>0.01660327036554681</v>
+        <v>0.01660327036554676</v>
       </c>
       <c r="P8" t="n">
-        <v>0.01685788357673177</v>
+        <v>0.01685788357673176</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01728689777429203</v>
+        <v>0.01728689777429201</v>
       </c>
       <c r="R8" t="n">
-        <v>0.01715544317352048</v>
+        <v>0.01715544317352044</v>
       </c>
       <c r="S8" t="n">
-        <v>0.01672250742606631</v>
+        <v>0.0167225074260663</v>
       </c>
       <c r="T8" t="n">
-        <v>0.01639576260664673</v>
+        <v>0.01639576260664671</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01573384066382896</v>
+        <v>0.01573384066382891</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0176927332594047</v>
+        <v>0.01769273325940469</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01692006518190817</v>
+        <v>0.01692006518190814</v>
       </c>
       <c r="X8" t="n">
         <v>0.01727303888954275</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.01706115140031464</v>
+        <v>0.01706115140031459</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.01725798409015054</v>
+        <v>0.01725798409015048</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01609315913645267</v>
+        <v>0.01609315913645265</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.01554492697937244</v>
+        <v>0.01554492697937242</v>
       </c>
     </row>
   </sheetData>
@@ -1361,52 +1361,52 @@
         <v>0.01656858112964234</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01674482253260142</v>
+        <v>0.01674482253260141</v>
       </c>
       <c r="D2" t="n">
         <v>0.01664473408533976</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03015478024454273</v>
+        <v>0.03015478024454271</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01681553961305889</v>
+        <v>0.01681553961305888</v>
       </c>
       <c r="G2" t="n">
         <v>0.01604782440588783</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01667847944986235</v>
+        <v>0.01667847944986234</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0166739646615131</v>
+        <v>0.01667396466151309</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01674584892341746</v>
+        <v>0.01674584892341744</v>
       </c>
       <c r="K2" t="n">
         <v>0.01680110084810157</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01695661779346193</v>
+        <v>0.01695661779346191</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01668781509928324</v>
+        <v>0.01668781509928325</v>
       </c>
       <c r="N2" t="n">
-        <v>0.01674680390538374</v>
+        <v>0.01674680390538373</v>
       </c>
       <c r="O2" t="n">
         <v>0.01687558945596741</v>
       </c>
       <c r="P2" t="n">
-        <v>0.01676973744747241</v>
+        <v>0.0167697374474724</v>
       </c>
       <c r="Q2" t="n">
         <v>0.01662791391661194</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01687676461579086</v>
+        <v>0.01687676461579084</v>
       </c>
       <c r="S2" t="n">
         <v>0.01684240471670512</v>
@@ -1415,25 +1415,25 @@
         <v>0.01674108560701516</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01671575897192256</v>
+        <v>0.01671575897192254</v>
       </c>
       <c r="V2" t="n">
-        <v>0.01629996848704001</v>
+        <v>0.01629996848703993</v>
       </c>
       <c r="W2" t="n">
-        <v>0.01695852437730086</v>
+        <v>0.01695852437730087</v>
       </c>
       <c r="X2" t="n">
         <v>0.01722549159906038</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.01707504232337584</v>
+        <v>0.01707504232337582</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.01670272495425585</v>
+        <v>0.01670272495425586</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.01706798920829459</v>
+        <v>0.01706798920829458</v>
       </c>
       <c r="AB2" t="n">
         <v>0.0159291566648795</v>
@@ -1446,16 +1446,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01687581488703103</v>
+        <v>0.01687581488703104</v>
       </c>
       <c r="C3" t="n">
         <v>0.01697140972251253</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01687581488703103</v>
+        <v>0.01687581488703104</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03064252034977909</v>
+        <v>0.03064252034977907</v>
       </c>
       <c r="F3" t="n">
         <v>0.01693764115274309</v>
@@ -1464,10 +1464,10 @@
         <v>0.01615626077856951</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01687581488703103</v>
+        <v>0.01687581488703104</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01687581488703103</v>
+        <v>0.01687581488703104</v>
       </c>
       <c r="J3" t="n">
         <v>0.01687045268758463</v>
@@ -1476,55 +1476,55 @@
         <v>0.01690807533580639</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01687581488703103</v>
+        <v>0.01687581488703104</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01687581488703103</v>
+        <v>0.01687581488703104</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01687581488703103</v>
+        <v>0.01687581488703104</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01687581488703103</v>
+        <v>0.01687581488703104</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01687581488703103</v>
+        <v>0.01687581488703104</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01687581488703103</v>
+        <v>0.01687581488703104</v>
       </c>
       <c r="R3" t="n">
         <v>0.01669160889243725</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01687581488703103</v>
+        <v>0.01687581488703104</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01687581488703103</v>
+        <v>0.01687581488703104</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01687581488703103</v>
+        <v>0.01687581488703104</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0164042259574803</v>
+        <v>0.0164042259574802</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01687581488703103</v>
+        <v>0.01687581488703104</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01661191392218468</v>
+        <v>0.01661191392218469</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01687581488703103</v>
+        <v>0.01687581488703104</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01688256225308991</v>
+        <v>0.01688256225308992</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.01687581488703103</v>
+        <v>0.01687581488703104</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01617403476061417</v>
+        <v>0.01617403476061418</v>
       </c>
     </row>
     <row r="4">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02693718685820111</v>
+        <v>0.02693718685820105</v>
       </c>
       <c r="C4" t="n">
         <v>0.05048372877075612</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0479232816936459</v>
+        <v>0.04792328169364594</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03402929005337516</v>
+        <v>0.03402929005337508</v>
       </c>
       <c r="F4" t="n">
-        <v>0.07769382733131877</v>
+        <v>0.07769382733131867</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05745188250069323</v>
+        <v>0.05745188250069306</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05979753533196979</v>
+        <v>0.05979753533196975</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05668867035100867</v>
+        <v>0.05668867035100869</v>
       </c>
       <c r="J4" t="n">
-        <v>0.07118082383085278</v>
+        <v>0.0711808238308527</v>
       </c>
       <c r="K4" t="n">
-        <v>0.07472039755016659</v>
+        <v>0.07472039755016652</v>
       </c>
       <c r="L4" t="n">
-        <v>0.115813662892974</v>
+        <v>0.1158136628929741</v>
       </c>
       <c r="M4" t="n">
-        <v>0.059469829633622</v>
+        <v>0.05946982963362194</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0748635010547688</v>
+        <v>0.07486350105476886</v>
       </c>
       <c r="O4" t="n">
-        <v>0.09512443173631684</v>
+        <v>0.09512443173631692</v>
       </c>
       <c r="P4" t="n">
-        <v>0.07204855998001854</v>
+        <v>0.07204855998001855</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0423261217658857</v>
+        <v>0.04232612176588568</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1570153550767402</v>
+        <v>0.1570153550767401</v>
       </c>
       <c r="S4" t="n">
-        <v>0.08859683441777612</v>
+        <v>0.08859683441777604</v>
       </c>
       <c r="T4" t="n">
-        <v>0.07454186075527529</v>
+        <v>0.07454186075527527</v>
       </c>
       <c r="U4" t="n">
-        <v>0.06032955908616774</v>
+        <v>0.06032955908616747</v>
       </c>
       <c r="V4" t="n">
-        <v>0.07123552498358353</v>
+        <v>0.07123552498358346</v>
       </c>
       <c r="W4" t="n">
         <v>0.126331173570492</v>
       </c>
       <c r="X4" t="n">
-        <v>0.2474544611467912</v>
+        <v>0.2474544611467914</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1583524662535888</v>
+        <v>0.1583524662535886</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.05396512560229394</v>
+        <v>0.05396512560229399</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.1558773951453484</v>
+        <v>0.1558773951453485</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0309033788971524</v>
+        <v>0.03090337889715238</v>
       </c>
     </row>
     <row r="5">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01580952982486501</v>
+        <v>0.015809529824865</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0235636461122323</v>
+        <v>0.02356364611223224</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0235636461122323</v>
+        <v>0.02356364611223224</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01943480792148515</v>
+        <v>0.01943480792148513</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01701753051806293</v>
+        <v>0.01701753051806289</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02517151263773259</v>
+        <v>0.02517151263773254</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0235636461122323</v>
+        <v>0.02356364611223224</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0235636461122323</v>
+        <v>0.02356364611223224</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02354575785698694</v>
+        <v>0.02354575785698687</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0235636461122323</v>
+        <v>0.02356364611223224</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0235636461122323</v>
+        <v>0.02356364611223224</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02356364611223223</v>
+        <v>0.02356364611223217</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0748635010547688</v>
+        <v>0.01755290875391474</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01920471156993937</v>
+        <v>0.01920471156993935</v>
       </c>
       <c r="P5" t="n">
-        <v>0.01879981478662107</v>
+        <v>0.01879981478662103</v>
       </c>
       <c r="Q5" t="n">
         <v>0.01428566899553144</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0235636461122323</v>
+        <v>0.02356364611223224</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0235636461122323</v>
+        <v>0.02356364611223224</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0235636461122323</v>
+        <v>0.02356364611223224</v>
       </c>
       <c r="U5" t="n">
-        <v>0.01977370451326938</v>
+        <v>0.01977370451326935</v>
       </c>
       <c r="V5" t="n">
-        <v>0.02132364911358644</v>
+        <v>0.02132364911358635</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02356517001746837</v>
+        <v>0.02356517001746829</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01499634916045086</v>
+        <v>0.01499634916045087</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.03126438751804842</v>
+        <v>0.03126438751804839</v>
       </c>
       <c r="Z5" t="n">
         <v>0.01566549313391362</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0235636461122323</v>
+        <v>0.02356364611223224</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.03166346896232564</v>
+        <v>0.03166346896232558</v>
       </c>
     </row>
     <row r="6">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01851943197800633</v>
+        <v>0.01851943197800632</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02264387314092675</v>
+        <v>0.02264387314092672</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02264387314092675</v>
+        <v>0.02264387314092672</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02169197104564941</v>
+        <v>0.0216919710456494</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01313590702696907</v>
+        <v>0.01313590702696906</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02264387587340813</v>
+        <v>0.0226438758734081</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02264387314092675</v>
+        <v>0.02264387314092672</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02264387314092675</v>
+        <v>0.02264387314092672</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02262598488568137</v>
+        <v>0.02262598488568132</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02264387314092675</v>
+        <v>0.02264387314092672</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02264387314092675</v>
+        <v>0.02264387314092672</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02264387314092675</v>
+        <v>0.02264387314092672</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0748635010547688</v>
+        <v>0.02264387314092672</v>
       </c>
       <c r="O6" t="n">
-        <v>0.02401071117984668</v>
+        <v>0.02401071117984666</v>
       </c>
       <c r="P6" t="n">
         <v>0.02430797440805186</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.02264387587340813</v>
+        <v>0.0226438758734081</v>
       </c>
       <c r="R6" t="n">
-        <v>0.02264387314092675</v>
+        <v>0.02264387314092672</v>
       </c>
       <c r="S6" t="n">
-        <v>0.02264387314092675</v>
+        <v>0.02264387314092672</v>
       </c>
       <c r="T6" t="n">
-        <v>0.02264387314092675</v>
+        <v>0.02264387314092672</v>
       </c>
       <c r="U6" t="n">
-        <v>0.02264387314092675</v>
+        <v>0.02264387314092672</v>
       </c>
       <c r="V6" t="n">
-        <v>0.02728851483301444</v>
+        <v>0.02728851483301434</v>
       </c>
       <c r="W6" t="n">
-        <v>0.02264387314092675</v>
+        <v>0.02264387314092672</v>
       </c>
       <c r="X6" t="n">
-        <v>0.02264387314092675</v>
+        <v>0.02264387314092672</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.02264387314092675</v>
+        <v>0.02264387314092672</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.02015720296434196</v>
+        <v>0.02015720296434195</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.02264387314092675</v>
+        <v>0.02264387314092672</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.02264387314092675</v>
+        <v>0.02264387314092672</v>
       </c>
     </row>
     <row r="7">
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01638789162952631</v>
+        <v>0.01638789162952629</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01596930209417879</v>
+        <v>0.0159693020941788</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01594945095071812</v>
+        <v>0.01594945095071811</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02993415597190733</v>
+        <v>0.0299341559719073</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01534954405463855</v>
+        <v>0.01534954405463856</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0148552783758394</v>
+        <v>0.01485527837583941</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01575941790583444</v>
+        <v>0.01575941790583443</v>
       </c>
       <c r="I7" t="n">
         <v>0.01578030006714062</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01530777797615385</v>
+        <v>0.01530777797615383</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01523609434245228</v>
+        <v>0.0152360943424523</v>
       </c>
       <c r="L7" t="n">
         <v>0.01409698867176389</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01570160311594891</v>
+        <v>0.01570160311594893</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0153450949024597</v>
+        <v>0.01534509490245971</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01455891747986226</v>
+        <v>0.01455891747986228</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01518783094388933</v>
+        <v>0.01518783094388932</v>
       </c>
       <c r="Q7" t="n">
         <v>0.01604583997236943</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0134330279865878</v>
+        <v>0.01343302798658779</v>
       </c>
       <c r="S7" t="n">
         <v>0.01476542595906519</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01538602018240686</v>
+        <v>0.01538602018240687</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01551954754397276</v>
+        <v>0.01551954754397277</v>
       </c>
       <c r="V7" t="n">
-        <v>0.01474841055857988</v>
+        <v>0.01474841055857978</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01409038423770312</v>
+        <v>0.01409038423770311</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01086561547449424</v>
+        <v>0.01086561547449427</v>
       </c>
       <c r="Y7" t="n">
         <v>0.01340831843788964</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.01563466837294956</v>
+        <v>0.01563466837294955</v>
       </c>
       <c r="AA7" t="n">
         <v>0.01344712128933637</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01568283748274764</v>
+        <v>0.01568283748274763</v>
       </c>
     </row>
     <row r="8">
@@ -1886,13 +1886,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01634657449255852</v>
+        <v>0.01634657449255851</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01628886036818206</v>
+        <v>0.01628886036818205</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01622323554217067</v>
+        <v>0.01622323554217066</v>
       </c>
       <c r="E8" t="n">
         <v>0.0298324721951878</v>
@@ -1904,19 +1904,19 @@
         <v>0.01545587326666072</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0161705152656718</v>
+        <v>0.01617051526567179</v>
       </c>
       <c r="I8" t="n">
         <v>0.01617550192726436</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01603482694976764</v>
+        <v>0.01603482694976762</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01604034416783818</v>
+        <v>0.01604034416783817</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01569224300992165</v>
+        <v>0.01569224300992164</v>
       </c>
       <c r="M8" t="n">
         <v>0.01615354500144998</v>
@@ -1925,16 +1925,16 @@
         <v>0.01605032143428861</v>
       </c>
       <c r="O8" t="n">
-        <v>0.01582139375219166</v>
+        <v>0.01582139375219168</v>
       </c>
       <c r="P8" t="n">
-        <v>0.01600169937405724</v>
+        <v>0.01600169937405727</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01625027268546779</v>
+        <v>0.0162502726854678</v>
       </c>
       <c r="R8" t="n">
-        <v>0.01539409991914816</v>
+        <v>0.01539409991914815</v>
       </c>
       <c r="S8" t="n">
         <v>0.01588217102907019</v>
@@ -1946,7 +1946,7 @@
         <v>0.01609865300866347</v>
       </c>
       <c r="V8" t="n">
-        <v>0.01554656720376973</v>
+        <v>0.01554656720376963</v>
       </c>
       <c r="W8" t="n">
         <v>0.01569114455521587</v>
@@ -1955,16 +1955,16 @@
         <v>0.01461090749299465</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.01549732038876098</v>
+        <v>0.01549732038876097</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.01613492926199014</v>
+        <v>0.01613492926199013</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01550792269474534</v>
+        <v>0.01550792269474533</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.01570566033809739</v>
+        <v>0.01570566033809741</v>
       </c>
     </row>
   </sheetData>
@@ -2130,85 +2130,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01867167856808359</v>
+        <v>0.01867167856808362</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01813563321869034</v>
+        <v>0.01813563321869035</v>
       </c>
       <c r="D2" t="n">
         <v>0.01861530485570173</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03083973635588247</v>
+        <v>0.03083973635588251</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01827380763957266</v>
+        <v>0.01827380763957267</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01840177289869831</v>
+        <v>0.01840177289869832</v>
       </c>
       <c r="H2" t="n">
         <v>0.01821176416481302</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01848680362871769</v>
+        <v>0.0184868036287177</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01874144608734944</v>
+        <v>0.01874144608734946</v>
       </c>
       <c r="K2" t="n">
         <v>0.01931870894973544</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01873434776663314</v>
+        <v>0.01873434776663317</v>
       </c>
       <c r="M2" t="n">
-        <v>0.02077255461801292</v>
+        <v>0.02077255461801293</v>
       </c>
       <c r="N2" t="n">
-        <v>0.01871352459496378</v>
+        <v>0.01871352459496379</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01857359375384707</v>
+        <v>0.01857359375384709</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0187541295905874</v>
+        <v>0.01875412959058741</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.01827845975633212</v>
+        <v>0.01827845975633214</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01823394196929758</v>
+        <v>0.01823394196929759</v>
       </c>
       <c r="S2" t="n">
         <v>0.01870498183250151</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01864982307185335</v>
+        <v>0.01864982307185336</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01906667383220478</v>
+        <v>0.01906667383220479</v>
       </c>
       <c r="V2" t="n">
         <v>0.01817666242549697</v>
       </c>
       <c r="W2" t="n">
-        <v>0.01877178462057371</v>
+        <v>0.01877178462057372</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01848245119708974</v>
+        <v>0.01848245119708977</v>
       </c>
       <c r="Y2" t="n">
         <v>0.01847312625172111</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.01829988644837759</v>
+        <v>0.01829988644837762</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.01882119192811506</v>
+        <v>0.01882119192811507</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.01875581126337884</v>
+        <v>0.01875581126337886</v>
       </c>
     </row>
     <row r="3">
@@ -2218,85 +2218,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01821899332876084</v>
+        <v>0.01821899332876087</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01831037524485899</v>
+        <v>0.01831037524485901</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01821899332876084</v>
+        <v>0.01821899332876087</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03109497140713858</v>
+        <v>0.03109497140713861</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01825200089502308</v>
+        <v>0.0182520008950231</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01786611806057401</v>
+        <v>0.01786611806057403</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01821899332876084</v>
+        <v>0.01821899332876087</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01821899332876084</v>
+        <v>0.01821899332876087</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01819281238164483</v>
+        <v>0.01819281238164486</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01823673470345419</v>
+        <v>0.01823673470345421</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01821899332876084</v>
+        <v>0.01821899332876087</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01821899332876084</v>
+        <v>0.01821899332876087</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01821899332876084</v>
+        <v>0.01821899332876087</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01821899332876084</v>
+        <v>0.01821899332876087</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01821899332876084</v>
+        <v>0.01821899332876087</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01821899332876084</v>
+        <v>0.01821899332876087</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01822231828673679</v>
+        <v>0.01822231828673681</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01821899332876084</v>
+        <v>0.01821899332876087</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01821899332876084</v>
+        <v>0.01821899332876087</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01821899332876084</v>
+        <v>0.01821899332876087</v>
       </c>
       <c r="V3" t="n">
-        <v>0.01823138562005998</v>
+        <v>0.01823138562005999</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01821899332876084</v>
+        <v>0.01821899332876087</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0181707676760716</v>
+        <v>0.01817076767607162</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01821899332876084</v>
+        <v>0.01821899332876087</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01822307160333989</v>
+        <v>0.01822307160333991</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.01821899332876084</v>
+        <v>0.01821899332876087</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01751721320234398</v>
+        <v>0.017517213202344</v>
       </c>
     </row>
     <row r="4">
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2237872582973596</v>
+        <v>0.2237872582973609</v>
       </c>
       <c r="C4" t="n">
-        <v>0.07490716269457245</v>
+        <v>0.07490716269457247</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2372168895839558</v>
+        <v>0.2372168895839554</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1016796590693429</v>
+        <v>0.1016796590693446</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1315484167341479</v>
+        <v>0.1315484167341483</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2429055142276981</v>
+        <v>0.2429055142276983</v>
       </c>
       <c r="H4" t="n">
         <v>0.1266200086048905</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2027471341652342</v>
+        <v>0.2027471341652343</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2654831717538238</v>
+        <v>0.2654831717538232</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4007466089755692</v>
+        <v>0.4007466089755695</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2575620316523065</v>
+        <v>0.2575620316523155</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8545392955992569</v>
+        <v>0.8545392955992543</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2579550597110481</v>
+        <v>0.2579550597110484</v>
       </c>
       <c r="O4" t="n">
         <v>0.1945236502473766</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2497377658066222</v>
+        <v>0.2497377658066235</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1379155666344308</v>
+        <v>0.1379155666344319</v>
       </c>
       <c r="R4" t="n">
         <v>0.1306121750513781</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2381781578495467</v>
+        <v>0.2381781578495471</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2466315228576434</v>
+        <v>0.2466315228576443</v>
       </c>
       <c r="U4" t="n">
         <v>0.3400121781641792</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0962351499301521</v>
+        <v>0.09623514993015206</v>
       </c>
       <c r="W4" t="n">
         <v>0.2696611233039307</v>
       </c>
       <c r="X4" t="n">
-        <v>0.2082599955630298</v>
+        <v>0.2082599955630313</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.186541084901007</v>
+        <v>0.1865410849010069</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.1331047555980838</v>
+        <v>0.1331047555980844</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.2825895527888123</v>
+        <v>0.2825895527888136</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.4818967868784861</v>
+        <v>0.4818967868784887</v>
       </c>
     </row>
     <row r="5">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01871983676091328</v>
+        <v>0.01871983676091327</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02819838809473926</v>
+        <v>0.0281983880947393</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02819838809473926</v>
+        <v>0.0281983880947393</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02315133910948548</v>
+        <v>0.02315133910948551</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02019648428040185</v>
+        <v>0.02019648428040186</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03016382746074786</v>
+        <v>0.03016382746074783</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02819838809473926</v>
+        <v>0.0281983880947393</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02819838809473926</v>
+        <v>0.0281983880947393</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02817588669184078</v>
+        <v>0.02817588669184076</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02819838809473926</v>
+        <v>0.0281983880947393</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02819838809473926</v>
+        <v>0.0281983880947393</v>
       </c>
       <c r="M5" t="n">
         <v>0.02819838809474082</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2579550597110481</v>
+        <v>0.02085092508361369</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02287007171541521</v>
+        <v>0.0228700717154152</v>
       </c>
       <c r="P5" t="n">
-        <v>0.02237513008660305</v>
+        <v>0.02237513008660309</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01685708508674947</v>
+        <v>0.01685708508674942</v>
       </c>
       <c r="R5" t="n">
-        <v>0.02819838809473926</v>
+        <v>0.02819838809473927</v>
       </c>
       <c r="S5" t="n">
-        <v>0.02819838809473926</v>
+        <v>0.0281983880947393</v>
       </c>
       <c r="T5" t="n">
-        <v>0.02819838809473926</v>
+        <v>0.02819838809473927</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0235676315461192</v>
+        <v>0.02356763154611919</v>
       </c>
       <c r="V5" t="n">
         <v>0.02545862815944109</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02820025090046573</v>
+        <v>0.02820025090046572</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01772581314993182</v>
+        <v>0.01772581314993178</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.03761516514085981</v>
+        <v>0.03761516514085984</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.01854376780368076</v>
+        <v>0.01854376780368079</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.02819838809473926</v>
+        <v>0.0281983880947393</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.03809952754539759</v>
+        <v>0.03809952754539765</v>
       </c>
     </row>
     <row r="6">
@@ -2482,85 +2482,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02533521937903962</v>
+        <v>0.02533521937903958</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03129031456049006</v>
+        <v>0.03129031456049004</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03129031456049006</v>
+        <v>0.03129031456049004</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02991589953834952</v>
+        <v>0.02991589953834953</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01756220054315641</v>
+        <v>0.01756220054315638</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03129031021229094</v>
+        <v>0.03129031021229096</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03129031456049006</v>
+        <v>0.03129031456049004</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03129031456049006</v>
+        <v>0.03129031456049004</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03126781315759158</v>
+        <v>0.03126781315759155</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03129031456049006</v>
+        <v>0.03129031456049004</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03129031456049006</v>
+        <v>0.03129031456049004</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03129031456049006</v>
+        <v>0.03129031456049004</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2579550597110481</v>
+        <v>0.03129031456049004</v>
       </c>
       <c r="O6" t="n">
-        <v>0.03326381951690534</v>
+        <v>0.03326381951690537</v>
       </c>
       <c r="P6" t="n">
-        <v>0.03369302393094097</v>
+        <v>0.03369302393094098</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.03129031021229094</v>
+        <v>0.03129031021229096</v>
       </c>
       <c r="R6" t="n">
-        <v>0.03129031456049006</v>
+        <v>0.03129031456049004</v>
       </c>
       <c r="S6" t="n">
-        <v>0.03129031456049006</v>
+        <v>0.03129031456049004</v>
       </c>
       <c r="T6" t="n">
-        <v>0.03129031456049006</v>
+        <v>0.03129031456049004</v>
       </c>
       <c r="U6" t="n">
-        <v>0.03129031456049006</v>
+        <v>0.03129031456049004</v>
       </c>
       <c r="V6" t="n">
-        <v>0.03801807643079159</v>
+        <v>0.03801807643079162</v>
       </c>
       <c r="W6" t="n">
-        <v>0.03129031456049006</v>
+        <v>0.03129031456049004</v>
       </c>
       <c r="X6" t="n">
-        <v>0.03129031456049006</v>
+        <v>0.03129031456049004</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.03129031456049006</v>
+        <v>0.03129031456049004</v>
       </c>
       <c r="Z6" t="n">
         <v>0.02769991998717882</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.03129031456049006</v>
+        <v>0.03129031456049004</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.03129031456049006</v>
+        <v>0.03129031456049004</v>
       </c>
     </row>
     <row r="7">
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01309954932753633</v>
+        <v>0.01309954932753631</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01689731397336341</v>
+        <v>0.01689731397336343</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01350873873394324</v>
+        <v>0.01350873873394326</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02898388856825365</v>
+        <v>0.0289838885682536</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01573115848652533</v>
+        <v>0.01573115848652534</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01243700658233175</v>
+        <v>0.01243700658233177</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01588836928707455</v>
+        <v>0.01588836928707458</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01426886125910165</v>
+        <v>0.01426886125910167</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01254983034044461</v>
+        <v>0.01254983034044462</v>
       </c>
       <c r="K7" t="n">
-        <v>0.009488839588298794</v>
+        <v>0.009488839588298817</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0127612343683908</v>
+        <v>0.01276123436839082</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0009384377464695451</v>
+        <v>0.0009384377464695538</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0129110198748855</v>
+        <v>0.01291101987488552</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01367812497201851</v>
+        <v>0.01367812497201853</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0125979209828808</v>
+        <v>0.01259792098288082</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.01547480063558429</v>
+        <v>0.01547480063558431</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01577342532059375</v>
+        <v>0.01577342532059377</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01291786377978985</v>
+        <v>0.01291786377978983</v>
       </c>
       <c r="T7" t="n">
         <v>0.01330967126575417</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01078915862657824</v>
+        <v>0.01078915862657826</v>
       </c>
       <c r="V7" t="n">
         <v>0.01612239391739003</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0125494016543794</v>
+        <v>0.01254940165437941</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01397652781437023</v>
+        <v>0.01397652781437024</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01431839731312325</v>
+        <v>0.01431839731312327</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.01534086058795433</v>
+        <v>0.01534086058795432</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01226265299900019</v>
+        <v>0.0122626529990002</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.008229598197798707</v>
+        <v>0.008229598197798692</v>
       </c>
     </row>
     <row r="8">
@@ -2658,58 +2658,58 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01634231523282645</v>
+        <v>0.01634231523282646</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01749268583700076</v>
+        <v>0.01749268583700077</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01647212400436901</v>
+        <v>0.016472124004369</v>
       </c>
       <c r="E8" t="n">
         <v>0.02987918693656802</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01712681631025808</v>
+        <v>0.01712681631025809</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01593150987454638</v>
+        <v>0.01593150987454639</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01715132279858762</v>
+        <v>0.01715132279858763</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01668948094869879</v>
+        <v>0.0166894809486988</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01617387127548657</v>
+        <v>0.01617387127548659</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01533838879445212</v>
+        <v>0.01533838879445215</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01625105004681895</v>
+        <v>0.01625105004681896</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01290984675820724</v>
+        <v>0.01290984675820725</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01629837975794276</v>
+        <v>0.01629837975794278</v>
       </c>
       <c r="O8" t="n">
-        <v>0.01650748418064049</v>
+        <v>0.01650748418064051</v>
       </c>
       <c r="P8" t="n">
-        <v>0.01619652375991728</v>
+        <v>0.0161965237599173</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01702984333571358</v>
+        <v>0.01702984333571361</v>
       </c>
       <c r="R8" t="n">
-        <v>0.01711968786554367</v>
+        <v>0.01711968786554368</v>
       </c>
       <c r="S8" t="n">
-        <v>0.01629295099402221</v>
+        <v>0.01629295099402223</v>
       </c>
       <c r="T8" t="n">
         <v>0.01641606588810419</v>
@@ -2718,22 +2718,22 @@
         <v>0.01568607536523338</v>
       </c>
       <c r="V8" t="n">
-        <v>0.01721706447982437</v>
+        <v>0.01721706447982436</v>
       </c>
       <c r="W8" t="n">
         <v>0.01619210234081355</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01657405869376629</v>
+        <v>0.01657405869376628</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.01669834263414403</v>
+        <v>0.01669834263414404</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.01698847125131566</v>
+        <v>0.01698847125131568</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01611103809634361</v>
+        <v>0.01611103809634363</v>
       </c>
       <c r="AB8" t="n">
         <v>0.01452991683843791</v>
@@ -2902,34 +2902,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01843966047627445</v>
+        <v>0.01843966047627446</v>
       </c>
       <c r="C2" t="n">
         <v>0.01806408486760886</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01871590207914619</v>
+        <v>0.01871590207914622</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03083567900973538</v>
+        <v>0.03083567900973542</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01822866081073084</v>
+        <v>0.01822866081073085</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01824310405546203</v>
+        <v>0.01824310405546204</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01804108708753785</v>
+        <v>0.01804108708753786</v>
       </c>
       <c r="I2" t="n">
         <v>0.01868695935603016</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01865682137381928</v>
+        <v>0.0186568213738193</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01887570486802133</v>
+        <v>0.01887570486802135</v>
       </c>
       <c r="L2" t="n">
         <v>0.01852643637664724</v>
@@ -2944,7 +2944,7 @@
         <v>0.01835132295312823</v>
       </c>
       <c r="P2" t="n">
-        <v>0.01867533456207074</v>
+        <v>0.01867533456207075</v>
       </c>
       <c r="Q2" t="n">
         <v>0.01818477743857087</v>
@@ -2956,10 +2956,10 @@
         <v>0.01858590062578323</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01848440331495844</v>
+        <v>0.01848440331495845</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0186394236026004</v>
+        <v>0.01863942360260041</v>
       </c>
       <c r="V2" t="n">
         <v>0.01820210560694321</v>
@@ -2968,19 +2968,19 @@
         <v>0.01859957617349575</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01814778621419413</v>
+        <v>0.01814778621419414</v>
       </c>
       <c r="Y2" t="n">
         <v>0.01886753080939606</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.01825226922055411</v>
+        <v>0.01825226922055412</v>
       </c>
       <c r="AA2" t="n">
         <v>0.0187908667990609</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.01859627632755759</v>
+        <v>0.0185962763275576</v>
       </c>
     </row>
     <row r="3">
@@ -2990,82 +2990,82 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01817786422568064</v>
+        <v>0.01817786422568065</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01827383423167579</v>
+        <v>0.0182738342316758</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01817786422568064</v>
+        <v>0.01817786422568065</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03107021345110367</v>
+        <v>0.03107021345110366</v>
       </c>
       <c r="F3" t="n">
         <v>0.01822444860035939</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01775845942230537</v>
+        <v>0.01775845942230538</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01817786422568064</v>
+        <v>0.01817786422568065</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01817786422568064</v>
+        <v>0.01817786422568065</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01815700831786114</v>
+        <v>0.01815700831786115</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01820302916603018</v>
+        <v>0.01820302916603019</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01817786422568064</v>
+        <v>0.01817786422568065</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01817786422568064</v>
+        <v>0.01817786422568065</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01817786422568064</v>
+        <v>0.01817786422568065</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01817786422568064</v>
+        <v>0.01817786422568065</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01817786422568064</v>
+        <v>0.01817786422568065</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01817786422568064</v>
+        <v>0.01817786422568065</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01808230584100252</v>
+        <v>0.01808230584100253</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01817786422568064</v>
+        <v>0.01817786422568065</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01817786422568064</v>
+        <v>0.01817786422568065</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01817786422568064</v>
+        <v>0.01817786422568065</v>
       </c>
       <c r="V3" t="n">
         <v>0.01817898390749696</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01817786422568064</v>
+        <v>0.01817786422568065</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01760222656770894</v>
+        <v>0.01760222656770895</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01817786422568064</v>
+        <v>0.01817786422568065</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01818472168804359</v>
+        <v>0.0181847216880436</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.01817786422568064</v>
+        <v>0.01817786422568065</v>
       </c>
       <c r="AB3" t="n">
         <v>0.01747608409926378</v>
@@ -3078,85 +3078,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1665995135667721</v>
+        <v>0.1665995135667726</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05985029388940096</v>
+        <v>0.05985029388940101</v>
       </c>
       <c r="D4" t="n">
         <v>0.2560893254856332</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1001641120108674</v>
+        <v>0.1001641120108672</v>
       </c>
       <c r="F4" t="n">
-        <v>0.11653612742287</v>
+        <v>0.1165361274228701</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2094389035011886</v>
+        <v>0.2094389035011889</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0826515872114281</v>
+        <v>0.08265158721142814</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2524629918922247</v>
+        <v>0.2524629918922244</v>
       </c>
       <c r="J4" t="n">
         <v>0.2340868225655789</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2613966842130223</v>
+        <v>0.2613966842130222</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1969518570297036</v>
+        <v>0.1969518570297037</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6932655167888995</v>
+        <v>0.6932655167888991</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1620204503010219</v>
+        <v>0.162020450301022</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1389657296779607</v>
+        <v>0.1389657296779609</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2209640598734961</v>
+        <v>0.2209640598734966</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1126838872719953</v>
+        <v>0.1126838872719954</v>
       </c>
       <c r="R4" t="n">
-        <v>0.08108431887963125</v>
+        <v>0.08108431887963129</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2014420710340206</v>
+        <v>0.2014420710340208</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1971907070980642</v>
+        <v>0.1971907070980647</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2192021206777227</v>
+        <v>0.2192021206777226</v>
       </c>
       <c r="V4" t="n">
-        <v>0.105862631217904</v>
+        <v>0.1058626312179047</v>
       </c>
       <c r="W4" t="n">
-        <v>0.217975211843045</v>
+        <v>0.2179752118430448</v>
       </c>
       <c r="X4" t="n">
-        <v>0.241786387639081</v>
+        <v>0.2417863876390813</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.2834129962022776</v>
+        <v>0.2834129962022786</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.1153100669357401</v>
+        <v>0.11531006693574</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.2666318150242094</v>
+        <v>0.2666318150242096</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.4174738706390659</v>
+        <v>0.4174738706390663</v>
       </c>
     </row>
     <row r="5">
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01748450504839115</v>
+        <v>0.01748450504839123</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0261430918180377</v>
+        <v>0.02614309181803773</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0261430918180377</v>
+        <v>0.02614309181803773</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02153264977575677</v>
+        <v>0.02153264977575679</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01883341167191998</v>
+        <v>0.01883341167192002</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02793850619009517</v>
+        <v>0.02793850619009531</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0261430918180377</v>
+        <v>0.02614309181803773</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0261430918180377</v>
+        <v>0.02614309181803773</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02612252697435979</v>
+        <v>0.02612252697435985</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0261430918180377</v>
+        <v>0.02614309181803773</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02614309181803771</v>
+        <v>0.02614309181803774</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02614309181804114</v>
+        <v>0.02614309181804118</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1620204503010219</v>
+        <v>0.01943123852125361</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02127571408468229</v>
+        <v>0.02127571408468235</v>
       </c>
       <c r="P5" t="n">
-        <v>0.02082358855536978</v>
+        <v>0.02082358855536981</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01578289512585185</v>
+        <v>0.01578289512585193</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0261430918180377</v>
+        <v>0.02614309181803773</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0261430918180377</v>
+        <v>0.02614309181803773</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0261430918180377</v>
+        <v>0.02614309181803773</v>
       </c>
       <c r="U5" t="n">
-        <v>0.02191132297391306</v>
+        <v>0.02191132297391312</v>
       </c>
       <c r="V5" t="n">
-        <v>0.02363860318517253</v>
+        <v>0.02363860318517256</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02614479347730401</v>
+        <v>0.02614479347730406</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01657647180747463</v>
+        <v>0.01657647180747467</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.03474249933757503</v>
+        <v>0.03474249933757514</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.01732366735390651</v>
+        <v>0.01732366735390653</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0261430918180377</v>
+        <v>0.02614309181803773</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.03518770971715143</v>
+        <v>0.03518770971715148</v>
       </c>
     </row>
     <row r="6">
@@ -3254,85 +3254,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02248893689020755</v>
+        <v>0.02248893689020756</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02764162162254144</v>
+        <v>0.02764162162254146</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02764162162254144</v>
+        <v>0.02764162162254146</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02645240068996088</v>
+        <v>0.02645240068996089</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0157632809397022</v>
+        <v>0.01576328093970222</v>
       </c>
       <c r="G6" t="n">
         <v>0.02764161861452828</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02764162162254144</v>
+        <v>0.02764162162254146</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02764162162254144</v>
+        <v>0.02764162162254146</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02762105677886355</v>
+        <v>0.02762105677886357</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02764162162254144</v>
+        <v>0.02764162162254146</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02764162162254144</v>
+        <v>0.02764162162254148</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02764162162254144</v>
+        <v>0.02764162162254146</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1620204503010219</v>
+        <v>0.02764162162254146</v>
       </c>
       <c r="O6" t="n">
         <v>0.02934921059110817</v>
       </c>
       <c r="P6" t="n">
-        <v>0.02972058254866921</v>
+        <v>0.02972058254866924</v>
       </c>
       <c r="Q6" t="n">
         <v>0.02764161861452828</v>
       </c>
       <c r="R6" t="n">
-        <v>0.02764162162254144</v>
+        <v>0.02764162162254146</v>
       </c>
       <c r="S6" t="n">
-        <v>0.02764162162254144</v>
+        <v>0.02764162162254146</v>
       </c>
       <c r="T6" t="n">
-        <v>0.02764162162254144</v>
+        <v>0.02764162162254146</v>
       </c>
       <c r="U6" t="n">
-        <v>0.02764162162254144</v>
+        <v>0.02764162162254146</v>
       </c>
       <c r="V6" t="n">
-        <v>0.03345593787159764</v>
+        <v>0.03345593787159767</v>
       </c>
       <c r="W6" t="n">
-        <v>0.02764162162254144</v>
+        <v>0.02764162162254146</v>
       </c>
       <c r="X6" t="n">
-        <v>0.02764162162254144</v>
+        <v>0.02764162162254148</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.02764162162254144</v>
+        <v>0.02764162162254146</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.02453500972909932</v>
+        <v>0.02453500972909937</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.02764162162254144</v>
+        <v>0.02764162162254146</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.02764162162254144</v>
+        <v>0.02764162162254146</v>
       </c>
     </row>
     <row r="7">
@@ -3342,28 +3342,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01420364407971787</v>
+        <v>0.01420364407971789</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01707320253494406</v>
+        <v>0.01707320253494408</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01264688673737685</v>
+        <v>0.01264688673737686</v>
       </c>
       <c r="E7" t="n">
         <v>0.02884491732156677</v>
       </c>
       <c r="F7" t="n">
-        <v>0.015808741713354</v>
+        <v>0.01580874171335401</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01267632338678719</v>
+        <v>0.0126763233867872</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01661033375302409</v>
+        <v>0.01661033375302408</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01282647004655908</v>
+        <v>0.01282647004655907</v>
       </c>
       <c r="J7" t="n">
         <v>0.01281552343529359</v>
@@ -3375,43 +3375,43 @@
         <v>0.01371562691719325</v>
       </c>
       <c r="M7" t="n">
-        <v>0.003189359422817654</v>
+        <v>0.003189359422817669</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01467040111716645</v>
+        <v>0.01467040111716646</v>
       </c>
       <c r="O7" t="n">
         <v>0.0147254153547337</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01279092754565151</v>
+        <v>0.01279092754565152</v>
       </c>
       <c r="Q7" t="n">
         <v>0.01575175859140508</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01651254384704995</v>
+        <v>0.01651254384704996</v>
       </c>
       <c r="S7" t="n">
         <v>0.0133486158289575</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01400555383535711</v>
+        <v>0.01400555383535712</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01304253555091787</v>
+        <v>0.01304253555091788</v>
       </c>
       <c r="V7" t="n">
-        <v>0.01561914093429198</v>
+        <v>0.01561914093429196</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01329141519538994</v>
+        <v>0.01329141519538995</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0123126629460638</v>
+        <v>0.01231266294606378</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01172041049666563</v>
+        <v>0.01172041049666565</v>
       </c>
       <c r="Z7" t="n">
         <v>0.01536574047817552</v>
@@ -3420,7 +3420,7 @@
         <v>0.01216731876331815</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.008891317849324213</v>
+        <v>0.008891317849324201</v>
       </c>
     </row>
     <row r="8">
@@ -3430,61 +3430,61 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01663137764477325</v>
+        <v>0.01663137764477327</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01751779361940971</v>
+        <v>0.01751779361940972</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01619928969578859</v>
+        <v>0.0161992896957886</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02982316217919807</v>
+        <v>0.02982316217919811</v>
       </c>
       <c r="F8" t="n">
         <v>0.01712950647874232</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01593071596349467</v>
+        <v>0.01593071596349468</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01732785572705592</v>
+        <v>0.01732785572705591</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01625205795064848</v>
+        <v>0.01625205795064849</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01622642872994875</v>
+        <v>0.01622642872994876</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01599038740986808</v>
+        <v>0.01599038740986809</v>
       </c>
       <c r="L8" t="n">
         <v>0.01649610418097894</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01352042983834391</v>
+        <v>0.01352042983834392</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01677201199996603</v>
+        <v>0.01677201199996605</v>
       </c>
       <c r="O8" t="n">
-        <v>0.01678044771454563</v>
+        <v>0.01678044771454565</v>
       </c>
       <c r="P8" t="n">
         <v>0.01622426120550892</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01708089164343555</v>
+        <v>0.01708089164343557</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0172391369921114</v>
+        <v>0.01723913699211142</v>
       </c>
       <c r="S8" t="n">
-        <v>0.01638857721537269</v>
+        <v>0.0163885772153727</v>
       </c>
       <c r="T8" t="n">
-        <v>0.01658598879099694</v>
+        <v>0.01658598879099696</v>
       </c>
       <c r="U8" t="n">
         <v>0.01630283269026189</v>
@@ -3493,22 +3493,22 @@
         <v>0.01703736889639941</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01637622629252438</v>
+        <v>0.01637622629252439</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01574101790950651</v>
+        <v>0.01574101790950653</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0159293687840102</v>
+        <v>0.01592936878401021</v>
       </c>
       <c r="Z8" t="n">
         <v>0.01696962378650407</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.0160560494592141</v>
+        <v>0.01605604945921411</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.01469018032580832</v>
+        <v>0.01469018032580834</v>
       </c>
     </row>
   </sheetData>
@@ -3677,19 +3677,19 @@
         <v>0.01762239989738098</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01731753261255504</v>
+        <v>0.01731753261255507</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01768200885641892</v>
+        <v>0.01768200885641895</v>
       </c>
       <c r="E2" t="n">
         <v>0.03062852580250827</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01757907873318694</v>
+        <v>0.01757907873318697</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01716590563294719</v>
+        <v>0.0171659056329472</v>
       </c>
       <c r="H2" t="n">
         <v>0.01731153201609973</v>
@@ -3698,61 +3698,61 @@
         <v>0.01790327828556246</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01788361607381408</v>
+        <v>0.01788361607381407</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01834369721162101</v>
+        <v>0.01834369721162103</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01771815504140871</v>
+        <v>0.01771815504140869</v>
       </c>
       <c r="M2" t="n">
         <v>0.01918450875844273</v>
       </c>
       <c r="N2" t="n">
-        <v>0.01744490669521728</v>
+        <v>0.01744490669521731</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01759880744155695</v>
+        <v>0.01759880744155699</v>
       </c>
       <c r="P2" t="n">
-        <v>0.01785273788939886</v>
+        <v>0.0178527378893989</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.01743998133968592</v>
+        <v>0.01743998133968593</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01728810671140726</v>
+        <v>0.01728810671140728</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0178112197813695</v>
+        <v>0.01781121978136956</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01781679569728531</v>
+        <v>0.01781679569728534</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01790696014044503</v>
+        <v>0.01790696014044505</v>
       </c>
       <c r="V2" t="n">
-        <v>0.01723241078188192</v>
+        <v>0.01723241078188193</v>
       </c>
       <c r="W2" t="n">
-        <v>0.01757980958257279</v>
+        <v>0.01757980958257282</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01778771183192426</v>
+        <v>0.01778771183192431</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.01866857513325001</v>
+        <v>0.01866857513324999</v>
       </c>
       <c r="Z2" t="n">
         <v>0.01746516512445055</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.01814801837438514</v>
+        <v>0.01814801837438519</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.01775452853334219</v>
+        <v>0.0177545285333422</v>
       </c>
     </row>
     <row r="3">
@@ -3762,85 +3762,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01744373108442671</v>
+        <v>0.01744373108442673</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01753932591990821</v>
+        <v>0.01753932591990822</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01744373108442671</v>
+        <v>0.01744373108442673</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0309806609937396</v>
+        <v>0.03098066099373961</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01750555735013876</v>
+        <v>0.01750555735013878</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01672417697596518</v>
+        <v>0.0167241769759652</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01744373108442671</v>
+        <v>0.01744373108442673</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01744373108442671</v>
+        <v>0.01744373108442673</v>
       </c>
       <c r="J3" t="n">
         <v>0.0174340022188071</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01747599153320207</v>
+        <v>0.01747599153320208</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01744373108442671</v>
+        <v>0.01744373108442673</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01744373108442671</v>
+        <v>0.01744373108442673</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01744373108442671</v>
+        <v>0.01744373108442673</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01744373108442671</v>
+        <v>0.01744373108442673</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01744373108442671</v>
+        <v>0.01744373108442673</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01744373108442671</v>
+        <v>0.01744373108442673</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01725952508983292</v>
+        <v>0.01725952508983294</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01744373108442671</v>
+        <v>0.01744373108442673</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01744373108442671</v>
+        <v>0.01744373108442673</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01744373108442671</v>
+        <v>0.01744373108442673</v>
       </c>
       <c r="V3" t="n">
         <v>0.01701364122718824</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01744373108442671</v>
+        <v>0.01744373108442673</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01717983011958036</v>
+        <v>0.01717983011958037</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01744373108442671</v>
+        <v>0.01744373108442673</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01745047845048559</v>
+        <v>0.01745047845048561</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.01744373108442671</v>
+        <v>0.01744373108442673</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01674195095800985</v>
+        <v>0.01674195095800986</v>
       </c>
     </row>
     <row r="4">
@@ -3850,82 +3850,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.139937249697413</v>
+        <v>0.1399372496974129</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05370805588126099</v>
+        <v>0.053708055881261</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1678341069407983</v>
+        <v>0.1678341069407987</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06712877328715516</v>
+        <v>0.06712877328715514</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1307744397865629</v>
+        <v>0.1307744397865631</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1845792613242026</v>
+        <v>0.1845792613242021</v>
       </c>
       <c r="H4" t="n">
-        <v>0.08080361365968552</v>
+        <v>0.08080361365968571</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2319993009225901</v>
+        <v>0.2319993009225902</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2131784730620094</v>
+        <v>0.2131784730620095</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3043742299011618</v>
+        <v>0.3043742299011625</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1692753038458076</v>
+        <v>0.169275303845808</v>
       </c>
       <c r="M4" t="n">
-        <v>0.552952038214753</v>
+        <v>0.5529520382147536</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1104477977541438</v>
+        <v>0.1104477977541437</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1323941148608753</v>
+        <v>0.1323941148608754</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1909495656709618</v>
+        <v>0.1909495656709617</v>
       </c>
       <c r="Q4" t="n">
         <v>0.1046526511497115</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1185393392254005</v>
+        <v>0.1185393392254006</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1865582555024012</v>
+        <v>0.1865582555024013</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2119377539279917</v>
+        <v>0.211937753927992</v>
       </c>
       <c r="U4" t="n">
-        <v>0.209483231970671</v>
+        <v>0.2094832319706707</v>
       </c>
       <c r="V4" t="n">
-        <v>0.14398542355022</v>
+        <v>0.1439854235502202</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1427058412383797</v>
+        <v>0.1427058412383799</v>
       </c>
       <c r="X4" t="n">
-        <v>0.2539158144512676</v>
+        <v>0.2539158144512677</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4231474580196712</v>
+        <v>0.423147458019671</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.09622990687941284</v>
+        <v>0.09622990687941295</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.2883983330478461</v>
+        <v>0.2883983330478466</v>
       </c>
       <c r="AB4" t="n">
         <v>0.3785741787206808</v>
@@ -3938,85 +3938,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01745096132706244</v>
+        <v>0.01745096132706241</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02600025736425681</v>
+        <v>0.02600025736425682</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02600025736425681</v>
+        <v>0.02600025736425682</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0214480094131223</v>
+        <v>0.02144800941312238</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01878284173178748</v>
+        <v>0.01878284173178752</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02777300959097918</v>
+        <v>0.0277730095909792</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02600025736425681</v>
+        <v>0.02600025736425682</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02600025736425681</v>
+        <v>0.02600025736425682</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0259813461268444</v>
+        <v>0.02598134612684449</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02600025736425681</v>
+        <v>0.02600025736425682</v>
       </c>
       <c r="L5" t="n">
         <v>0.02600025736425682</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02600025736426183</v>
+        <v>0.02600025736426182</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1104477977541438</v>
+        <v>0.01937312266907395</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02119431682520428</v>
+        <v>0.02119431682520431</v>
       </c>
       <c r="P5" t="n">
         <v>0.02074789813137533</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01577082952787746</v>
+        <v>0.01577082952787756</v>
       </c>
       <c r="R5" t="n">
-        <v>0.02600025736425681</v>
+        <v>0.02600025736425682</v>
       </c>
       <c r="S5" t="n">
-        <v>0.02600025736425681</v>
+        <v>0.02600025736425682</v>
       </c>
       <c r="T5" t="n">
-        <v>0.02600025736425681</v>
+        <v>0.02600025736425682</v>
       </c>
       <c r="U5" t="n">
-        <v>0.02182193639319402</v>
+        <v>0.02182193639319403</v>
       </c>
       <c r="V5" t="n">
-        <v>0.02353615769367274</v>
+        <v>0.02353615769367276</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02600193754480279</v>
+        <v>0.02600193754480277</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01655438949673205</v>
+        <v>0.01655438949673213</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.03449117840838437</v>
+        <v>0.03449117840838436</v>
       </c>
       <c r="Z5" t="n">
         <v>0.01729215376403903</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.02600025736425681</v>
+        <v>0.02600025736425682</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.03493071195462092</v>
+        <v>0.0349307119546209</v>
       </c>
     </row>
     <row r="6">
@@ -4026,85 +4026,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02150844130094538</v>
+        <v>0.02150844130094543</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02635167183111137</v>
+        <v>0.02635167183111138</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02635167183111137</v>
+        <v>0.02635167183111138</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0252338721858305</v>
+        <v>0.02523387218583054</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01518670666048171</v>
+        <v>0.01518670666048174</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02635166949870573</v>
+        <v>0.02635166949870572</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02635167183111137</v>
+        <v>0.02635167183111138</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02635167183111137</v>
+        <v>0.02635167183111138</v>
       </c>
       <c r="J6" t="n">
         <v>0.02633276059369902</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02635167183111137</v>
+        <v>0.02635167183111138</v>
       </c>
       <c r="L6" t="n">
+        <v>0.02635167183111139</v>
+      </c>
+      <c r="M6" t="n">
         <v>0.02635167183111138</v>
       </c>
-      <c r="M6" t="n">
-        <v>0.02635167183111137</v>
-      </c>
       <c r="N6" t="n">
-        <v>0.1104477977541438</v>
+        <v>0.02635167183111138</v>
       </c>
       <c r="O6" t="n">
-        <v>0.02795670898177831</v>
+        <v>0.02795670898177835</v>
       </c>
       <c r="P6" t="n">
-        <v>0.02830577753150602</v>
+        <v>0.02830577753150605</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.02635166949870573</v>
+        <v>0.02635166949870572</v>
       </c>
       <c r="R6" t="n">
-        <v>0.02635167183111137</v>
+        <v>0.02635167183111138</v>
       </c>
       <c r="S6" t="n">
-        <v>0.02635167183111137</v>
+        <v>0.02635167183111138</v>
       </c>
       <c r="T6" t="n">
-        <v>0.02635167183111137</v>
+        <v>0.02635167183111138</v>
       </c>
       <c r="U6" t="n">
-        <v>0.02635167183111137</v>
+        <v>0.02635167183111138</v>
       </c>
       <c r="V6" t="n">
-        <v>0.03181929020453696</v>
+        <v>0.03181929020453702</v>
       </c>
       <c r="W6" t="n">
-        <v>0.02635167183111137</v>
+        <v>0.02635167183111138</v>
       </c>
       <c r="X6" t="n">
+        <v>0.02635167183111139</v>
+      </c>
+      <c r="Y6" t="n">
         <v>0.02635167183111138</v>
       </c>
-      <c r="Y6" t="n">
-        <v>0.02635167183111137</v>
-      </c>
       <c r="Z6" t="n">
-        <v>0.02343163357211152</v>
+        <v>0.02343163357211153</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.02635167183111137</v>
+        <v>0.02635167183111138</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.02635167183111137</v>
+        <v>0.02635167183111138</v>
       </c>
     </row>
     <row r="7">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01403719591451299</v>
+        <v>0.01403719591451303</v>
       </c>
       <c r="C7" t="n">
         <v>0.01648161442339001</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01374062571319656</v>
+        <v>0.01374062571319655</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02946359782216078</v>
+        <v>0.02946359782216082</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01474986107110229</v>
+        <v>0.01474986107110231</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01212410931787685</v>
+        <v>0.01212410931787689</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01592109727783577</v>
+        <v>0.01592109727783578</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01245390527906395</v>
+        <v>0.01245390527906398</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01246463149196093</v>
+        <v>0.01246463149196091</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01005919835182625</v>
+        <v>0.01005919835182623</v>
       </c>
       <c r="L7" t="n">
         <v>0.01349253209208214</v>
       </c>
       <c r="M7" t="n">
-        <v>0.004987165816582701</v>
+        <v>0.004987165816582696</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01511963654949189</v>
+        <v>0.01511963654949191</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01417398634268647</v>
+        <v>0.0141739863426865</v>
       </c>
       <c r="P7" t="n">
         <v>0.01265741063229623</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.01515244603184469</v>
+        <v>0.0151524460318447</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01488711877826313</v>
+        <v>0.01488711877826314</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01292788269983364</v>
+        <v>0.01292788269983362</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01295396499736888</v>
+        <v>0.01295396499736885</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01237128041857028</v>
+        <v>0.0123712804185703</v>
       </c>
       <c r="V7" t="n">
-        <v>0.01340628245698613</v>
+        <v>0.01340628245698614</v>
       </c>
       <c r="W7" t="n">
         <v>0.01431564833785322</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01143944250575497</v>
+        <v>0.01143944250575499</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.007905221428838006</v>
+        <v>0.007905221428838007</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.01501874764625356</v>
+        <v>0.01501874764625357</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0109673691076151</v>
+        <v>0.01096736910761509</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.008859398398201223</v>
+        <v>0.008859398398201244</v>
       </c>
     </row>
     <row r="8">
@@ -4202,70 +4202,70 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01607241553908673</v>
+        <v>0.01607241553908679</v>
       </c>
       <c r="C8" t="n">
         <v>0.01683627051091274</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0159970841114126</v>
+        <v>0.01599708411141261</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0299382572248465</v>
+        <v>0.02993825722484646</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01632522814434238</v>
+        <v>0.0163252281443424</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01507286018897118</v>
+        <v>0.0150728601889712</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01661872878175484</v>
+        <v>0.01661872878175483</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01563289164249106</v>
+        <v>0.01563289164249107</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01562253655665421</v>
+        <v>0.01562253655665419</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01496903267817753</v>
+        <v>0.01496903267817754</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01592034690816785</v>
+        <v>0.01592034690816782</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01351673186485557</v>
+        <v>0.01351673186485558</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01638743627537216</v>
+        <v>0.01638743627537213</v>
       </c>
       <c r="O8" t="n">
-        <v>0.01611106316400699</v>
+        <v>0.016111063164007</v>
       </c>
       <c r="P8" t="n">
-        <v>0.01567494683058127</v>
+        <v>0.01567494683058128</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01639743933886888</v>
+        <v>0.01639743933886885</v>
       </c>
       <c r="R8" t="n">
-        <v>0.01620865427923268</v>
+        <v>0.01620865427923269</v>
       </c>
       <c r="S8" t="n">
-        <v>0.01575649437522476</v>
+        <v>0.01575649437522477</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0157739378196384</v>
+        <v>0.01577393781963842</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01559897892253922</v>
+        <v>0.01559897892253924</v>
       </c>
       <c r="V8" t="n">
         <v>0.01559105104546969</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01615652196427359</v>
+        <v>0.01615652196427361</v>
       </c>
       <c r="X8" t="n">
         <v>0.01517581717410388</v>
@@ -4274,13 +4274,13 @@
         <v>0.01432852284253043</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.01635871985905868</v>
+        <v>0.01635871985905867</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01520125303599489</v>
+        <v>0.01520125303599487</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.01416794199842472</v>
+        <v>0.01416794199842474</v>
       </c>
     </row>
   </sheetData>
@@ -4452,16 +4452,16 @@
         <v>0.01743493651586019</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01773960102795214</v>
+        <v>0.01773960102795215</v>
       </c>
       <c r="E2" t="n">
         <v>0.03044678528719304</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01751217379964775</v>
+        <v>0.01751217379964777</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01725672987640372</v>
+        <v>0.01725672987640373</v>
       </c>
       <c r="H2" t="n">
         <v>0.01769618698864655</v>
@@ -4470,22 +4470,22 @@
         <v>0.01767594209464683</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0176640566266436</v>
+        <v>0.01766405662664361</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01801569433558185</v>
+        <v>0.01801569433558184</v>
       </c>
       <c r="L2" t="n">
         <v>0.01789772215571629</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01829325610335449</v>
+        <v>0.01829325610335448</v>
       </c>
       <c r="N2" t="n">
         <v>0.01787093117815633</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01753690135123178</v>
+        <v>0.01753690135123179</v>
       </c>
       <c r="P2" t="n">
         <v>0.01772868037070847</v>
@@ -4497,7 +4497,7 @@
         <v>0.01773330009857465</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01769447304176602</v>
+        <v>0.01769447304176603</v>
       </c>
       <c r="T2" t="n">
         <v>0.01757345290741221</v>
@@ -4509,7 +4509,7 @@
         <v>0.01750789744117775</v>
       </c>
       <c r="W2" t="n">
-        <v>0.01787226452042663</v>
+        <v>0.01787226452042665</v>
       </c>
       <c r="X2" t="n">
         <v>0.01774393670143258</v>
@@ -4518,13 +4518,13 @@
         <v>0.01747837807932612</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.01764813125457759</v>
+        <v>0.01764813125457758</v>
       </c>
       <c r="AA2" t="n">
         <v>0.01783719181643192</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0170946877663417</v>
+        <v>0.01709468776634171</v>
       </c>
     </row>
     <row r="3">
@@ -4537,19 +4537,19 @@
         <v>0.01767674670341959</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01776812861951774</v>
+        <v>0.01776812861951773</v>
       </c>
       <c r="D3" t="n">
         <v>0.01767674670341959</v>
       </c>
       <c r="E3" t="n">
-        <v>0.030790004689595</v>
+        <v>0.03079000468959504</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01770975426968183</v>
+        <v>0.01770975426968182</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01732387143523276</v>
+        <v>0.01732387143523275</v>
       </c>
       <c r="H3" t="n">
         <v>0.01767674670341959</v>
@@ -4558,10 +4558,10 @@
         <v>0.01767674670341959</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01766241183986051</v>
+        <v>0.0176624118398605</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01769448807811294</v>
+        <v>0.01769448807811293</v>
       </c>
       <c r="L3" t="n">
         <v>0.01767674670341959</v>
@@ -4582,7 +4582,7 @@
         <v>0.01767674670341959</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01768007166139554</v>
+        <v>0.01768007166139553</v>
       </c>
       <c r="S3" t="n">
         <v>0.01767674670341959</v>
@@ -4606,13 +4606,13 @@
         <v>0.01767674670341959</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01768082497799864</v>
+        <v>0.01768082497799863</v>
       </c>
       <c r="AA3" t="n">
         <v>0.01767674670341959</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01697496657700273</v>
+        <v>0.01697496657700272</v>
       </c>
     </row>
     <row r="4">
@@ -4622,22 +4622,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.05914432614722782</v>
+        <v>0.05914432614722781</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0298250491467378</v>
+        <v>0.02982504914673776</v>
       </c>
       <c r="D4" t="n">
         <v>0.1385365431597194</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07729533613251723</v>
+        <v>0.07729533613251718</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06637065459767508</v>
+        <v>0.06637065459767504</v>
       </c>
       <c r="G4" t="n">
-        <v>0.08070886207790888</v>
+        <v>0.08070886207790887</v>
       </c>
       <c r="H4" t="n">
         <v>0.1321034180847863</v>
@@ -4652,55 +4652,55 @@
         <v>0.1932938917877216</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1575626043083581</v>
+        <v>0.1575626043083582</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2707728968221596</v>
+        <v>0.2707728968221597</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1678703982097322</v>
+        <v>0.1678703982097321</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0719292143369016</v>
+        <v>0.07192921433690171</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1231282712105112</v>
+        <v>0.1231282712105109</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1097162101701388</v>
+        <v>0.1097162101701387</v>
       </c>
       <c r="R4" t="n">
-        <v>0.14087596279772</v>
+        <v>0.1408759627977199</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1031372757442423</v>
+        <v>0.1031372757442422</v>
       </c>
       <c r="T4" t="n">
-        <v>0.08952600660601719</v>
+        <v>0.0895260066060171</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1407075344616179</v>
+        <v>0.140707534461618</v>
       </c>
       <c r="V4" t="n">
-        <v>0.05554550839174644</v>
+        <v>0.05554550839174639</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1705844440320419</v>
+        <v>0.1705844440320421</v>
       </c>
       <c r="X4" t="n">
         <v>0.1501437074130696</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.06312881156799587</v>
+        <v>0.06312881156799574</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.09774315501677469</v>
+        <v>0.0977431550167747</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.1606913326034622</v>
+        <v>0.1606913326034621</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1408901403272981</v>
+        <v>0.140890140327298</v>
       </c>
     </row>
     <row r="5">
@@ -4710,85 +4710,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01708952364380346</v>
+        <v>0.01708952364380348</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02569831932618569</v>
+        <v>0.02569831932618571</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02569831932618569</v>
+        <v>0.02569831932618571</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02111438956909204</v>
+        <v>0.02111438956909202</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01843067339787003</v>
+        <v>0.01843067339787005</v>
       </c>
       <c r="G5" t="n">
         <v>0.02748340919194862</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02569831932618569</v>
+        <v>0.02569831932618571</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02569831932618569</v>
+        <v>0.02569831932618571</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02567845808801974</v>
+        <v>0.02567845808801973</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02569831932618569</v>
+        <v>0.02569831932618571</v>
       </c>
       <c r="L5" t="n">
         <v>0.02569831932618569</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02569831932618614</v>
+        <v>0.02569831932618616</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1678703982097322</v>
+        <v>0.01902506245193417</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02085893138340476</v>
+        <v>0.02085893138340473</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0204094057958676</v>
+        <v>0.02040940579586761</v>
       </c>
       <c r="Q5" t="n">
         <v>0.01539769880628723</v>
       </c>
       <c r="R5" t="n">
-        <v>0.02569831932618569</v>
+        <v>0.02569831932618571</v>
       </c>
       <c r="S5" t="n">
-        <v>0.02569831932618569</v>
+        <v>0.02569831932618571</v>
       </c>
       <c r="T5" t="n">
-        <v>0.02569831932618569</v>
+        <v>0.02569831932618571</v>
       </c>
       <c r="U5" t="n">
-        <v>0.02149081755562635</v>
+        <v>0.02149081755562633</v>
       </c>
       <c r="V5" t="n">
-        <v>0.02321172938912145</v>
+        <v>0.02321172938912143</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02570001120022871</v>
+        <v>0.02570001120022874</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01618671203592257</v>
+        <v>0.01618671203592255</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.03424816032725551</v>
+        <v>0.03424816032725552</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.01692961084430715</v>
+        <v>0.01692961084430714</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.02569831932618569</v>
+        <v>0.02569831932618571</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0346909262713392</v>
+        <v>0.03469092627133916</v>
       </c>
     </row>
     <row r="6">
@@ -4798,7 +4798,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02191030277767835</v>
+        <v>0.02191030277767833</v>
       </c>
       <c r="C6" t="n">
         <v>0.0269905214451376</v>
@@ -4807,13 +4807,13 @@
         <v>0.0269905214451376</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02581802863717735</v>
+        <v>0.02581802863717736</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0152792293006054</v>
+        <v>0.01527922930060541</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02699052266543147</v>
+        <v>0.02699052266543148</v>
       </c>
       <c r="H6" t="n">
         <v>0.0269905214451376</v>
@@ -4822,7 +4822,7 @@
         <v>0.0269905214451376</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02697066020697155</v>
+        <v>0.02697066020697157</v>
       </c>
       <c r="K6" t="n">
         <v>0.0269905214451376</v>
@@ -4834,16 +4834,16 @@
         <v>0.0269905214451376</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1678703982097322</v>
+        <v>0.0269905214451376</v>
       </c>
       <c r="O6" t="n">
-        <v>0.02867410088425335</v>
+        <v>0.0286741008842534</v>
       </c>
       <c r="P6" t="n">
-        <v>0.02904025026150877</v>
+        <v>0.02904025026150882</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.02699052266543147</v>
+        <v>0.02699052266543148</v>
       </c>
       <c r="R6" t="n">
         <v>0.0269905214451376</v>
@@ -4870,7 +4870,7 @@
         <v>0.0269905214451376</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.02392760182389479</v>
+        <v>0.02392760182389482</v>
       </c>
       <c r="AA6" t="n">
         <v>0.0269905214451376</v>
@@ -4889,52 +4889,52 @@
         <v>0.01645560584674558</v>
       </c>
       <c r="C7" t="n">
-        <v>0.017312265180554</v>
+        <v>0.01731226518055399</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01494769054279982</v>
+        <v>0.01494769054279984</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0292059774611845</v>
+        <v>0.02920597746118455</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01649553295052856</v>
+        <v>0.01649553295052855</v>
       </c>
       <c r="G7" t="n">
         <v>0.01550729552284505</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0152187305162647</v>
+        <v>0.01521873051626471</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01532499904131234</v>
+        <v>0.01532499904131235</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0152735354278995</v>
+        <v>0.01527353542789951</v>
       </c>
       <c r="K7" t="n">
         <v>0.01343713567919257</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01398753349821625</v>
+        <v>0.01398753349821624</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01172733003595676</v>
+        <v>0.01172733003595675</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01416358904629192</v>
+        <v>0.01416358904629191</v>
       </c>
       <c r="O7" t="n">
         <v>0.01610906114430926</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01496447874586355</v>
+        <v>0.01496447874586357</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.01541722275102691</v>
+        <v>0.0154172227510269</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01501628870593566</v>
+        <v>0.01501628870593569</v>
       </c>
       <c r="S7" t="n">
         <v>0.01518110516958407</v>
@@ -4943,28 +4943,28 @@
         <v>0.01592202807280862</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01462525379829187</v>
+        <v>0.01462525379829188</v>
       </c>
       <c r="V7" t="n">
-        <v>0.01658467430380717</v>
+        <v>0.01658467430380716</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01414395114816251</v>
+        <v>0.0141439511481625</v>
       </c>
       <c r="X7" t="n">
         <v>0.01461302214384128</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01647062184182134</v>
+        <v>0.01647062184182135</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.01547775072977731</v>
+        <v>0.0154777507297773</v>
       </c>
       <c r="AA7" t="n">
         <v>0.01435365932978519</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01426766615700932</v>
+        <v>0.01426766615700931</v>
       </c>
     </row>
     <row r="8">
@@ -4974,22 +4974,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01692331550659744</v>
+        <v>0.01692331550659745</v>
       </c>
       <c r="C8" t="n">
         <v>0.0172275171983811</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01649787177788422</v>
+        <v>0.01649787177788421</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02972604785027097</v>
+        <v>0.02972604785027098</v>
       </c>
       <c r="F8" t="n">
         <v>0.01695969922993929</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01643018204718337</v>
+        <v>0.01643018204718336</v>
       </c>
       <c r="H8" t="n">
         <v>0.01657778179025826</v>
@@ -4998,19 +4998,19 @@
         <v>0.0166058894138129</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01657711024630394</v>
+        <v>0.01657711024630393</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01607858542669598</v>
+        <v>0.01607858542669599</v>
       </c>
       <c r="L8" t="n">
         <v>0.01621911839052389</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01558625255999291</v>
+        <v>0.0155862525599929</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01627243324839407</v>
+        <v>0.01627243324839406</v>
       </c>
       <c r="O8" t="n">
         <v>0.01682359942591915</v>
@@ -5019,28 +5019,28 @@
         <v>0.01649458980653533</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01663036462081543</v>
+        <v>0.01663036462081545</v>
       </c>
       <c r="R8" t="n">
-        <v>0.01652127036486781</v>
+        <v>0.0165212703648678</v>
       </c>
       <c r="S8" t="n">
-        <v>0.01655894819073319</v>
+        <v>0.01655894819073318</v>
       </c>
       <c r="T8" t="n">
-        <v>0.01677505033852774</v>
+        <v>0.01677505033852772</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01640089542754194</v>
+        <v>0.01640089542754195</v>
       </c>
       <c r="V8" t="n">
-        <v>0.01699065196211517</v>
+        <v>0.01699065196211516</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01626483128443323</v>
+        <v>0.01626483128443324</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01637187508897324</v>
+        <v>0.01637187508897323</v>
       </c>
       <c r="Y8" t="n">
         <v>0.01692958742360705</v>
@@ -5049,7 +5049,7 @@
         <v>0.01664572545085583</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01632517647137716</v>
+        <v>0.01632517647137714</v>
       </c>
       <c r="AB8" t="n">
         <v>0.01586285744759018</v>
@@ -5221,40 +5221,40 @@
         <v>0.01740440335048424</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01749493433947851</v>
+        <v>0.0174949343394785</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0173922020371869</v>
+        <v>0.01739220203718689</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03049057261605776</v>
+        <v>0.03049057261605775</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01759869888384511</v>
+        <v>0.0175986988838451</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0170982451437229</v>
+        <v>0.01709824514372288</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01751249183056796</v>
+        <v>0.01751249183056795</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01750658788351084</v>
+        <v>0.01750658788351083</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01751352835450864</v>
+        <v>0.01751352835450862</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01745766312822871</v>
+        <v>0.0174576631282287</v>
       </c>
       <c r="L2" t="n">
         <v>0.01756204255072306</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01736902984349662</v>
+        <v>0.01736902984349661</v>
       </c>
       <c r="N2" t="n">
-        <v>0.01755850718774514</v>
+        <v>0.01755850718774513</v>
       </c>
       <c r="O2" t="n">
         <v>0.01757080203073976</v>
@@ -5263,7 +5263,7 @@
         <v>0.01753610886887695</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.01736106629187852</v>
+        <v>0.01736106629187851</v>
       </c>
       <c r="R2" t="n">
         <v>0.01772410699241096</v>
@@ -5272,31 +5272,31 @@
         <v>0.01754260841158366</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01741224226507533</v>
+        <v>0.0174122422650753</v>
       </c>
       <c r="U2" t="n">
         <v>0.01733892664613948</v>
       </c>
       <c r="V2" t="n">
-        <v>0.01755770441904441</v>
+        <v>0.01755770441904443</v>
       </c>
       <c r="W2" t="n">
         <v>0.01780240479211841</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01763649890889724</v>
+        <v>0.01763649890889725</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.017511636866044</v>
+        <v>0.01751163686604399</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.01761515549976388</v>
+        <v>0.01761515549976387</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.01767529951193925</v>
+        <v>0.01767529951193924</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0166477904352591</v>
+        <v>0.01664779043525909</v>
       </c>
     </row>
     <row r="3">
@@ -5315,13 +5315,13 @@
         <v>0.01763376702911074</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03077282800249961</v>
+        <v>0.0307728280024996</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01768035140378949</v>
+        <v>0.01768035140378948</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01721436222573548</v>
+        <v>0.01721436222573547</v>
       </c>
       <c r="H3" t="n">
         <v>0.01763376702911074</v>
@@ -5330,10 +5330,10 @@
         <v>0.01763376702911074</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01762562063748294</v>
+        <v>0.01762562063748295</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01765893196946029</v>
+        <v>0.01765893196946028</v>
       </c>
       <c r="L3" t="n">
         <v>0.01763376702911074</v>
@@ -5366,25 +5366,25 @@
         <v>0.01763376702911074</v>
       </c>
       <c r="V3" t="n">
-        <v>0.01767397985206641</v>
+        <v>0.01767397985206631</v>
       </c>
       <c r="W3" t="n">
         <v>0.01763376702911074</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01705812937113905</v>
+        <v>0.01705812937113904</v>
       </c>
       <c r="Y3" t="n">
         <v>0.01763376702911074</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0176406244914737</v>
+        <v>0.01764062449147369</v>
       </c>
       <c r="AA3" t="n">
         <v>0.01763376702911074</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01693198690269388</v>
+        <v>0.01693198690269387</v>
       </c>
     </row>
     <row r="4">
@@ -5394,85 +5394,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0481582539875807</v>
+        <v>0.04815825398758077</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05159335091036651</v>
+        <v>0.05159335091036646</v>
       </c>
       <c r="D4" t="n">
-        <v>0.04807381454970693</v>
+        <v>0.04807381454970687</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0868725388256012</v>
+        <v>0.08687253882560125</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0898070610224609</v>
+        <v>0.08980706102246087</v>
       </c>
       <c r="G4" t="n">
-        <v>0.06198021457466726</v>
+        <v>0.06198021457466736</v>
       </c>
       <c r="H4" t="n">
         <v>0.08361530633554547</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07867167238537788</v>
+        <v>0.07867167238537774</v>
       </c>
       <c r="J4" t="n">
-        <v>0.07466484998072836</v>
+        <v>0.07466484998072834</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0563562779530735</v>
+        <v>0.05635627795307348</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07637558446949681</v>
+        <v>0.07637558446949669</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04152623913329969</v>
+        <v>0.04152623913329964</v>
       </c>
       <c r="N4" t="n">
-        <v>0.08759206097340479</v>
+        <v>0.08759206097340468</v>
       </c>
       <c r="O4" t="n">
-        <v>0.08360113955073672</v>
+        <v>0.08360113955073684</v>
       </c>
       <c r="P4" t="n">
-        <v>0.07827381727773047</v>
+        <v>0.07827381727773053</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.03793650391634258</v>
+        <v>0.03793650391634255</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1600548238973827</v>
+        <v>0.1600548238973823</v>
       </c>
       <c r="S4" t="n">
-        <v>0.07420922426292283</v>
+        <v>0.07420922426292284</v>
       </c>
       <c r="T4" t="n">
-        <v>0.05294751920852216</v>
+        <v>0.05294751920852209</v>
       </c>
       <c r="U4" t="n">
-        <v>0.03286850492805001</v>
+        <v>0.03286850492804999</v>
       </c>
       <c r="V4" t="n">
-        <v>0.07205123691237696</v>
+        <v>0.07205123691237711</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1438273244573504</v>
+        <v>0.1438273244573503</v>
       </c>
       <c r="X4" t="n">
-        <v>0.232997310519172</v>
+        <v>0.2329973105191722</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.07834467358709131</v>
+        <v>0.07834467358709134</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.09152924425894483</v>
+        <v>0.09152924425894467</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.1194803250255745</v>
+        <v>0.1194803250255747</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.02341834276453786</v>
+        <v>0.02341834276453784</v>
       </c>
     </row>
     <row r="5">
@@ -5482,85 +5482,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0158647845493126</v>
+        <v>0.01586478454931254</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02365060506604575</v>
+        <v>0.02365060506604564</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02365060506604575</v>
+        <v>0.02365060506604564</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01950488530838835</v>
+        <v>0.01950488530838826</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01707772439090396</v>
+        <v>0.0170777243909039</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02526504567003597</v>
+        <v>0.02526504567003586</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02365060506604575</v>
+        <v>0.02365060506604564</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02365060506604575</v>
+        <v>0.02365060506604564</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02363283022189424</v>
+        <v>0.02363283022189411</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02365060506604575</v>
+        <v>0.02365060506604564</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02365060506604575</v>
+        <v>0.02365060506604564</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02365060506604468</v>
+        <v>0.02365060506604456</v>
       </c>
       <c r="N5" t="n">
-        <v>0.08759206097340479</v>
+        <v>0.01761529162595438</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0192738481626152</v>
+        <v>0.0192738481626151</v>
       </c>
       <c r="P5" t="n">
-        <v>0.01886729587917979</v>
+        <v>0.01886729587917971</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01433469311530764</v>
+        <v>0.01433469311530761</v>
       </c>
       <c r="R5" t="n">
-        <v>0.02365060506604575</v>
+        <v>0.02365060506604564</v>
       </c>
       <c r="S5" t="n">
-        <v>0.02365060506604575</v>
+        <v>0.02365060506604564</v>
       </c>
       <c r="T5" t="n">
-        <v>0.02365060506604575</v>
+        <v>0.02365060506604564</v>
       </c>
       <c r="U5" t="n">
-        <v>0.01984530113677417</v>
+        <v>0.0198453011367741</v>
       </c>
       <c r="V5" t="n">
-        <v>0.02140297308437096</v>
+        <v>0.02140297308437086</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02365213520202135</v>
+        <v>0.02365213520202126</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01504827903581506</v>
+        <v>0.015048279035815</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.03138306100332022</v>
+        <v>0.03138306100332008</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.01572015893602736</v>
+        <v>0.01572015893602731</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.02365060506604575</v>
+        <v>0.02365060506604564</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.03178354563473047</v>
+        <v>0.03178354563473034</v>
       </c>
     </row>
     <row r="6">
@@ -5570,7 +5570,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01957767662938491</v>
+        <v>0.01957767662938489</v>
       </c>
       <c r="C6" t="n">
         <v>0.02399329800178229</v>
@@ -5579,13 +5579,13 @@
         <v>0.02399329800178229</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02297419356746373</v>
+        <v>0.02297419356746369</v>
       </c>
       <c r="F6" t="n">
         <v>0.01381408056550665</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02399330185958735</v>
+        <v>0.02399330185958733</v>
       </c>
       <c r="H6" t="n">
         <v>0.02399329800178229</v>
@@ -5594,7 +5594,7 @@
         <v>0.02399329800178229</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02397552315763082</v>
+        <v>0.02397552315763072</v>
       </c>
       <c r="K6" t="n">
         <v>0.02399329800178229</v>
@@ -5606,16 +5606,16 @@
         <v>0.02399329800178229</v>
       </c>
       <c r="N6" t="n">
-        <v>0.08759206097340479</v>
+        <v>0.02399329800178229</v>
       </c>
       <c r="O6" t="n">
-        <v>0.02545663427910941</v>
+        <v>0.0254566342791094</v>
       </c>
       <c r="P6" t="n">
-        <v>0.02577488397379868</v>
+        <v>0.02577488397379864</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.02399330185958735</v>
+        <v>0.02399330185958733</v>
       </c>
       <c r="R6" t="n">
         <v>0.02399329800178229</v>
@@ -5630,7 +5630,7 @@
         <v>0.02399329800178229</v>
       </c>
       <c r="V6" t="n">
-        <v>0.02897486350979334</v>
+        <v>0.02897486350979325</v>
       </c>
       <c r="W6" t="n">
         <v>0.02399329800178229</v>
@@ -5658,19 +5658,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0166100061457174</v>
+        <v>0.01661000614571739</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01670407918277835</v>
+        <v>0.01670407918277834</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01669735788728331</v>
+        <v>0.01669735788728329</v>
       </c>
       <c r="E7" t="n">
         <v>0.0288358216101967</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01579302733253044</v>
+        <v>0.01579302733253043</v>
       </c>
       <c r="G7" t="n">
         <v>0.01573272264993272</v>
@@ -5679,28 +5679,28 @@
         <v>0.01600387459305286</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01603035988910466</v>
+        <v>0.01603035988910465</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01591451065197433</v>
+        <v>0.01591451065197436</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0164720950157207</v>
+        <v>0.01647209501572069</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01568453874131495</v>
+        <v>0.01568453874131494</v>
       </c>
       <c r="M7" t="n">
         <v>0.01683615578290334</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01571510692225529</v>
+        <v>0.01571510692225528</v>
       </c>
       <c r="O7" t="n">
         <v>0.01561787052801749</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01582287759833016</v>
+        <v>0.01582287759833017</v>
       </c>
       <c r="Q7" t="n">
         <v>0.0168777895113175</v>
@@ -5712,31 +5712,31 @@
         <v>0.01579352203635417</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01658064551639139</v>
+        <v>0.0165806455163914</v>
       </c>
       <c r="U7" t="n">
         <v>0.01700292781833694</v>
       </c>
       <c r="V7" t="n">
-        <v>0.01597047030010345</v>
+        <v>0.01597047030010333</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01426919080583627</v>
+        <v>0.01426919080583625</v>
       </c>
       <c r="X7" t="n">
         <v>0.01160424330825066</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01598796962243282</v>
+        <v>0.01598796962243281</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.01540283350325743</v>
+        <v>0.01540283350325742</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01502149474314105</v>
+        <v>0.01502149474314104</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01659960522915822</v>
+        <v>0.01659960522915821</v>
       </c>
     </row>
     <row r="8">
@@ -5746,31 +5746,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01693858888600791</v>
+        <v>0.0169385888860079</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01702825674809183</v>
+        <v>0.01702825674809182</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01696613289349655</v>
+        <v>0.01696613289349654</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02960922853468683</v>
+        <v>0.02960922853468684</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0167399604168773</v>
+        <v>0.01673996041687729</v>
       </c>
       <c r="G8" t="n">
         <v>0.01642409441502747</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01677088557800261</v>
+        <v>0.0167708855780026</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01677703252505271</v>
+        <v>0.0167770325250527</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01673496785811825</v>
+        <v>0.01673496785811824</v>
       </c>
       <c r="K8" t="n">
         <v>0.01691764853205222</v>
@@ -5782,7 +5782,7 @@
         <v>0.01700611418463605</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01668551072471893</v>
+        <v>0.01668551072471891</v>
       </c>
       <c r="O8" t="n">
         <v>0.01665356269846134</v>
@@ -5797,16 +5797,16 @@
         <v>0.01618680666257582</v>
       </c>
       <c r="S8" t="n">
-        <v>0.01670529107536661</v>
+        <v>0.01670529107536662</v>
       </c>
       <c r="T8" t="n">
-        <v>0.01693306862068888</v>
+        <v>0.01693306862068889</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01705189279487212</v>
+        <v>0.01705189279487211</v>
       </c>
       <c r="V8" t="n">
-        <v>0.01678260214413843</v>
+        <v>0.01678260214413846</v>
       </c>
       <c r="W8" t="n">
         <v>0.0162715118882603</v>
@@ -5815,16 +5815,16 @@
         <v>0.01515496336977938</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.01676279380116039</v>
+        <v>0.0167627938011604</v>
       </c>
       <c r="Z8" t="n">
         <v>0.01659695346870873</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.0164867072970052</v>
+        <v>0.01648670729700519</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.01649655571456284</v>
+        <v>0.01649655571456283</v>
       </c>
     </row>
   </sheetData>
@@ -5990,31 +5990,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01677835915279521</v>
+        <v>0.0167783591527952</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01679096533208118</v>
+        <v>0.01679096533208117</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01671060174964183</v>
+        <v>0.01671060174964181</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03058892164990315</v>
+        <v>0.03058892164990311</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01683955290403676</v>
+        <v>0.01683955290403674</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01602008686524568</v>
+        <v>0.01602008686524567</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01669044449815716</v>
+        <v>0.01669044449815715</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01667290788574855</v>
+        <v>0.01667290788574854</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01675718372492202</v>
+        <v>0.01675718372492201</v>
       </c>
       <c r="K2" t="n">
         <v>0.01667683808348118</v>
@@ -6023,52 +6023,52 @@
         <v>0.01687206493457657</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01662671138831185</v>
+        <v>0.01662671138831183</v>
       </c>
       <c r="N2" t="n">
-        <v>0.01673599517936945</v>
+        <v>0.01673599517936943</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01705789578636806</v>
+        <v>0.01705789578636805</v>
       </c>
       <c r="P2" t="n">
-        <v>0.01688068366087662</v>
+        <v>0.01688068366087661</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.01662169615255754</v>
+        <v>0.01662169615255753</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01692302520858609</v>
+        <v>0.01692302520858607</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01678837218775488</v>
+        <v>0.01678837218775486</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01665028205933293</v>
+        <v>0.01665028205933292</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01662446787372217</v>
+        <v>0.01662446787372216</v>
       </c>
       <c r="V2" t="n">
         <v>0.01633559610591798</v>
       </c>
       <c r="W2" t="n">
-        <v>0.01699774804447213</v>
+        <v>0.01699774804447212</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0173932958788952</v>
+        <v>0.01739329587889519</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.01676736831051526</v>
+        <v>0.01676736831051524</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.01682210560687446</v>
+        <v>0.01682210560687445</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.01697632535198286</v>
+        <v>0.01697632535198285</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.01596235888830594</v>
+        <v>0.01596235888830593</v>
       </c>
     </row>
     <row r="3">
@@ -6078,85 +6078,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01689336657320269</v>
+        <v>0.01689336657320268</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01698896140868418</v>
+        <v>0.01698896140868417</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01689336657320269</v>
+        <v>0.01689336657320268</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0307885971208401</v>
+        <v>0.03078859712084009</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01695519283891474</v>
+        <v>0.01695519283891473</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01617381246474116</v>
+        <v>0.01617381246474115</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01689336657320269</v>
+        <v>0.01689336657320268</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01689336657320269</v>
+        <v>0.01689336657320268</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01688922121011146</v>
+        <v>0.01688922121011144</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01692562702197805</v>
+        <v>0.01692562702197804</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01689336657320269</v>
+        <v>0.01689336657320268</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01689336657320269</v>
+        <v>0.01689336657320268</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01689336657320269</v>
+        <v>0.01689336657320268</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01689336657320269</v>
+        <v>0.01689336657320268</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01689336657320269</v>
+        <v>0.01689336657320268</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01689336657320269</v>
+        <v>0.01689336657320268</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0167091605786089</v>
+        <v>0.01670916057860889</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01689336657320269</v>
+        <v>0.01689336657320268</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01689336657320269</v>
+        <v>0.01689336657320268</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01689336657320269</v>
+        <v>0.01689336657320268</v>
       </c>
       <c r="V3" t="n">
         <v>0.01640504406322647</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01689336657320269</v>
+        <v>0.01689336657320268</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01662946560835634</v>
+        <v>0.01662946560835633</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01689336657320269</v>
+        <v>0.01689336657320268</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01690011393926157</v>
+        <v>0.01690011393926156</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.01689336657320269</v>
+        <v>0.01689336657320268</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01619158644678583</v>
+        <v>0.01619158644678582</v>
       </c>
     </row>
     <row r="4">
@@ -6166,58 +6166,58 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.07152292638570894</v>
+        <v>0.07152292638570891</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05795545407344117</v>
+        <v>0.05795545407344124</v>
       </c>
       <c r="D4" t="n">
-        <v>0.06017155634082614</v>
+        <v>0.06017155634082611</v>
       </c>
       <c r="E4" t="n">
         <v>0.1017902732864946</v>
       </c>
       <c r="F4" t="n">
-        <v>0.08027202477390562</v>
+        <v>0.08027202477390574</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04741017519029344</v>
+        <v>0.04741017519029355</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05808549127868089</v>
+        <v>0.05808549127868091</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0520361851818283</v>
+        <v>0.05203618518182825</v>
       </c>
       <c r="J4" t="n">
-        <v>0.06873264109243903</v>
+        <v>0.06873264109243912</v>
       </c>
       <c r="K4" t="n">
-        <v>0.04358180216613115</v>
+        <v>0.04358180216613113</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08846389210624245</v>
+        <v>0.08846389210624246</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03948155519936169</v>
+        <v>0.03948155519936172</v>
       </c>
       <c r="N4" t="n">
-        <v>0.06583723582804531</v>
+        <v>0.06583723582804529</v>
       </c>
       <c r="O4" t="n">
         <v>0.131834258590986</v>
       </c>
       <c r="P4" t="n">
-        <v>0.092992437851584</v>
+        <v>0.09299243785158391</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.03653486941696493</v>
+        <v>0.03653486941696497</v>
       </c>
       <c r="R4" t="n">
         <v>0.1640382454457747</v>
       </c>
       <c r="S4" t="n">
-        <v>0.07221303373460557</v>
+        <v>0.07221303373460558</v>
       </c>
       <c r="T4" t="n">
         <v>0.04552689462868683</v>
@@ -6226,25 +6226,25 @@
         <v>0.03606257282797653</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0792958479338229</v>
+        <v>0.07929584793382299</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1278476745993354</v>
+        <v>0.1278476745993355</v>
       </c>
       <c r="X4" t="n">
         <v>0.2770440242156799</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.075026457859417</v>
+        <v>0.07502645785941718</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.07593662175492069</v>
+        <v>0.07593662175492065</v>
       </c>
       <c r="AA4" t="n">
         <v>0.1273394940734316</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.03494797343101315</v>
+        <v>0.03494797343101312</v>
       </c>
     </row>
     <row r="5">
@@ -6254,85 +6254,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01577171397112347</v>
+        <v>0.01577171397112348</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02348275343634382</v>
+        <v>0.02348275343634381</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02348275343634382</v>
+        <v>0.02348275343634381</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01937685238269916</v>
+        <v>0.01937685238269915</v>
       </c>
       <c r="F5" t="n">
         <v>0.01697300379888133</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02508168770215458</v>
+        <v>0.0250816877021546</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02348275343634382</v>
+        <v>0.02348275343634381</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02348275343634382</v>
+        <v>0.02348275343634381</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02346506235823531</v>
+        <v>0.02346506235823533</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02348275343634382</v>
+        <v>0.02348275343634381</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02348275343634382</v>
+        <v>0.02348275343634381</v>
       </c>
       <c r="M5" t="n">
         <v>0.02348275343634236</v>
       </c>
       <c r="N5" t="n">
-        <v>0.06583723582804533</v>
+        <v>0.01750540782179005</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01914803429670493</v>
+        <v>0.0191480342967049</v>
       </c>
       <c r="P5" t="n">
-        <v>0.01874538685632327</v>
+        <v>0.01874538685632324</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01425631872051423</v>
+        <v>0.01425631872051425</v>
       </c>
       <c r="R5" t="n">
-        <v>0.02348275343634382</v>
+        <v>0.02348275343634381</v>
       </c>
       <c r="S5" t="n">
-        <v>0.02348275343634382</v>
+        <v>0.02348275343634381</v>
       </c>
       <c r="T5" t="n">
-        <v>0.02348275343634382</v>
+        <v>0.02348275343634381</v>
       </c>
       <c r="U5" t="n">
         <v>0.01971418244059256</v>
       </c>
       <c r="V5" t="n">
-        <v>0.02125617650642028</v>
+        <v>0.0212561765064203</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0234842688757725</v>
+        <v>0.02348426887577248</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0149630508091031</v>
+        <v>0.01496305080910309</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.03114125538522778</v>
+        <v>0.03114125538522777</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.01562847745425552</v>
+        <v>0.01562847745425553</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.02348275343634382</v>
+        <v>0.02348275343634381</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.03153757894370246</v>
+        <v>0.03153757894370247</v>
       </c>
     </row>
     <row r="6">
@@ -6342,85 +6342,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01858473105571582</v>
+        <v>0.01858473105571584</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02271893913242547</v>
+        <v>0.02271893913242544</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02271893913242547</v>
+        <v>0.02271893913242544</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02176478341473997</v>
+        <v>0.02176478341473994</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01318845669773602</v>
+        <v>0.01318845669773601</v>
       </c>
       <c r="G6" t="n">
         <v>0.02271894256882387</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02271893913242547</v>
+        <v>0.02271893913242544</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02271893913242547</v>
+        <v>0.02271893913242544</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02270124805431693</v>
+        <v>0.0227012480543169</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02271893913242547</v>
+        <v>0.02271893913242544</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02271893913242547</v>
+        <v>0.02271893913242544</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02271893913242547</v>
+        <v>0.02271893913242544</v>
       </c>
       <c r="N6" t="n">
-        <v>0.06583723582804531</v>
+        <v>0.02271893913242544</v>
       </c>
       <c r="O6" t="n">
-        <v>0.02408901485098075</v>
+        <v>0.02408901485098073</v>
       </c>
       <c r="P6" t="n">
-        <v>0.02438698206586753</v>
+        <v>0.02438698206586748</v>
       </c>
       <c r="Q6" t="n">
         <v>0.02271894256882387</v>
       </c>
       <c r="R6" t="n">
-        <v>0.02271893913242547</v>
+        <v>0.02271893913242544</v>
       </c>
       <c r="S6" t="n">
-        <v>0.02271893913242547</v>
+        <v>0.02271893913242544</v>
       </c>
       <c r="T6" t="n">
-        <v>0.02271893913242547</v>
+        <v>0.02271893913242544</v>
       </c>
       <c r="U6" t="n">
-        <v>0.02271893913242547</v>
+        <v>0.02271893913242544</v>
       </c>
       <c r="V6" t="n">
-        <v>0.02737611827886612</v>
+        <v>0.02737611827886611</v>
       </c>
       <c r="W6" t="n">
-        <v>0.02271893913242547</v>
+        <v>0.02271893913242544</v>
       </c>
       <c r="X6" t="n">
-        <v>0.02271893913242547</v>
+        <v>0.02271893913242544</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.02271893913242547</v>
+        <v>0.02271893913242544</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.02022638065485133</v>
+        <v>0.02022638065485131</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.02271893913242547</v>
+        <v>0.02271893913242544</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.02271893913242547</v>
+        <v>0.02271893913242544</v>
       </c>
     </row>
     <row r="7">
@@ -6433,16 +6433,16 @@
         <v>0.01526069114372459</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01581803847686858</v>
+        <v>0.01581803847686859</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01568284387219132</v>
+        <v>0.01568284387219131</v>
       </c>
       <c r="E7" t="n">
         <v>0.0283645252479944</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01532829058414445</v>
+        <v>0.01532829058414444</v>
       </c>
       <c r="G7" t="n">
         <v>0.01514095002231968</v>
@@ -6451,19 +6451,19 @@
         <v>0.01580833417054532</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01590550311639503</v>
+        <v>0.01590550311639502</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01536846377976992</v>
+        <v>0.01536846377976989</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01608435831352296</v>
+        <v>0.01608435831352295</v>
       </c>
       <c r="L7" t="n">
         <v>0.01471700894309855</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01617699080142015</v>
+        <v>0.01617699080142014</v>
       </c>
       <c r="N7" t="n">
         <v>0.01552832014595368</v>
@@ -6472,7 +6472,7 @@
         <v>0.01359408229758529</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01464749656952607</v>
+        <v>0.01464749656952606</v>
       </c>
       <c r="Q7" t="n">
         <v>0.01620182863429091</v>
@@ -6487,13 +6487,13 @@
         <v>0.01603671741536982</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0161800444346808</v>
+        <v>0.01618004443468079</v>
       </c>
       <c r="V7" t="n">
-        <v>0.014543209077199</v>
+        <v>0.01454320907719901</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01397887331516869</v>
+        <v>0.01397887331516868</v>
       </c>
       <c r="X7" t="n">
         <v>0.01000106357264887</v>
@@ -6502,10 +6502,10 @@
         <v>0.01534109122129047</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.01504592987445426</v>
+        <v>0.01504592987445425</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01410758235686806</v>
+        <v>0.01410758235686805</v>
       </c>
       <c r="AB7" t="n">
         <v>0.01560759046812212</v>
@@ -6518,7 +6518,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01603548662935481</v>
+        <v>0.0160354866293548</v>
       </c>
       <c r="C8" t="n">
         <v>0.01625819166659512</v>
@@ -6527,10 +6527,10 @@
         <v>0.01615981006297471</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02948596122269965</v>
+        <v>0.02948596122269963</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01609930719348642</v>
+        <v>0.0160993071934864</v>
       </c>
       <c r="G8" t="n">
         <v>0.01555013116240659</v>
@@ -6542,28 +6542,28 @@
         <v>0.01622342686476703</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01606523424775026</v>
+        <v>0.01606523424775025</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0162940581401698</v>
+        <v>0.01629405814016982</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01588181527723894</v>
+        <v>0.01588181527723893</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01630075812919667</v>
+        <v>0.01630075812919666</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01611489470482629</v>
+        <v>0.01611489470482628</v>
       </c>
       <c r="O8" t="n">
         <v>0.01555671092676702</v>
       </c>
       <c r="P8" t="n">
-        <v>0.01585880565204072</v>
+        <v>0.01585880565204071</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01630704418655205</v>
+        <v>0.01630704418655204</v>
       </c>
       <c r="R8" t="n">
         <v>0.01536362759586521</v>
@@ -6572,10 +6572,10 @@
         <v>0.01602078288803104</v>
       </c>
       <c r="T8" t="n">
-        <v>0.01626050396254009</v>
+        <v>0.01626050396254008</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01629990402747193</v>
+        <v>0.01629990402747192</v>
       </c>
       <c r="V8" t="n">
         <v>0.01548845525395942</v>
@@ -6584,19 +6584,19 @@
         <v>0.01567164432412773</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01437735182918435</v>
+        <v>0.01437735182918433</v>
       </c>
       <c r="Y8" t="n">
         <v>0.01606107807858715</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.01597844594845313</v>
+        <v>0.01597844594845312</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01570878465578307</v>
+        <v>0.01570878465578304</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.01569663885692918</v>
+        <v>0.01569663885692917</v>
       </c>
     </row>
   </sheetData>
@@ -6765,19 +6765,19 @@
         <v>0.01824184446434622</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0179102421681317</v>
+        <v>0.01791024216813172</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01831028951446944</v>
+        <v>0.01831028951446945</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03071207778105232</v>
+        <v>0.03071207778105235</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01806622386378218</v>
+        <v>0.01806622386378216</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01823419900956154</v>
+        <v>0.01823419900956155</v>
       </c>
       <c r="H2" t="n">
         <v>0.01807585749348394</v>
@@ -6786,61 +6786,61 @@
         <v>0.0184136957250416</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01852127600416941</v>
+        <v>0.0185212760041694</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01877539472245904</v>
+        <v>0.01877539472245906</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01854440990153373</v>
+        <v>0.01854440990153376</v>
       </c>
       <c r="M2" t="n">
-        <v>0.02058084722779673</v>
+        <v>0.02058084722779674</v>
       </c>
       <c r="N2" t="n">
-        <v>0.01876320578090353</v>
+        <v>0.01876320578090355</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01821793342323794</v>
+        <v>0.01821793342323796</v>
       </c>
       <c r="P2" t="n">
-        <v>0.01850094108429385</v>
+        <v>0.01850094108429387</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.01814639231883953</v>
+        <v>0.01814639231883959</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01823994786510582</v>
+        <v>0.01823994786510585</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01834843630649637</v>
+        <v>0.01834843630649636</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01835697047266695</v>
+        <v>0.01835697047266694</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01865035820684144</v>
+        <v>0.01865035820684145</v>
       </c>
       <c r="V2" t="n">
-        <v>0.01796828813402733</v>
+        <v>0.01796828813402737</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0182864774497857</v>
+        <v>0.01828647744978572</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01850844787777139</v>
+        <v>0.01850844787777138</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.01828173735190232</v>
+        <v>0.01828173735190235</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.01818324190093619</v>
+        <v>0.01818324190093621</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.01857844099895617</v>
+        <v>0.0185784409989562</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.01841234778770985</v>
+        <v>0.01841234778770986</v>
       </c>
     </row>
     <row r="3">
@@ -6850,85 +6850,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01808357102125382</v>
+        <v>0.01808357102125385</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01817495293735196</v>
+        <v>0.018174952937352</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01808357102125382</v>
+        <v>0.01808357102125385</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03101608453982791</v>
+        <v>0.03101608453982796</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01811657858751605</v>
+        <v>0.01811657858751609</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01773069575306698</v>
+        <v>0.01773069575306702</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01808357102125382</v>
+        <v>0.01808357102125385</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01808357102125382</v>
+        <v>0.01808357102125385</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01805670861935143</v>
+        <v>0.01805670861935145</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01810131239594717</v>
+        <v>0.0181013123959472</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01808357102125382</v>
+        <v>0.01808357102125385</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01808357102125382</v>
+        <v>0.01808357102125385</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01808357102125382</v>
+        <v>0.01808357102125385</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01808357102125382</v>
+        <v>0.01808357102125385</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01808357102125382</v>
+        <v>0.01808357102125385</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01808357102125382</v>
+        <v>0.01808357102125385</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01808689597922977</v>
+        <v>0.0180868959792298</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01808357102125382</v>
+        <v>0.01808357102125385</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01808357102125382</v>
+        <v>0.01808357102125385</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01808357102125382</v>
+        <v>0.01808357102125385</v>
       </c>
       <c r="V3" t="n">
-        <v>0.01807056540992859</v>
+        <v>0.01807056540992862</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01808357102125382</v>
+        <v>0.01808357102125385</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01803534536856457</v>
+        <v>0.0180353453685646</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01808357102125382</v>
+        <v>0.01808357102125385</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01808764929583286</v>
+        <v>0.0180876492958329</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.01808357102125382</v>
+        <v>0.01808357102125385</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01738179089483696</v>
+        <v>0.01738179089483699</v>
       </c>
     </row>
     <row r="4">
@@ -6938,85 +6938,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.148893964575236</v>
+        <v>0.1488939645752373</v>
       </c>
       <c r="C4" t="n">
-        <v>0.04982489239235954</v>
+        <v>0.04982489239235964</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1884110102937429</v>
+        <v>0.188411010293743</v>
       </c>
       <c r="E4" t="n">
-        <v>0.08828697413649798</v>
+        <v>0.08828697413649818</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1093799774305411</v>
+        <v>0.109379977430541</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2245647840885282</v>
+        <v>0.2245647840885285</v>
       </c>
       <c r="H4" t="n">
         <v>0.1257728493449952</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2176991246813374</v>
+        <v>0.2176991246813372</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2323370718679098</v>
+        <v>0.23233707186791</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2829656452661015</v>
+        <v>0.2829656452661017</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2341253880578872</v>
+        <v>0.2341253880578895</v>
       </c>
       <c r="M4" t="n">
-        <v>0.769148110981087</v>
+        <v>0.7691481109810882</v>
       </c>
       <c r="N4" t="n">
         <v>0.3083382367951361</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1396895770242081</v>
+        <v>0.139689577024208</v>
       </c>
       <c r="P4" t="n">
         <v>0.2188415782936937</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1352691762941682</v>
+        <v>0.1352691762941683</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1712820271019724</v>
+        <v>0.1712820271019722</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1701839551988996</v>
+        <v>0.1701839551988999</v>
       </c>
       <c r="T4" t="n">
         <v>0.2012011593419385</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2636016065945078</v>
+        <v>0.2636016065945087</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0838614227800204</v>
+        <v>0.08386142278002073</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1738734313030444</v>
+        <v>0.1738734313030445</v>
       </c>
       <c r="X4" t="n">
-        <v>0.2525779076930331</v>
+        <v>0.2525779076930347</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1705221924195945</v>
+        <v>0.1705221924195946</v>
       </c>
       <c r="Z4" t="n">
         <v>0.1344341591472105</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.2526138934510375</v>
+        <v>0.2526138934510376</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.4176320410384335</v>
+        <v>0.4176320410384336</v>
       </c>
     </row>
     <row r="5">
@@ -7026,85 +7026,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01833805226902739</v>
+        <v>0.01833805226902745</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0276154076097025</v>
+        <v>0.02761540760970256</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0276154076097025</v>
+        <v>0.02761540760970256</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02267548955589014</v>
+        <v>0.02267548955589024</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01978335580421105</v>
+        <v>0.01978335580421107</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0295391276758607</v>
+        <v>0.02953912767586077</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0276154076097025</v>
+        <v>0.02761540760970253</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0276154076097025</v>
+        <v>0.02761540760970256</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02759281445762985</v>
+        <v>0.02759281445762992</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0276154076097025</v>
+        <v>0.02761540760970256</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0276154076097025</v>
+        <v>0.02761540760970256</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0276154076097046</v>
+        <v>0.02761540760970466</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3083382367951361</v>
+        <v>0.0204239051526273</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02240019246999465</v>
+        <v>0.02240019246999468</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0219157566947759</v>
+        <v>0.02191575669477593</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01651484019959085</v>
+        <v>0.01651484019959086</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0276154076097025</v>
+        <v>0.02761540760970253</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0276154076097025</v>
+        <v>0.02761540760970251</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0276154076097025</v>
+        <v>0.02761540760970256</v>
       </c>
       <c r="U5" t="n">
-        <v>0.023081787155697</v>
+        <v>0.02308178715569707</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0249288632592303</v>
+        <v>0.02492886325923031</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02761723087465651</v>
+        <v>0.02761723087465653</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01736512825022186</v>
+        <v>0.01736512825022183</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.03683031818104574</v>
+        <v>0.03683031818104582</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0181657206306615</v>
+        <v>0.01816572063066151</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0276154076097025</v>
+        <v>0.02761540760970253</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.03730638102178405</v>
+        <v>0.03730638102178386</v>
       </c>
     </row>
     <row r="6">
@@ -7114,85 +7114,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02484751933391123</v>
+        <v>0.02484751933391122</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03068575168777245</v>
+        <v>0.0306857516877725</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03068575168777245</v>
+        <v>0.0306857516877725</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02933830818487684</v>
+        <v>0.0293383081848767</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01722703828906378</v>
+        <v>0.01722703828906379</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03068574741148161</v>
+        <v>0.03068574741148165</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03068575168777245</v>
+        <v>0.0306857516877725</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03068575168777245</v>
+        <v>0.0306857516877725</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03066315853569979</v>
+        <v>0.03066315853569972</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03068575168777245</v>
+        <v>0.0306857516877725</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03068575168777245</v>
+        <v>0.0306857516877725</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03068575168777245</v>
+        <v>0.0306857516877725</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3083382367951361</v>
+        <v>0.0306857516877725</v>
       </c>
       <c r="O6" t="n">
-        <v>0.03262052855188205</v>
+        <v>0.03262052855188209</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0330413102546645</v>
+        <v>0.03304131025466456</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.03068574741148161</v>
+        <v>0.03068574741148165</v>
       </c>
       <c r="R6" t="n">
-        <v>0.03068575168777245</v>
+        <v>0.0306857516877725</v>
       </c>
       <c r="S6" t="n">
-        <v>0.03068575168777243</v>
+        <v>0.0306857516877725</v>
       </c>
       <c r="T6" t="n">
-        <v>0.03068575168777245</v>
+        <v>0.0306857516877725</v>
       </c>
       <c r="U6" t="n">
-        <v>0.03068575168777245</v>
+        <v>0.0306857516877725</v>
       </c>
       <c r="V6" t="n">
-        <v>0.03727805702327611</v>
+        <v>0.03727805702327618</v>
       </c>
       <c r="W6" t="n">
-        <v>0.03068575168777245</v>
+        <v>0.0306857516877725</v>
       </c>
       <c r="X6" t="n">
-        <v>0.03068575168777245</v>
+        <v>0.0306857516877725</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.03068575168777245</v>
+        <v>0.0306857516877725</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.02716581503620337</v>
+        <v>0.02716581503620336</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.03068575168777245</v>
+        <v>0.0306857516877725</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.03068575168777245</v>
+        <v>0.0306857516877725</v>
       </c>
     </row>
     <row r="7">
@@ -7208,37 +7208,37 @@
         <v>0.01729803412119718</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01437523954897817</v>
+        <v>0.01437523954897819</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02919678892390007</v>
+        <v>0.02919678892390012</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01602484633866863</v>
+        <v>0.01602484633866864</v>
       </c>
       <c r="G7" t="n">
         <v>0.01250140933882822</v>
       </c>
       <c r="H7" t="n">
-        <v>0.015764233687568</v>
+        <v>0.01576423368756804</v>
       </c>
       <c r="I7" t="n">
         <v>0.01377762414722731</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0129177014542232</v>
+        <v>0.01291770145422321</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01175458315193837</v>
+        <v>0.01175458315193839</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01295670545236517</v>
+        <v>0.01295670545236516</v>
       </c>
       <c r="M7" t="n">
-        <v>0.001139949930012282</v>
+        <v>0.001139949930012293</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01169532381084953</v>
+        <v>0.01169532381084959</v>
       </c>
       <c r="O7" t="n">
         <v>0.01486303396422821</v>
@@ -7247,40 +7247,40 @@
         <v>0.013173174344689</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.01532822536554354</v>
+        <v>0.01532822536554355</v>
       </c>
       <c r="R7" t="n">
         <v>0.01482133981032026</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01410251428441102</v>
+        <v>0.01410251428441103</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01410433749419273</v>
+        <v>0.01410433749419276</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01232460507506447</v>
+        <v>0.01232460507506446</v>
       </c>
       <c r="V7" t="n">
-        <v>0.01625484059436754</v>
+        <v>0.01625484059436756</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01448758283081214</v>
+        <v>0.01448758283081216</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01290321383946841</v>
+        <v>0.0129032138394684</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01452133280285559</v>
+        <v>0.01452133280285564</v>
       </c>
       <c r="Z7" t="n">
         <v>0.01510250112881607</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01276875143420968</v>
+        <v>0.01276875143420973</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.00932102970467104</v>
+        <v>0.009321029704671078</v>
       </c>
     </row>
     <row r="8">
@@ -7290,31 +7290,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01671336305229999</v>
+        <v>0.01671336305229997</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0175112413122068</v>
+        <v>0.01751124131220682</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01662298687683281</v>
+        <v>0.01662298687683283</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02988429247805403</v>
+        <v>0.02988429247805406</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01711447902460143</v>
+        <v>0.01711447902460144</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01585485702633586</v>
+        <v>0.01585485702633585</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01702055161536736</v>
+        <v>0.0170205516153674</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01645447617512102</v>
+        <v>0.01645447617512103</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01618301136699195</v>
+        <v>0.01618301136699197</v>
       </c>
       <c r="K8" t="n">
         <v>0.01588761269060901</v>
@@ -7326,46 +7326,46 @@
         <v>0.01287144563516521</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01585653294203366</v>
+        <v>0.01585653294203369</v>
       </c>
       <c r="O8" t="n">
-        <v>0.01675257879904864</v>
+        <v>0.01675257879904869</v>
       </c>
       <c r="P8" t="n">
-        <v>0.01626669494795112</v>
+        <v>0.01626669494795116</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01689270126472575</v>
+        <v>0.01689270126472579</v>
       </c>
       <c r="R8" t="n">
-        <v>0.01675410940154196</v>
+        <v>0.01675410940154197</v>
       </c>
       <c r="S8" t="n">
         <v>0.01653704280435782</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0165464065367893</v>
+        <v>0.01654640653678935</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01603001034858977</v>
+        <v>0.01603001034858979</v>
       </c>
       <c r="V8" t="n">
-        <v>0.01714212755657539</v>
+        <v>0.0171421275565754</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01665029136340031</v>
+        <v>0.01665029136340029</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01617331167689985</v>
+        <v>0.01617331167689988</v>
       </c>
       <c r="Y8" t="n">
         <v>0.01666090761035146</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.01682498997184081</v>
+        <v>0.01682498997184084</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01616018114952601</v>
+        <v>0.01616018114952603</v>
       </c>
       <c r="AB8" t="n">
         <v>0.01474467575806261</v>
@@ -7534,22 +7534,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01747741417860222</v>
+        <v>0.01747741417860223</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01764845691773026</v>
+        <v>0.01764845691773025</v>
       </c>
       <c r="D2" t="n">
         <v>0.01759106261028191</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03044779423487882</v>
+        <v>0.03044779423487885</v>
       </c>
       <c r="F2" t="n">
         <v>0.01768339123019203</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01781748954342865</v>
+        <v>0.01781748954342864</v>
       </c>
       <c r="H2" t="n">
         <v>0.01760763613739196</v>
@@ -7561,34 +7561,34 @@
         <v>0.01784329861782103</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01778428915912688</v>
+        <v>0.01778428915912689</v>
       </c>
       <c r="L2" t="n">
         <v>0.01808578543459604</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01776089114592683</v>
+        <v>0.01776089114592682</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0177413793092198</v>
+        <v>0.01774137930921979</v>
       </c>
       <c r="O2" t="n">
         <v>0.01763721042961271</v>
       </c>
       <c r="P2" t="n">
-        <v>0.01796796526620863</v>
+        <v>0.01796796526620864</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.01766785540102682</v>
+        <v>0.01766785540102683</v>
       </c>
       <c r="R2" t="n">
         <v>0.01786442122642609</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01779788194324582</v>
+        <v>0.01779788194324583</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01765992837207939</v>
+        <v>0.01765992837207937</v>
       </c>
       <c r="U2" t="n">
         <v>0.01760809047604225</v>
@@ -7603,16 +7603,16 @@
         <v>0.01774555285354198</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.01833844154651668</v>
+        <v>0.01833844154651667</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.01761896802063024</v>
+        <v>0.01761896802063023</v>
       </c>
       <c r="AA2" t="n">
         <v>0.01774056024824463</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.01765259594256742</v>
+        <v>0.01765259594256741</v>
       </c>
     </row>
     <row r="3">
@@ -7631,7 +7631,7 @@
         <v>0.0177827158640158</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03083011820079109</v>
+        <v>0.03083011820079108</v>
       </c>
       <c r="F3" t="n">
         <v>0.01782930023869455</v>
@@ -7646,7 +7646,7 @@
         <v>0.0177827158640158</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01775923869667947</v>
+        <v>0.01775923869667946</v>
       </c>
       <c r="K3" t="n">
         <v>0.01780788080436534</v>
@@ -7713,82 +7713,82 @@
         <v>0.03075128871747823</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05320172259955047</v>
+        <v>0.05320172259955051</v>
       </c>
       <c r="D4" t="n">
-        <v>0.06220953006201397</v>
+        <v>0.06220953006201402</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06213638174193938</v>
+        <v>0.06213638174193944</v>
       </c>
       <c r="F4" t="n">
-        <v>0.07483169492347132</v>
+        <v>0.07483169492347137</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1881660748489359</v>
+        <v>0.1881660748489357</v>
       </c>
       <c r="H4" t="n">
-        <v>0.07058940289293186</v>
+        <v>0.07058940289293188</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07187848396414608</v>
+        <v>0.07187848396414609</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1205151116928925</v>
+        <v>0.1205151116928926</v>
       </c>
       <c r="K4" t="n">
-        <v>0.09707667020203702</v>
+        <v>0.09707667020203707</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1690979177755145</v>
+        <v>0.1690979177755146</v>
       </c>
       <c r="M4" t="n">
         <v>0.1008864974445215</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1008086476581251</v>
+        <v>0.1008086476581252</v>
       </c>
       <c r="O4" t="n">
-        <v>0.06596506934611727</v>
+        <v>0.0659650693461174</v>
       </c>
       <c r="P4" t="n">
-        <v>0.144223097325677</v>
+        <v>0.1442230973256768</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.07581470382347251</v>
+        <v>0.07581470382347248</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1620381330818514</v>
+        <v>0.1620381330818516</v>
       </c>
       <c r="S4" t="n">
         <v>0.1011818474366674</v>
       </c>
       <c r="T4" t="n">
-        <v>0.08096084892198502</v>
+        <v>0.08096084892198489</v>
       </c>
       <c r="U4" t="n">
-        <v>0.06144473007482572</v>
+        <v>0.06144473007482569</v>
       </c>
       <c r="V4" t="n">
-        <v>0.06020810426584533</v>
+        <v>0.06020810426584531</v>
       </c>
       <c r="W4" t="n">
         <v>0.1561669525898659</v>
       </c>
       <c r="X4" t="n">
-        <v>0.2318721256926956</v>
+        <v>0.2318721256926954</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.2475690346165159</v>
+        <v>0.2475690346165153</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.06020208444779662</v>
+        <v>0.06020208444779661</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.09896278413170848</v>
+        <v>0.09896278413170846</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.2550378479858131</v>
+        <v>0.2550378479858132</v>
       </c>
     </row>
     <row r="5">
@@ -7798,85 +7798,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01638086539059789</v>
+        <v>0.0163808653905979</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02448836143587309</v>
+        <v>0.02448836143587311</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02448836143587309</v>
+        <v>0.02448836143587311</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02017135894813738</v>
+        <v>0.02017135894813739</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01764391852001741</v>
+        <v>0.01764391852001742</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02616950355621824</v>
+        <v>0.02616950355621825</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02448836143587309</v>
+        <v>0.02448836143587311</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02448836143587309</v>
+        <v>0.02448836143587311</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02446743494046554</v>
+        <v>0.02446743494046553</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02448836143587309</v>
+        <v>0.02448836143587311</v>
       </c>
       <c r="L5" t="n">
         <v>0.02448836143587309</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02448836143587303</v>
+        <v>0.02448836143587306</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1008086476581251</v>
+        <v>0.01820369564597645</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01993077637336465</v>
+        <v>0.01993077637336468</v>
       </c>
       <c r="P5" t="n">
-        <v>0.01950742715501566</v>
+        <v>0.01950742715501571</v>
       </c>
       <c r="Q5" t="n">
         <v>0.01478755737339887</v>
       </c>
       <c r="R5" t="n">
-        <v>0.02448836143587309</v>
+        <v>0.02448836143587311</v>
       </c>
       <c r="S5" t="n">
-        <v>0.02448836143587309</v>
+        <v>0.02448836143587311</v>
       </c>
       <c r="T5" t="n">
-        <v>0.02448836143587309</v>
+        <v>0.02448836143587311</v>
       </c>
       <c r="U5" t="n">
-        <v>0.02052481347292477</v>
+        <v>0.02052481347292478</v>
       </c>
       <c r="V5" t="n">
-        <v>0.02213130776321207</v>
+        <v>0.02213130776321209</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02448995479013664</v>
+        <v>0.02448995479013668</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01553062549517017</v>
+        <v>0.01553062549517018</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.03253853331367556</v>
+        <v>0.03253853331367559</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.01623026448923946</v>
+        <v>0.01623026448923949</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.02448836143587309</v>
+        <v>0.02448836143587311</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.03295731899203017</v>
+        <v>0.03295731899203024</v>
       </c>
     </row>
     <row r="6">
@@ -7889,82 +7889,82 @@
         <v>0.02104137460667304</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02585907535193157</v>
+        <v>0.02585907535193156</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02585907535193157</v>
+        <v>0.02585907535193156</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02474717215762216</v>
+        <v>0.02474717215762214</v>
       </c>
       <c r="F6" t="n">
         <v>0.01475295603919168</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02585907858469264</v>
+        <v>0.02585907858469265</v>
       </c>
       <c r="H6" t="n">
+        <v>0.02585907535193156</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.02585907535193156</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.02583814885652397</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.02585907535193156</v>
+      </c>
+      <c r="L6" t="n">
         <v>0.02585907535193157</v>
       </c>
-      <c r="I6" t="n">
-        <v>0.02585907535193157</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.02583814885652398</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.02585907535193157</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.02585907535193158</v>
-      </c>
       <c r="M6" t="n">
-        <v>0.02585907535193157</v>
+        <v>0.02585907535193156</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1008086476581251</v>
+        <v>0.02585907535193156</v>
       </c>
       <c r="O6" t="n">
-        <v>0.02745565937476409</v>
+        <v>0.02745565937476408</v>
       </c>
       <c r="P6" t="n">
-        <v>0.02780288830389085</v>
+        <v>0.02780288830389086</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.02585907858469264</v>
+        <v>0.02585907858469265</v>
       </c>
       <c r="R6" t="n">
-        <v>0.02585907535193157</v>
+        <v>0.02585907535193156</v>
       </c>
       <c r="S6" t="n">
-        <v>0.02585907535193157</v>
+        <v>0.02585907535193156</v>
       </c>
       <c r="T6" t="n">
-        <v>0.02585907535193157</v>
+        <v>0.02585907535193156</v>
       </c>
       <c r="U6" t="n">
-        <v>0.02585907535193157</v>
+        <v>0.02585907535193156</v>
       </c>
       <c r="V6" t="n">
-        <v>0.03128449309256674</v>
+        <v>0.03128449309256673</v>
       </c>
       <c r="W6" t="n">
-        <v>0.02585907535193157</v>
+        <v>0.02585907535193156</v>
       </c>
       <c r="X6" t="n">
-        <v>0.02585907535193157</v>
+        <v>0.02585907535193156</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.02585907535193157</v>
+        <v>0.02585907535193156</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0229544314928998</v>
+        <v>0.02295443149289979</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.02585907535193157</v>
+        <v>0.02585907535193156</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.02585907535193157</v>
+        <v>0.02585907535193156</v>
       </c>
     </row>
     <row r="7">
@@ -7983,7 +7983,7 @@
         <v>0.01654867338737425</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02948747857192889</v>
+        <v>0.02948747857192887</v>
       </c>
       <c r="F7" t="n">
         <v>0.01631127648643282</v>
@@ -7995,31 +7995,31 @@
         <v>0.01646062247709035</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01637288111669338</v>
+        <v>0.01637288111669337</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01488049024397197</v>
+        <v>0.01488049024397198</v>
       </c>
       <c r="K7" t="n">
         <v>0.01557353716332012</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01361244175187864</v>
+        <v>0.01361244175187863</v>
       </c>
       <c r="M7" t="n">
-        <v>0.015562383569795</v>
+        <v>0.01556238356979501</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01565921181755399</v>
+        <v>0.01565921181755398</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01625303737192679</v>
+        <v>0.0162530373719268</v>
       </c>
       <c r="P7" t="n">
         <v>0.01428006188504936</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.01609453234737395</v>
+        <v>0.01609453234737396</v>
       </c>
       <c r="R7" t="n">
         <v>0.01435362474423998</v>
@@ -8028,31 +8028,31 @@
         <v>0.01530653858028091</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01614633454677222</v>
+        <v>0.01614633454677221</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01643514628218871</v>
+        <v>0.0164351462821887</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0164070105222736</v>
+        <v>0.01640701052227361</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01432506057717757</v>
+        <v>0.01432506057717754</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01198182360119289</v>
+        <v>0.01198182360119288</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0121373846931602</v>
+        <v>0.01213738469316021</v>
       </c>
       <c r="Z7" t="n">
         <v>0.0164089149438209</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0156586570093872</v>
+        <v>0.01565865700938722</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01173121992395899</v>
+        <v>0.01173121992395898</v>
       </c>
     </row>
     <row r="8">
@@ -8062,16 +8062,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01721471781400861</v>
+        <v>0.0172147178140086</v>
       </c>
       <c r="C8" t="n">
         <v>0.01716717285376213</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01702956935074997</v>
+        <v>0.01702956935074998</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0298368889250079</v>
+        <v>0.02983688892500793</v>
       </c>
       <c r="F8" t="n">
         <v>0.01699268558525828</v>
@@ -8080,16 +8080,16 @@
         <v>0.01559803143547232</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01700607943307926</v>
+        <v>0.01700607943307925</v>
       </c>
       <c r="I8" t="n">
         <v>0.01698004838600952</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01653345889781213</v>
+        <v>0.01653345889781214</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01676765568202063</v>
+        <v>0.01676765568202062</v>
       </c>
       <c r="L8" t="n">
         <v>0.01618829742369857</v>
@@ -8098,46 +8098,46 @@
         <v>0.01675063287627719</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0167751782008738</v>
+        <v>0.01677517820087378</v>
       </c>
       <c r="O8" t="n">
-        <v>0.01694120184091609</v>
+        <v>0.0169412018409161</v>
       </c>
       <c r="P8" t="n">
-        <v>0.01637424654348301</v>
+        <v>0.016374246543483</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0168997265210331</v>
+        <v>0.01689972652103314</v>
       </c>
       <c r="R8" t="n">
         <v>0.01634765320861813</v>
       </c>
       <c r="S8" t="n">
-        <v>0.01667121338803766</v>
+        <v>0.01667121338803765</v>
       </c>
       <c r="T8" t="n">
-        <v>0.01691536965789571</v>
+        <v>0.01691536965789568</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01699494202186148</v>
+        <v>0.01699494202186146</v>
       </c>
       <c r="V8" t="n">
         <v>0.01697556173839935</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01639297979687344</v>
+        <v>0.01639297979687345</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01536804535643627</v>
+        <v>0.01536804535643625</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.01576979787317442</v>
+        <v>0.0157697978731744</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.01699076405666922</v>
+        <v>0.0169907640566692</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01677410670041466</v>
+        <v>0.01677410670041467</v>
       </c>
       <c r="AB8" t="n">
         <v>0.01521845819882848</v>
